--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1266]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1268]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8925" uniqueCount="7836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8939" uniqueCount="7850">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -16943,6 +16943,48 @@
   </si>
   <si>
     <t xml:space="preserve">Karten im Deck haben sich geändert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.cast.debuffed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n}장이 무력해졌습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} cards debuffed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} 枚が無力化されました</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} 张被削弱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} 張被削弱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} Karten geschwächt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.cast.hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n}장이 엎어졌습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} cards turned face down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} 枚が裏返りました</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} 张被翻面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} 張被翻面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} Karten umgedreht</t>
   </si>
   <si>
     <t xml:space="preserve">ui.note.rest_of_run</t>
@@ -23733,7 +23775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1266"/>
+  <dimension ref="A1:H1268"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -44675,50 +44717,50 @@
         <v>5695</v>
       </c>
       <c r="G912" s="6" t="s">
-        <v>5695</v>
+        <v>5696</v>
       </c>
       <c r="H912" s="6" t="s">
-        <v>5696</v>
+        <v>5697</v>
       </c>
     </row>
     <row r="913">
       <c r="B913" s="5" t="s">
-        <v>5697</v>
+        <v>5698</v>
       </c>
       <c r="C913" s="5" t="s">
-        <v>5698</v>
+        <v>5699</v>
       </c>
       <c r="D913" s="5" t="s">
-        <v>5699</v>
+        <v>5700</v>
       </c>
       <c r="E913" s="5" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="F913" s="5" t="s">
-        <v>5701</v>
+        <v>5702</v>
       </c>
       <c r="G913" s="5" t="s">
-        <v>5702</v>
+        <v>5703</v>
       </c>
       <c r="H913" s="5" t="s">
-        <v>5703</v>
+        <v>5704</v>
       </c>
     </row>
     <row r="914">
       <c r="B914" s="6" t="s">
-        <v>5704</v>
+        <v>5705</v>
       </c>
       <c r="C914" s="6" t="s">
-        <v>5705</v>
+        <v>5706</v>
       </c>
       <c r="D914" s="6" t="s">
-        <v>5706</v>
+        <v>5707</v>
       </c>
       <c r="E914" s="6" t="s">
-        <v>5707</v>
+        <v>5708</v>
       </c>
       <c r="F914" s="6" t="s">
-        <v>5708</v>
+        <v>5709</v>
       </c>
       <c r="G914" s="6" t="s">
         <v>5709</v>
@@ -44744,50 +44786,50 @@
         <v>5715</v>
       </c>
       <c r="G915" s="5" t="s">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="H915" s="5" t="s">
-        <v>5716</v>
+        <v>5717</v>
       </c>
     </row>
     <row r="916">
       <c r="B916" s="6" t="s">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="C916" s="6" t="s">
-        <v>5718</v>
+        <v>5719</v>
       </c>
       <c r="D916" s="6" t="s">
-        <v>5719</v>
+        <v>5720</v>
       </c>
       <c r="E916" s="6" t="s">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="F916" s="6" t="s">
-        <v>5721</v>
+        <v>5722</v>
       </c>
       <c r="G916" s="6" t="s">
-        <v>5722</v>
+        <v>5723</v>
       </c>
       <c r="H916" s="6" t="s">
-        <v>5723</v>
+        <v>5724</v>
       </c>
     </row>
     <row r="917">
       <c r="B917" s="5" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
       <c r="C917" s="5" t="s">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="D917" s="5" t="s">
-        <v>5726</v>
+        <v>5727</v>
       </c>
       <c r="E917" s="5" t="s">
-        <v>5727</v>
+        <v>5728</v>
       </c>
       <c r="F917" s="5" t="s">
-        <v>5728</v>
+        <v>5729</v>
       </c>
       <c r="G917" s="5" t="s">
         <v>5729</v>
@@ -44836,73 +44878,73 @@
         <v>5742</v>
       </c>
       <c r="G919" s="5" t="s">
-        <v>5742</v>
+        <v>5743</v>
       </c>
       <c r="H919" s="5" t="s">
-        <v>5743</v>
+        <v>5744</v>
       </c>
     </row>
     <row r="920">
       <c r="B920" s="6" t="s">
-        <v>5744</v>
+        <v>5745</v>
       </c>
       <c r="C920" s="6" t="s">
-        <v>5745</v>
+        <v>5746</v>
       </c>
       <c r="D920" s="6" t="s">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="E920" s="6" t="s">
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="F920" s="6" t="s">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="G920" s="6" t="s">
-        <v>5748</v>
+        <v>5750</v>
       </c>
       <c r="H920" s="6" t="s">
-        <v>5749</v>
+        <v>5751</v>
       </c>
     </row>
     <row r="921">
       <c r="B921" s="5" t="s">
-        <v>5750</v>
+        <v>5752</v>
       </c>
       <c r="C921" s="5" t="s">
-        <v>5751</v>
+        <v>5753</v>
       </c>
       <c r="D921" s="5" t="s">
-        <v>5752</v>
+        <v>5754</v>
       </c>
       <c r="E921" s="5" t="s">
-        <v>5753</v>
+        <v>5755</v>
       </c>
       <c r="F921" s="5" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="G921" s="5" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="H921" s="5" t="s">
-        <v>5756</v>
+        <v>5757</v>
       </c>
     </row>
     <row r="922">
       <c r="B922" s="6" t="s">
-        <v>5757</v>
+        <v>5758</v>
       </c>
       <c r="C922" s="6" t="s">
-        <v>5758</v>
+        <v>5759</v>
       </c>
       <c r="D922" s="6" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="E922" s="6" t="s">
-        <v>5760</v>
+        <v>5761</v>
       </c>
       <c r="F922" s="6" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="G922" s="6" t="s">
         <v>5762</v>
@@ -44988,111 +45030,111 @@
         <v>5786</v>
       </c>
       <c r="D926" s="6" t="s">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="E926" s="6" t="s">
-        <v>5786</v>
+        <v>5788</v>
       </c>
       <c r="F926" s="6" t="s">
-        <v>5786</v>
+        <v>5789</v>
       </c>
       <c r="G926" s="6" t="s">
-        <v>5786</v>
+        <v>5790</v>
       </c>
       <c r="H926" s="6" t="s">
-        <v>5786</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="927">
       <c r="B927" s="5" t="s">
-        <v>5787</v>
+        <v>5792</v>
       </c>
       <c r="C927" s="5" t="s">
-        <v>5788</v>
+        <v>5793</v>
       </c>
       <c r="D927" s="5" t="s">
-        <v>5789</v>
+        <v>5794</v>
       </c>
       <c r="E927" s="5" t="s">
-        <v>5790</v>
+        <v>5795</v>
       </c>
       <c r="F927" s="5" t="s">
-        <v>5791</v>
+        <v>5796</v>
       </c>
       <c r="G927" s="5" t="s">
-        <v>5792</v>
+        <v>5797</v>
       </c>
       <c r="H927" s="5" t="s">
-        <v>5793</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="928">
       <c r="B928" s="6" t="s">
-        <v>5794</v>
+        <v>5799</v>
       </c>
       <c r="C928" s="6" t="s">
-        <v>5795</v>
+        <v>5800</v>
       </c>
       <c r="D928" s="6" t="s">
-        <v>5796</v>
+        <v>5800</v>
       </c>
       <c r="E928" s="6" t="s">
-        <v>5797</v>
+        <v>5800</v>
       </c>
       <c r="F928" s="6" t="s">
-        <v>5798</v>
+        <v>5800</v>
       </c>
       <c r="G928" s="6" t="s">
-        <v>5799</v>
+        <v>5800</v>
       </c>
       <c r="H928" s="6" t="s">
-        <v>5796</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="929">
       <c r="B929" s="5" t="s">
-        <v>5800</v>
+        <v>5801</v>
       </c>
       <c r="C929" s="5" t="s">
-        <v>5801</v>
+        <v>5802</v>
       </c>
       <c r="D929" s="5" t="s">
-        <v>5802</v>
+        <v>5803</v>
       </c>
       <c r="E929" s="5" t="s">
-        <v>5803</v>
+        <v>5804</v>
       </c>
       <c r="F929" s="5" t="s">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="G929" s="5" t="s">
-        <v>5805</v>
+        <v>5806</v>
       </c>
       <c r="H929" s="5" t="s">
-        <v>5806</v>
+        <v>5807</v>
       </c>
     </row>
     <row r="930">
       <c r="B930" s="6" t="s">
-        <v>5807</v>
+        <v>5808</v>
       </c>
       <c r="C930" s="6" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="D930" s="6" t="s">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="E930" s="6" t="s">
+        <v>5811</v>
+      </c>
+      <c r="F930" s="6" t="s">
+        <v>5812</v>
+      </c>
+      <c r="G930" s="6" t="s">
+        <v>5813</v>
+      </c>
+      <c r="H930" s="6" t="s">
         <v>5810</v>
-      </c>
-      <c r="F930" s="6" t="s">
-        <v>5811</v>
-      </c>
-      <c r="G930" s="6" t="s">
-        <v>5812</v>
-      </c>
-      <c r="H930" s="6" t="s">
-        <v>5813</v>
       </c>
     </row>
     <row r="931">
@@ -45169,114 +45211,114 @@
         <v>5835</v>
       </c>
       <c r="C934" s="6" t="s">
-        <v>3163</v>
+        <v>5836</v>
       </c>
       <c r="D934" s="6" t="s">
-        <v>5836</v>
+        <v>5837</v>
       </c>
       <c r="E934" s="6" t="s">
-        <v>3165</v>
+        <v>5838</v>
       </c>
       <c r="F934" s="6" t="s">
-        <v>5837</v>
+        <v>5839</v>
       </c>
       <c r="G934" s="6" t="s">
-        <v>5838</v>
+        <v>5840</v>
       </c>
       <c r="H934" s="6" t="s">
-        <v>5839</v>
+        <v>5841</v>
       </c>
     </row>
     <row r="935">
       <c r="B935" s="5" t="s">
-        <v>5840</v>
+        <v>5842</v>
       </c>
       <c r="C935" s="5" t="s">
-        <v>3156</v>
+        <v>5843</v>
       </c>
       <c r="D935" s="5" t="s">
-        <v>5841</v>
+        <v>5844</v>
       </c>
       <c r="E935" s="5" t="s">
-        <v>3158</v>
+        <v>5845</v>
       </c>
       <c r="F935" s="5" t="s">
-        <v>5842</v>
+        <v>5846</v>
       </c>
       <c r="G935" s="5" t="s">
-        <v>5843</v>
+        <v>5847</v>
       </c>
       <c r="H935" s="5" t="s">
-        <v>5844</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="936">
       <c r="B936" s="6" t="s">
-        <v>5845</v>
+        <v>5849</v>
       </c>
       <c r="C936" s="6" t="s">
-        <v>4619</v>
+        <v>3163</v>
       </c>
       <c r="D936" s="6" t="s">
-        <v>4620</v>
+        <v>5850</v>
       </c>
       <c r="E936" s="6" t="s">
-        <v>4621</v>
+        <v>3165</v>
       </c>
       <c r="F936" s="6" t="s">
-        <v>4622</v>
+        <v>5851</v>
       </c>
       <c r="G936" s="6" t="s">
-        <v>4622</v>
+        <v>5852</v>
       </c>
       <c r="H936" s="6" t="s">
-        <v>4620</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="937">
       <c r="B937" s="5" t="s">
-        <v>5846</v>
+        <v>5854</v>
       </c>
       <c r="C937" s="5" t="s">
-        <v>5847</v>
+        <v>3156</v>
       </c>
       <c r="D937" s="5" t="s">
-        <v>5848</v>
+        <v>5855</v>
       </c>
       <c r="E937" s="5" t="s">
-        <v>5849</v>
+        <v>3158</v>
       </c>
       <c r="F937" s="5" t="s">
-        <v>5850</v>
+        <v>5856</v>
       </c>
       <c r="G937" s="5" t="s">
-        <v>5851</v>
+        <v>5857</v>
       </c>
       <c r="H937" s="5" t="s">
-        <v>5852</v>
+        <v>5858</v>
       </c>
     </row>
     <row r="938">
       <c r="B938" s="6" t="s">
-        <v>5853</v>
+        <v>5859</v>
       </c>
       <c r="C938" s="6" t="s">
-        <v>5854</v>
+        <v>4619</v>
       </c>
       <c r="D938" s="6" t="s">
-        <v>5855</v>
+        <v>4620</v>
       </c>
       <c r="E938" s="6" t="s">
-        <v>5856</v>
+        <v>4621</v>
       </c>
       <c r="F938" s="6" t="s">
-        <v>5857</v>
+        <v>4622</v>
       </c>
       <c r="G938" s="6" t="s">
-        <v>5858</v>
+        <v>4622</v>
       </c>
       <c r="H938" s="6" t="s">
-        <v>5859</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="939">
@@ -45399,114 +45441,114 @@
         <v>5895</v>
       </c>
       <c r="C944" s="6" t="s">
-        <v>4456</v>
+        <v>5896</v>
       </c>
       <c r="D944" s="6" t="s">
-        <v>4457</v>
+        <v>5897</v>
       </c>
       <c r="E944" s="6" t="s">
-        <v>4458</v>
+        <v>5898</v>
       </c>
       <c r="F944" s="6" t="s">
-        <v>4459</v>
+        <v>5899</v>
       </c>
       <c r="G944" s="6" t="s">
-        <v>4460</v>
+        <v>5900</v>
       </c>
       <c r="H944" s="6" t="s">
-        <v>4457</v>
+        <v>5901</v>
       </c>
     </row>
     <row r="945">
       <c r="B945" s="5" t="s">
-        <v>5896</v>
+        <v>5902</v>
       </c>
       <c r="C945" s="5" t="s">
-        <v>5897</v>
+        <v>5903</v>
       </c>
       <c r="D945" s="5" t="s">
-        <v>5898</v>
+        <v>5904</v>
       </c>
       <c r="E945" s="5" t="s">
-        <v>5899</v>
+        <v>5905</v>
       </c>
       <c r="F945" s="5" t="s">
-        <v>5900</v>
+        <v>5906</v>
       </c>
       <c r="G945" s="5" t="s">
-        <v>5901</v>
+        <v>5907</v>
       </c>
       <c r="H945" s="5" t="s">
-        <v>5902</v>
+        <v>5908</v>
       </c>
     </row>
     <row r="946">
       <c r="B946" s="6" t="s">
-        <v>5903</v>
+        <v>5909</v>
       </c>
       <c r="C946" s="6" t="s">
-        <v>4798</v>
+        <v>4456</v>
       </c>
       <c r="D946" s="6" t="s">
-        <v>4799</v>
+        <v>4457</v>
       </c>
       <c r="E946" s="6" t="s">
-        <v>4801</v>
+        <v>4458</v>
       </c>
       <c r="F946" s="6" t="s">
-        <v>4801</v>
+        <v>4459</v>
       </c>
       <c r="G946" s="6" t="s">
-        <v>4801</v>
+        <v>4460</v>
       </c>
       <c r="H946" s="6" t="s">
-        <v>5245</v>
+        <v>4457</v>
       </c>
     </row>
     <row r="947">
       <c r="B947" s="5" t="s">
-        <v>5904</v>
+        <v>5910</v>
       </c>
       <c r="C947" s="5" t="s">
-        <v>5905</v>
+        <v>5911</v>
       </c>
       <c r="D947" s="5" t="s">
-        <v>5906</v>
+        <v>5912</v>
       </c>
       <c r="E947" s="5" t="s">
-        <v>5907</v>
+        <v>5913</v>
       </c>
       <c r="F947" s="5" t="s">
-        <v>5908</v>
+        <v>5914</v>
       </c>
       <c r="G947" s="5" t="s">
-        <v>5909</v>
+        <v>5915</v>
       </c>
       <c r="H947" s="5" t="s">
-        <v>5910</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="948">
       <c r="B948" s="6" t="s">
-        <v>5911</v>
+        <v>5917</v>
       </c>
       <c r="C948" s="6" t="s">
-        <v>5912</v>
+        <v>4798</v>
       </c>
       <c r="D948" s="6" t="s">
-        <v>5913</v>
+        <v>4799</v>
       </c>
       <c r="E948" s="6" t="s">
-        <v>5914</v>
+        <v>4801</v>
       </c>
       <c r="F948" s="6" t="s">
-        <v>5915</v>
+        <v>4801</v>
       </c>
       <c r="G948" s="6" t="s">
-        <v>5916</v>
+        <v>4801</v>
       </c>
       <c r="H948" s="6" t="s">
-        <v>5917</v>
+        <v>5245</v>
       </c>
     </row>
     <row r="949">
@@ -45583,131 +45625,131 @@
         <v>5939</v>
       </c>
       <c r="C952" s="6" t="s">
-        <v>3882</v>
+        <v>5940</v>
       </c>
       <c r="D952" s="6" t="s">
-        <v>5275</v>
+        <v>5941</v>
       </c>
       <c r="E952" s="6" t="s">
-        <v>3884</v>
+        <v>5942</v>
       </c>
       <c r="F952" s="6" t="s">
-        <v>3885</v>
+        <v>5943</v>
       </c>
       <c r="G952" s="6" t="s">
-        <v>3885</v>
+        <v>5944</v>
       </c>
       <c r="H952" s="6" t="s">
-        <v>3886</v>
+        <v>5945</v>
       </c>
     </row>
     <row r="953">
       <c r="B953" s="5" t="s">
-        <v>5940</v>
+        <v>5946</v>
       </c>
       <c r="C953" s="5" t="s">
-        <v>3890</v>
+        <v>5947</v>
       </c>
       <c r="D953" s="5" t="s">
-        <v>4434</v>
+        <v>5948</v>
       </c>
       <c r="E953" s="5" t="s">
-        <v>3892</v>
+        <v>5949</v>
       </c>
       <c r="F953" s="5" t="s">
-        <v>3893</v>
+        <v>5950</v>
       </c>
       <c r="G953" s="5" t="s">
-        <v>3893</v>
+        <v>5951</v>
       </c>
       <c r="H953" s="5" t="s">
-        <v>4435</v>
+        <v>5952</v>
       </c>
     </row>
     <row r="954">
       <c r="B954" s="6" t="s">
-        <v>5941</v>
+        <v>5953</v>
       </c>
       <c r="C954" s="6" t="s">
-        <v>3751</v>
+        <v>3882</v>
       </c>
       <c r="D954" s="6" t="s">
-        <v>4796</v>
+        <v>5275</v>
       </c>
       <c r="E954" s="6" t="s">
-        <v>3753</v>
+        <v>3884</v>
       </c>
       <c r="F954" s="6" t="s">
-        <v>5942</v>
+        <v>3885</v>
       </c>
       <c r="G954" s="6" t="s">
-        <v>5942</v>
+        <v>3885</v>
       </c>
       <c r="H954" s="6" t="s">
-        <v>3123</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="955">
       <c r="B955" s="5" t="s">
-        <v>5943</v>
+        <v>5954</v>
       </c>
       <c r="C955" s="5" t="s">
-        <v>5944</v>
+        <v>3890</v>
       </c>
       <c r="D955" s="5" t="s">
-        <v>5945</v>
+        <v>4434</v>
       </c>
       <c r="E955" s="5" t="s">
-        <v>5946</v>
+        <v>3892</v>
       </c>
       <c r="F955" s="5" t="s">
-        <v>5947</v>
+        <v>3893</v>
       </c>
       <c r="G955" s="5" t="s">
-        <v>5947</v>
+        <v>3893</v>
       </c>
       <c r="H955" s="5" t="s">
-        <v>5948</v>
+        <v>4435</v>
       </c>
     </row>
     <row r="956">
       <c r="B956" s="6" t="s">
-        <v>5949</v>
+        <v>5955</v>
       </c>
       <c r="C956" s="6" t="s">
-        <v>5950</v>
+        <v>3751</v>
       </c>
       <c r="D956" s="6" t="s">
-        <v>5951</v>
+        <v>4796</v>
       </c>
       <c r="E956" s="6" t="s">
-        <v>5952</v>
+        <v>3753</v>
       </c>
       <c r="F956" s="6" t="s">
-        <v>5953</v>
+        <v>5956</v>
       </c>
       <c r="G956" s="6" t="s">
-        <v>5954</v>
+        <v>5956</v>
       </c>
       <c r="H956" s="6" t="s">
-        <v>5955</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="957">
       <c r="B957" s="5" t="s">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="C957" s="5" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="D957" s="5" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="E957" s="5" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
       <c r="F957" s="5" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="G957" s="5" t="s">
         <v>5961</v>
@@ -45733,96 +45775,96 @@
         <v>5967</v>
       </c>
       <c r="G958" s="6" t="s">
-        <v>5967</v>
+        <v>5968</v>
       </c>
       <c r="H958" s="6" t="s">
-        <v>5968</v>
+        <v>5969</v>
       </c>
     </row>
     <row r="959">
       <c r="B959" s="5" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="C959" s="5" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
       <c r="D959" s="5" t="s">
-        <v>5971</v>
+        <v>5972</v>
       </c>
       <c r="E959" s="5" t="s">
-        <v>5972</v>
+        <v>5973</v>
       </c>
       <c r="F959" s="5" t="s">
-        <v>5973</v>
+        <v>5974</v>
       </c>
       <c r="G959" s="5" t="s">
-        <v>5973</v>
+        <v>5975</v>
       </c>
       <c r="H959" s="5" t="s">
-        <v>5974</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="960">
       <c r="B960" s="6" t="s">
-        <v>5975</v>
+        <v>5977</v>
       </c>
       <c r="C960" s="6" t="s">
-        <v>5976</v>
+        <v>5978</v>
       </c>
       <c r="D960" s="6" t="s">
-        <v>5977</v>
+        <v>5979</v>
       </c>
       <c r="E960" s="6" t="s">
-        <v>5978</v>
+        <v>5980</v>
       </c>
       <c r="F960" s="6" t="s">
-        <v>5979</v>
+        <v>5981</v>
       </c>
       <c r="G960" s="6" t="s">
-        <v>5979</v>
+        <v>5981</v>
       </c>
       <c r="H960" s="6" t="s">
-        <v>5980</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="961">
       <c r="B961" s="5" t="s">
-        <v>5981</v>
+        <v>5983</v>
       </c>
       <c r="C961" s="5" t="s">
-        <v>5982</v>
+        <v>5984</v>
       </c>
       <c r="D961" s="5" t="s">
-        <v>5983</v>
+        <v>5985</v>
       </c>
       <c r="E961" s="5" t="s">
-        <v>5984</v>
+        <v>5986</v>
       </c>
       <c r="F961" s="5" t="s">
-        <v>5985</v>
+        <v>5987</v>
       </c>
       <c r="G961" s="5" t="s">
-        <v>5986</v>
+        <v>5987</v>
       </c>
       <c r="H961" s="5" t="s">
-        <v>5987</v>
+        <v>5988</v>
       </c>
     </row>
     <row r="962">
       <c r="B962" s="6" t="s">
-        <v>5988</v>
+        <v>5989</v>
       </c>
       <c r="C962" s="6" t="s">
-        <v>5989</v>
+        <v>5990</v>
       </c>
       <c r="D962" s="6" t="s">
-        <v>5990</v>
+        <v>5991</v>
       </c>
       <c r="E962" s="6" t="s">
-        <v>5991</v>
+        <v>5992</v>
       </c>
       <c r="F962" s="6" t="s">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="G962" s="6" t="s">
         <v>5993</v>
@@ -45917,102 +45959,102 @@
         <v>6020</v>
       </c>
       <c r="G966" s="6" t="s">
-        <v>6020</v>
+        <v>6021</v>
       </c>
       <c r="H966" s="6" t="s">
-        <v>6021</v>
+        <v>6022</v>
       </c>
     </row>
     <row r="967">
       <c r="B967" s="5" t="s">
-        <v>6022</v>
+        <v>6023</v>
       </c>
       <c r="C967" s="5" t="s">
-        <v>6023</v>
+        <v>6024</v>
       </c>
       <c r="D967" s="5" t="s">
-        <v>6024</v>
+        <v>6025</v>
       </c>
       <c r="E967" s="5" t="s">
-        <v>6025</v>
+        <v>6026</v>
       </c>
       <c r="F967" s="5" t="s">
-        <v>6026</v>
+        <v>6027</v>
       </c>
       <c r="G967" s="5" t="s">
-        <v>6027</v>
+        <v>6028</v>
       </c>
       <c r="H967" s="5" t="s">
-        <v>6028</v>
+        <v>6029</v>
       </c>
     </row>
     <row r="968">
       <c r="B968" s="6" t="s">
-        <v>6029</v>
+        <v>6030</v>
       </c>
       <c r="C968" s="6" t="s">
-        <v>6030</v>
+        <v>6031</v>
       </c>
       <c r="D968" s="6" t="s">
-        <v>6031</v>
+        <v>6032</v>
       </c>
       <c r="E968" s="6" t="s">
-        <v>6032</v>
+        <v>6033</v>
       </c>
       <c r="F968" s="6" t="s">
-        <v>6033</v>
+        <v>6034</v>
       </c>
       <c r="G968" s="6" t="s">
         <v>6034</v>
       </c>
       <c r="H968" s="6" t="s">
-        <v>5763</v>
+        <v>6035</v>
       </c>
     </row>
     <row r="969">
       <c r="B969" s="5" t="s">
-        <v>6035</v>
+        <v>6036</v>
       </c>
       <c r="C969" s="5" t="s">
-        <v>6036</v>
+        <v>6037</v>
       </c>
       <c r="D969" s="5" t="s">
-        <v>6037</v>
+        <v>6038</v>
       </c>
       <c r="E969" s="5" t="s">
-        <v>6038</v>
+        <v>6039</v>
       </c>
       <c r="F969" s="5" t="s">
-        <v>6039</v>
+        <v>6040</v>
       </c>
       <c r="G969" s="5" t="s">
-        <v>6040</v>
+        <v>6041</v>
       </c>
       <c r="H969" s="5" t="s">
-        <v>6041</v>
+        <v>6042</v>
       </c>
     </row>
     <row r="970">
       <c r="B970" s="6" t="s">
-        <v>6042</v>
+        <v>6043</v>
       </c>
       <c r="C970" s="6" t="s">
-        <v>6043</v>
+        <v>6044</v>
       </c>
       <c r="D970" s="6" t="s">
-        <v>6044</v>
+        <v>6045</v>
       </c>
       <c r="E970" s="6" t="s">
-        <v>6045</v>
+        <v>6046</v>
       </c>
       <c r="F970" s="6" t="s">
-        <v>6046</v>
+        <v>6047</v>
       </c>
       <c r="G970" s="6" t="s">
-        <v>6047</v>
+        <v>6048</v>
       </c>
       <c r="H970" s="6" t="s">
-        <v>6048</v>
+        <v>5777</v>
       </c>
     </row>
     <row r="971">
@@ -46029,59 +46071,59 @@
         <v>6052</v>
       </c>
       <c r="F971" s="5" t="s">
-        <v>6052</v>
+        <v>6053</v>
       </c>
       <c r="G971" s="5" t="s">
-        <v>6052</v>
+        <v>6054</v>
       </c>
       <c r="H971" s="5" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
     </row>
     <row r="972">
       <c r="B972" s="6" t="s">
-        <v>6053</v>
+        <v>6056</v>
       </c>
       <c r="C972" s="6" t="s">
-        <v>6054</v>
+        <v>6057</v>
       </c>
       <c r="D972" s="6" t="s">
-        <v>6055</v>
+        <v>6058</v>
       </c>
       <c r="E972" s="6" t="s">
-        <v>6056</v>
+        <v>6059</v>
       </c>
       <c r="F972" s="6" t="s">
-        <v>6057</v>
+        <v>6060</v>
       </c>
       <c r="G972" s="6" t="s">
-        <v>6058</v>
+        <v>6061</v>
       </c>
       <c r="H972" s="6" t="s">
-        <v>6059</v>
+        <v>6062</v>
       </c>
     </row>
     <row r="973">
       <c r="B973" s="5" t="s">
-        <v>6060</v>
+        <v>6063</v>
       </c>
       <c r="C973" s="5" t="s">
-        <v>6061</v>
+        <v>6064</v>
       </c>
       <c r="D973" s="5" t="s">
-        <v>6062</v>
+        <v>6065</v>
       </c>
       <c r="E973" s="5" t="s">
-        <v>6063</v>
+        <v>6066</v>
       </c>
       <c r="F973" s="5" t="s">
-        <v>6064</v>
+        <v>6066</v>
       </c>
       <c r="G973" s="5" t="s">
+        <v>6066</v>
+      </c>
+      <c r="H973" s="5" t="s">
         <v>6065</v>
-      </c>
-      <c r="H973" s="5" t="s">
-        <v>6066</v>
       </c>
     </row>
     <row r="974">
@@ -46138,111 +46180,111 @@
         <v>6082</v>
       </c>
       <c r="D976" s="6" t="s">
-        <v>6051</v>
+        <v>6083</v>
       </c>
       <c r="E976" s="6" t="s">
-        <v>6083</v>
+        <v>6084</v>
       </c>
       <c r="F976" s="6" t="s">
-        <v>6084</v>
+        <v>6085</v>
       </c>
       <c r="G976" s="6" t="s">
-        <v>6084</v>
+        <v>6086</v>
       </c>
       <c r="H976" s="6" t="s">
-        <v>6051</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="977">
       <c r="B977" s="5" t="s">
-        <v>6085</v>
+        <v>6088</v>
       </c>
       <c r="C977" s="5" t="s">
-        <v>6086</v>
+        <v>6089</v>
       </c>
       <c r="D977" s="5" t="s">
-        <v>6087</v>
+        <v>6090</v>
       </c>
       <c r="E977" s="5" t="s">
-        <v>6088</v>
+        <v>6091</v>
       </c>
       <c r="F977" s="5" t="s">
-        <v>6089</v>
+        <v>6092</v>
       </c>
       <c r="G977" s="5" t="s">
-        <v>6090</v>
+        <v>6093</v>
       </c>
       <c r="H977" s="5" t="s">
-        <v>6091</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="978">
       <c r="B978" s="6" t="s">
-        <v>6092</v>
+        <v>6095</v>
       </c>
       <c r="C978" s="6" t="s">
-        <v>6093</v>
+        <v>6096</v>
       </c>
       <c r="D978" s="6" t="s">
-        <v>6094</v>
+        <v>6065</v>
       </c>
       <c r="E978" s="6" t="s">
-        <v>6095</v>
+        <v>6097</v>
       </c>
       <c r="F978" s="6" t="s">
-        <v>6096</v>
+        <v>6098</v>
       </c>
       <c r="G978" s="6" t="s">
-        <v>6097</v>
+        <v>6098</v>
       </c>
       <c r="H978" s="6" t="s">
-        <v>6094</v>
+        <v>6065</v>
       </c>
     </row>
     <row r="979">
       <c r="B979" s="5" t="s">
-        <v>6098</v>
+        <v>6099</v>
       </c>
       <c r="C979" s="5" t="s">
-        <v>6099</v>
+        <v>6100</v>
       </c>
       <c r="D979" s="5" t="s">
-        <v>6100</v>
+        <v>6101</v>
       </c>
       <c r="E979" s="5" t="s">
-        <v>6101</v>
+        <v>6102</v>
       </c>
       <c r="F979" s="5" t="s">
-        <v>6102</v>
+        <v>6103</v>
       </c>
       <c r="G979" s="5" t="s">
-        <v>6103</v>
+        <v>6104</v>
       </c>
       <c r="H979" s="5" t="s">
-        <v>6104</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="980">
       <c r="B980" s="6" t="s">
-        <v>6105</v>
+        <v>6106</v>
       </c>
       <c r="C980" s="6" t="s">
-        <v>6106</v>
+        <v>6107</v>
       </c>
       <c r="D980" s="6" t="s">
-        <v>6107</v>
+        <v>6108</v>
       </c>
       <c r="E980" s="6" t="s">
+        <v>6109</v>
+      </c>
+      <c r="F980" s="6" t="s">
+        <v>6110</v>
+      </c>
+      <c r="G980" s="6" t="s">
+        <v>6111</v>
+      </c>
+      <c r="H980" s="6" t="s">
         <v>6108</v>
-      </c>
-      <c r="F980" s="6" t="s">
-        <v>6109</v>
-      </c>
-      <c r="G980" s="6" t="s">
-        <v>6110</v>
-      </c>
-      <c r="H980" s="6" t="s">
-        <v>6111</v>
       </c>
     </row>
     <row r="981">
@@ -46308,96 +46350,96 @@
         <v>6130</v>
       </c>
       <c r="G983" s="5" t="s">
-        <v>6130</v>
+        <v>6131</v>
       </c>
       <c r="H983" s="5" t="s">
-        <v>6131</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="984">
       <c r="B984" s="6" t="s">
-        <v>6132</v>
+        <v>6133</v>
       </c>
       <c r="C984" s="6" t="s">
-        <v>6133</v>
+        <v>6134</v>
       </c>
       <c r="D984" s="6" t="s">
-        <v>6134</v>
+        <v>6135</v>
       </c>
       <c r="E984" s="6" t="s">
-        <v>6135</v>
+        <v>6136</v>
       </c>
       <c r="F984" s="6" t="s">
-        <v>6136</v>
+        <v>6137</v>
       </c>
       <c r="G984" s="6" t="s">
-        <v>6137</v>
+        <v>6138</v>
       </c>
       <c r="H984" s="6" t="s">
-        <v>6138</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="985">
       <c r="B985" s="5" t="s">
-        <v>6139</v>
+        <v>6140</v>
       </c>
       <c r="C985" s="5" t="s">
-        <v>6140</v>
+        <v>6141</v>
       </c>
       <c r="D985" s="5" t="s">
-        <v>6141</v>
+        <v>6142</v>
       </c>
       <c r="E985" s="5" t="s">
-        <v>6142</v>
+        <v>6143</v>
       </c>
       <c r="F985" s="5" t="s">
-        <v>6143</v>
+        <v>6144</v>
       </c>
       <c r="G985" s="5" t="s">
-        <v>6143</v>
+        <v>6144</v>
       </c>
       <c r="H985" s="5" t="s">
-        <v>6144</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="986">
       <c r="B986" s="6" t="s">
-        <v>6145</v>
+        <v>6146</v>
       </c>
       <c r="C986" s="6" t="s">
-        <v>6146</v>
+        <v>6147</v>
       </c>
       <c r="D986" s="6" t="s">
-        <v>6147</v>
+        <v>6148</v>
       </c>
       <c r="E986" s="6" t="s">
-        <v>6148</v>
+        <v>6149</v>
       </c>
       <c r="F986" s="6" t="s">
-        <v>6149</v>
+        <v>6150</v>
       </c>
       <c r="G986" s="6" t="s">
-        <v>6150</v>
+        <v>6151</v>
       </c>
       <c r="H986" s="6" t="s">
-        <v>6151</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="987">
       <c r="B987" s="5" t="s">
-        <v>6152</v>
+        <v>6153</v>
       </c>
       <c r="C987" s="5" t="s">
-        <v>6153</v>
+        <v>6154</v>
       </c>
       <c r="D987" s="5" t="s">
-        <v>6154</v>
+        <v>6155</v>
       </c>
       <c r="E987" s="5" t="s">
-        <v>6155</v>
+        <v>6156</v>
       </c>
       <c r="F987" s="5" t="s">
-        <v>6156</v>
+        <v>6157</v>
       </c>
       <c r="G987" s="5" t="s">
         <v>6157</v>
@@ -46423,470 +46465,470 @@
         <v>6163</v>
       </c>
       <c r="G988" s="6" t="s">
-        <v>6162</v>
+        <v>6164</v>
       </c>
       <c r="H988" s="6" t="s">
-        <v>6164</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="989">
       <c r="B989" s="5" t="s">
-        <v>6165</v>
+        <v>6166</v>
       </c>
       <c r="C989" s="5" t="s">
-        <v>6166</v>
+        <v>6167</v>
       </c>
       <c r="D989" s="5" t="s">
-        <v>6167</v>
+        <v>6168</v>
       </c>
       <c r="E989" s="5" t="s">
-        <v>6168</v>
+        <v>6169</v>
       </c>
       <c r="F989" s="5" t="s">
-        <v>6169</v>
+        <v>6170</v>
       </c>
       <c r="G989" s="5" t="s">
-        <v>6169</v>
+        <v>6171</v>
       </c>
       <c r="H989" s="5" t="s">
-        <v>6167</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="990">
       <c r="B990" s="6" t="s">
-        <v>6170</v>
+        <v>6173</v>
       </c>
       <c r="C990" s="6" t="s">
-        <v>6171</v>
+        <v>6174</v>
       </c>
       <c r="D990" s="6" t="s">
-        <v>6172</v>
+        <v>6175</v>
       </c>
       <c r="E990" s="6" t="s">
-        <v>6173</v>
+        <v>6176</v>
       </c>
       <c r="F990" s="6" t="s">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="G990" s="6" t="s">
-        <v>6175</v>
+        <v>6176</v>
       </c>
       <c r="H990" s="6" t="s">
-        <v>6176</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="991">
       <c r="B991" s="5" t="s">
-        <v>6177</v>
+        <v>6179</v>
       </c>
       <c r="C991" s="5" t="s">
-        <v>6178</v>
+        <v>6180</v>
       </c>
       <c r="D991" s="5" t="s">
-        <v>6179</v>
+        <v>6181</v>
       </c>
       <c r="E991" s="5" t="s">
-        <v>6180</v>
+        <v>6182</v>
       </c>
       <c r="F991" s="5" t="s">
+        <v>6183</v>
+      </c>
+      <c r="G991" s="5" t="s">
+        <v>6183</v>
+      </c>
+      <c r="H991" s="5" t="s">
         <v>6181</v>
-      </c>
-      <c r="G991" s="5" t="s">
-        <v>6182</v>
-      </c>
-      <c r="H991" s="5" t="s">
-        <v>6179</v>
       </c>
     </row>
     <row r="992">
       <c r="B992" s="6" t="s">
-        <v>6183</v>
+        <v>6184</v>
       </c>
       <c r="C992" s="6" t="s">
-        <v>6184</v>
+        <v>6185</v>
       </c>
       <c r="D992" s="6" t="s">
-        <v>6185</v>
+        <v>6186</v>
       </c>
       <c r="E992" s="6" t="s">
-        <v>6186</v>
+        <v>6187</v>
       </c>
       <c r="F992" s="6" t="s">
-        <v>6187</v>
+        <v>6188</v>
       </c>
       <c r="G992" s="6" t="s">
-        <v>6188</v>
+        <v>6189</v>
       </c>
       <c r="H992" s="6" t="s">
-        <v>6189</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="993">
       <c r="B993" s="5" t="s">
-        <v>6190</v>
+        <v>6191</v>
       </c>
       <c r="C993" s="5" t="s">
-        <v>6191</v>
+        <v>6192</v>
       </c>
       <c r="D993" s="5" t="s">
-        <v>6192</v>
+        <v>6193</v>
       </c>
       <c r="E993" s="5" t="s">
+        <v>6194</v>
+      </c>
+      <c r="F993" s="5" t="s">
+        <v>6195</v>
+      </c>
+      <c r="G993" s="5" t="s">
+        <v>6196</v>
+      </c>
+      <c r="H993" s="5" t="s">
         <v>6193</v>
-      </c>
-      <c r="F993" s="5" t="s">
-        <v>6194</v>
-      </c>
-      <c r="G993" s="5" t="s">
-        <v>6194</v>
-      </c>
-      <c r="H993" s="5" t="s">
-        <v>6195</v>
       </c>
     </row>
     <row r="994">
       <c r="B994" s="6" t="s">
-        <v>6196</v>
+        <v>6197</v>
       </c>
       <c r="C994" s="6" t="s">
-        <v>6197</v>
+        <v>6198</v>
       </c>
       <c r="D994" s="6" t="s">
-        <v>6198</v>
+        <v>6199</v>
       </c>
       <c r="E994" s="6" t="s">
-        <v>6199</v>
+        <v>6200</v>
       </c>
       <c r="F994" s="6" t="s">
-        <v>6200</v>
+        <v>6201</v>
       </c>
       <c r="G994" s="6" t="s">
-        <v>6200</v>
+        <v>6202</v>
       </c>
       <c r="H994" s="6" t="s">
-        <v>6201</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="995">
       <c r="B995" s="5" t="s">
-        <v>6202</v>
+        <v>6204</v>
       </c>
       <c r="C995" s="5" t="s">
-        <v>6203</v>
+        <v>6205</v>
       </c>
       <c r="D995" s="5" t="s">
-        <v>6204</v>
+        <v>6206</v>
       </c>
       <c r="E995" s="5" t="s">
-        <v>6205</v>
+        <v>6207</v>
       </c>
       <c r="F995" s="5" t="s">
-        <v>6206</v>
+        <v>6208</v>
       </c>
       <c r="G995" s="5" t="s">
-        <v>6207</v>
+        <v>6208</v>
       </c>
       <c r="H995" s="5" t="s">
-        <v>6208</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="996">
       <c r="B996" s="6" t="s">
-        <v>6209</v>
+        <v>6210</v>
       </c>
       <c r="C996" s="6" t="s">
-        <v>6210</v>
+        <v>6211</v>
       </c>
       <c r="D996" s="6" t="s">
-        <v>6211</v>
+        <v>6212</v>
       </c>
       <c r="E996" s="6" t="s">
-        <v>6212</v>
+        <v>6213</v>
       </c>
       <c r="F996" s="6" t="s">
-        <v>6213</v>
+        <v>6214</v>
       </c>
       <c r="G996" s="6" t="s">
-        <v>6213</v>
+        <v>6214</v>
       </c>
       <c r="H996" s="6" t="s">
-        <v>6214</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="997">
       <c r="B997" s="5" t="s">
-        <v>6215</v>
+        <v>6216</v>
       </c>
       <c r="C997" s="5" t="s">
-        <v>6216</v>
+        <v>6217</v>
       </c>
       <c r="D997" s="5" t="s">
-        <v>6217</v>
+        <v>6218</v>
       </c>
       <c r="E997" s="5" t="s">
-        <v>6218</v>
+        <v>6219</v>
       </c>
       <c r="F997" s="5" t="s">
-        <v>6219</v>
+        <v>6220</v>
       </c>
       <c r="G997" s="5" t="s">
-        <v>6220</v>
+        <v>6221</v>
       </c>
       <c r="H997" s="5" t="s">
-        <v>6221</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="998">
       <c r="B998" s="6" t="s">
-        <v>6222</v>
+        <v>6223</v>
       </c>
       <c r="C998" s="6" t="s">
-        <v>6223</v>
+        <v>6224</v>
       </c>
       <c r="D998" s="6" t="s">
-        <v>6224</v>
+        <v>6225</v>
       </c>
       <c r="E998" s="6" t="s">
-        <v>6225</v>
+        <v>6226</v>
       </c>
       <c r="F998" s="6" t="s">
-        <v>6226</v>
+        <v>6227</v>
       </c>
       <c r="G998" s="6" t="s">
-        <v>6226</v>
+        <v>6227</v>
       </c>
       <c r="H998" s="6" t="s">
-        <v>6227</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="999">
       <c r="B999" s="5" t="s">
-        <v>6228</v>
+        <v>6229</v>
       </c>
       <c r="C999" s="5" t="s">
-        <v>6229</v>
+        <v>6230</v>
       </c>
       <c r="D999" s="5" t="s">
-        <v>6230</v>
+        <v>6231</v>
       </c>
       <c r="E999" s="5" t="s">
-        <v>6231</v>
+        <v>6232</v>
       </c>
       <c r="F999" s="5" t="s">
-        <v>6232</v>
+        <v>6233</v>
       </c>
       <c r="G999" s="5" t="s">
-        <v>6232</v>
+        <v>6234</v>
       </c>
       <c r="H999" s="5" t="s">
-        <v>6233</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="1000">
       <c r="B1000" s="6" t="s">
-        <v>6234</v>
+        <v>6236</v>
       </c>
       <c r="C1000" s="6" t="s">
-        <v>6235</v>
+        <v>6237</v>
       </c>
       <c r="D1000" s="6" t="s">
-        <v>6235</v>
+        <v>6238</v>
       </c>
       <c r="E1000" s="6" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="F1000" s="6" t="s">
-        <v>6235</v>
+        <v>6240</v>
       </c>
       <c r="G1000" s="6" t="s">
-        <v>6235</v>
+        <v>6240</v>
       </c>
       <c r="H1000" s="6" t="s">
-        <v>6235</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="1001">
       <c r="B1001" s="5" t="s">
-        <v>6236</v>
+        <v>6242</v>
       </c>
       <c r="C1001" s="5" t="s">
-        <v>6237</v>
+        <v>6243</v>
       </c>
       <c r="D1001" s="5" t="s">
-        <v>6238</v>
+        <v>6244</v>
       </c>
       <c r="E1001" s="5" t="s">
-        <v>6239</v>
+        <v>6245</v>
       </c>
       <c r="F1001" s="5" t="s">
-        <v>6240</v>
+        <v>6246</v>
       </c>
       <c r="G1001" s="5" t="s">
-        <v>6240</v>
+        <v>6246</v>
       </c>
       <c r="H1001" s="5" t="s">
-        <v>6238</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="1002">
       <c r="B1002" s="6" t="s">
-        <v>6241</v>
+        <v>6248</v>
       </c>
       <c r="C1002" s="6" t="s">
-        <v>6242</v>
+        <v>6249</v>
       </c>
       <c r="D1002" s="6" t="s">
-        <v>6243</v>
+        <v>6249</v>
       </c>
       <c r="E1002" s="6" t="s">
-        <v>6244</v>
+        <v>6249</v>
       </c>
       <c r="F1002" s="6" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="G1002" s="6" t="s">
-        <v>6246</v>
+        <v>6249</v>
       </c>
       <c r="H1002" s="6" t="s">
-        <v>6243</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="1003">
       <c r="B1003" s="5" t="s">
-        <v>6247</v>
+        <v>6250</v>
       </c>
       <c r="C1003" s="5" t="s">
-        <v>6248</v>
+        <v>6251</v>
       </c>
       <c r="D1003" s="5" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
       <c r="E1003" s="5" t="s">
-        <v>6250</v>
+        <v>6253</v>
       </c>
       <c r="F1003" s="5" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="G1003" s="5" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="H1003" s="5" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="1004">
       <c r="B1004" s="6" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="C1004" s="6" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="D1004" s="6" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="E1004" s="6" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
       <c r="F1004" s="6" t="s">
-        <v>6254</v>
+        <v>6259</v>
       </c>
       <c r="G1004" s="6" t="s">
-        <v>6254</v>
+        <v>6260</v>
       </c>
       <c r="H1004" s="6" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1005">
       <c r="B1005" s="5" t="s">
-        <v>6255</v>
+        <v>6261</v>
       </c>
       <c r="C1005" s="5" t="s">
-        <v>6256</v>
+        <v>6262</v>
       </c>
       <c r="D1005" s="5" t="s">
-        <v>6257</v>
+        <v>6263</v>
       </c>
       <c r="E1005" s="5" t="s">
-        <v>6258</v>
+        <v>6264</v>
       </c>
       <c r="F1005" s="5" t="s">
-        <v>6259</v>
+        <v>6264</v>
       </c>
       <c r="G1005" s="5" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="H1005" s="5" t="s">
-        <v>6261</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="1006">
       <c r="B1006" s="6" t="s">
-        <v>6262</v>
+        <v>6265</v>
       </c>
       <c r="C1006" s="6" t="s">
-        <v>6263</v>
+        <v>6266</v>
       </c>
       <c r="D1006" s="6" t="s">
-        <v>6264</v>
+        <v>6267</v>
       </c>
       <c r="E1006" s="6" t="s">
-        <v>6265</v>
+        <v>6268</v>
       </c>
       <c r="F1006" s="6" t="s">
-        <v>6266</v>
+        <v>6268</v>
       </c>
       <c r="G1006" s="6" t="s">
+        <v>6268</v>
+      </c>
+      <c r="H1006" s="6" t="s">
         <v>6267</v>
-      </c>
-      <c r="H1006" s="6" t="s">
-        <v>6264</v>
       </c>
     </row>
     <row r="1007">
       <c r="B1007" s="5" t="s">
-        <v>6268</v>
+        <v>6269</v>
       </c>
       <c r="C1007" s="5" t="s">
-        <v>6269</v>
+        <v>6270</v>
       </c>
       <c r="D1007" s="5" t="s">
-        <v>6270</v>
+        <v>6271</v>
       </c>
       <c r="E1007" s="5" t="s">
-        <v>6271</v>
+        <v>6272</v>
       </c>
       <c r="F1007" s="5" t="s">
-        <v>6272</v>
+        <v>6273</v>
       </c>
       <c r="G1007" s="5" t="s">
-        <v>6273</v>
+        <v>6274</v>
       </c>
       <c r="H1007" s="5" t="s">
-        <v>6274</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="1008">
       <c r="B1008" s="6" t="s">
-        <v>6275</v>
+        <v>6276</v>
       </c>
       <c r="C1008" s="6" t="s">
-        <v>6276</v>
+        <v>6277</v>
       </c>
       <c r="D1008" s="6" t="s">
-        <v>6277</v>
+        <v>6278</v>
       </c>
       <c r="E1008" s="6" t="s">
+        <v>6279</v>
+      </c>
+      <c r="F1008" s="6" t="s">
+        <v>6280</v>
+      </c>
+      <c r="G1008" s="6" t="s">
+        <v>6281</v>
+      </c>
+      <c r="H1008" s="6" t="s">
         <v>6278</v>
-      </c>
-      <c r="F1008" s="6" t="s">
-        <v>6279</v>
-      </c>
-      <c r="G1008" s="6" t="s">
-        <v>6280</v>
-      </c>
-      <c r="H1008" s="6" t="s">
-        <v>6281</v>
       </c>
     </row>
     <row r="1009">
@@ -46932,116 +46974,116 @@
         <v>6294</v>
       </c>
       <c r="H1010" s="6" t="s">
-        <v>6264</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="1011">
       <c r="B1011" s="5" t="s">
-        <v>6295</v>
+        <v>6296</v>
       </c>
       <c r="C1011" s="5" t="s">
-        <v>6296</v>
+        <v>6297</v>
       </c>
       <c r="D1011" s="5" t="s">
-        <v>6297</v>
+        <v>6298</v>
       </c>
       <c r="E1011" s="5" t="s">
-        <v>6298</v>
+        <v>6299</v>
       </c>
       <c r="F1011" s="5" t="s">
-        <v>6299</v>
+        <v>6300</v>
       </c>
       <c r="G1011" s="5" t="s">
-        <v>6300</v>
+        <v>6301</v>
       </c>
       <c r="H1011" s="5" t="s">
-        <v>6301</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="1012">
       <c r="B1012" s="6" t="s">
-        <v>6302</v>
+        <v>6303</v>
       </c>
       <c r="C1012" s="6" t="s">
-        <v>6303</v>
+        <v>6304</v>
       </c>
       <c r="D1012" s="6" t="s">
-        <v>6304</v>
+        <v>6305</v>
       </c>
       <c r="E1012" s="6" t="s">
-        <v>6305</v>
+        <v>6306</v>
       </c>
       <c r="F1012" s="6" t="s">
-        <v>6306</v>
+        <v>6307</v>
       </c>
       <c r="G1012" s="6" t="s">
-        <v>6306</v>
+        <v>6308</v>
       </c>
       <c r="H1012" s="6" t="s">
-        <v>6307</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="1013">
       <c r="B1013" s="5" t="s">
-        <v>6308</v>
+        <v>6309</v>
       </c>
       <c r="C1013" s="5" t="s">
-        <v>6309</v>
+        <v>6310</v>
       </c>
       <c r="D1013" s="5" t="s">
-        <v>6310</v>
+        <v>6311</v>
       </c>
       <c r="E1013" s="5" t="s">
-        <v>6311</v>
+        <v>6312</v>
       </c>
       <c r="F1013" s="5" t="s">
-        <v>6312</v>
+        <v>6313</v>
       </c>
       <c r="G1013" s="5" t="s">
-        <v>6312</v>
+        <v>6314</v>
       </c>
       <c r="H1013" s="5" t="s">
-        <v>6313</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="1014">
       <c r="B1014" s="6" t="s">
-        <v>6314</v>
+        <v>6316</v>
       </c>
       <c r="C1014" s="6" t="s">
-        <v>6315</v>
+        <v>6317</v>
       </c>
       <c r="D1014" s="6" t="s">
-        <v>6316</v>
+        <v>6318</v>
       </c>
       <c r="E1014" s="6" t="s">
-        <v>6317</v>
+        <v>6319</v>
       </c>
       <c r="F1014" s="6" t="s">
-        <v>6318</v>
+        <v>6320</v>
       </c>
       <c r="G1014" s="6" t="s">
-        <v>6319</v>
+        <v>6320</v>
       </c>
       <c r="H1014" s="6" t="s">
-        <v>6320</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="1015">
       <c r="B1015" s="5" t="s">
-        <v>6321</v>
+        <v>6322</v>
       </c>
       <c r="C1015" s="5" t="s">
-        <v>6322</v>
+        <v>6323</v>
       </c>
       <c r="D1015" s="5" t="s">
-        <v>6323</v>
+        <v>6324</v>
       </c>
       <c r="E1015" s="5" t="s">
-        <v>6324</v>
+        <v>6325</v>
       </c>
       <c r="F1015" s="5" t="s">
-        <v>6325</v>
+        <v>6326</v>
       </c>
       <c r="G1015" s="5" t="s">
         <v>6326</v>
@@ -47055,246 +47097,246 @@
         <v>6328</v>
       </c>
       <c r="C1016" s="6" t="s">
-        <v>4700</v>
+        <v>6329</v>
       </c>
       <c r="D1016" s="6" t="s">
-        <v>4701</v>
+        <v>6330</v>
       </c>
       <c r="E1016" s="6" t="s">
-        <v>6329</v>
+        <v>6331</v>
       </c>
       <c r="F1016" s="6" t="s">
-        <v>6330</v>
+        <v>6332</v>
       </c>
       <c r="G1016" s="6" t="s">
-        <v>6330</v>
+        <v>6333</v>
       </c>
       <c r="H1016" s="6" t="s">
-        <v>6331</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="1017">
       <c r="B1017" s="5" t="s">
-        <v>6332</v>
+        <v>6335</v>
       </c>
       <c r="C1017" s="5" t="s">
-        <v>3751</v>
+        <v>6336</v>
       </c>
       <c r="D1017" s="5" t="s">
-        <v>4796</v>
+        <v>6337</v>
       </c>
       <c r="E1017" s="5" t="s">
-        <v>3753</v>
+        <v>6338</v>
       </c>
       <c r="F1017" s="5" t="s">
-        <v>5942</v>
+        <v>6339</v>
       </c>
       <c r="G1017" s="5" t="s">
-        <v>5942</v>
+        <v>6340</v>
       </c>
       <c r="H1017" s="5" t="s">
-        <v>3123</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="1018">
       <c r="B1018" s="6" t="s">
-        <v>6333</v>
+        <v>6342</v>
       </c>
       <c r="C1018" s="6" t="s">
-        <v>6334</v>
+        <v>4700</v>
       </c>
       <c r="D1018" s="6" t="s">
-        <v>6335</v>
+        <v>4701</v>
       </c>
       <c r="E1018" s="6" t="s">
-        <v>6335</v>
+        <v>6343</v>
       </c>
       <c r="F1018" s="6" t="s">
-        <v>6335</v>
+        <v>6344</v>
       </c>
       <c r="G1018" s="6" t="s">
-        <v>6335</v>
+        <v>6344</v>
       </c>
       <c r="H1018" s="6" t="s">
-        <v>6335</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="1019">
       <c r="B1019" s="5" t="s">
-        <v>6336</v>
+        <v>6346</v>
       </c>
       <c r="C1019" s="5" t="s">
-        <v>6337</v>
+        <v>3751</v>
       </c>
       <c r="D1019" s="5" t="s">
-        <v>6338</v>
+        <v>4796</v>
       </c>
       <c r="E1019" s="5" t="s">
-        <v>6339</v>
+        <v>3753</v>
       </c>
       <c r="F1019" s="5" t="s">
-        <v>6340</v>
+        <v>5956</v>
       </c>
       <c r="G1019" s="5" t="s">
-        <v>6340</v>
+        <v>5956</v>
       </c>
       <c r="H1019" s="5" t="s">
-        <v>6341</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="1020">
       <c r="B1020" s="6" t="s">
-        <v>6342</v>
+        <v>6347</v>
       </c>
       <c r="C1020" s="6" t="s">
-        <v>6343</v>
+        <v>6348</v>
       </c>
       <c r="D1020" s="6" t="s">
-        <v>5934</v>
+        <v>6349</v>
       </c>
       <c r="E1020" s="6" t="s">
-        <v>6344</v>
+        <v>6349</v>
       </c>
       <c r="F1020" s="6" t="s">
-        <v>5936</v>
+        <v>6349</v>
       </c>
       <c r="G1020" s="6" t="s">
-        <v>5937</v>
+        <v>6349</v>
       </c>
       <c r="H1020" s="6" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="1021">
       <c r="B1021" s="5" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
       <c r="C1021" s="5" t="s">
-        <v>6347</v>
+        <v>6351</v>
       </c>
       <c r="D1021" s="5" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
       <c r="E1021" s="5" t="s">
-        <v>3963</v>
+        <v>6353</v>
       </c>
       <c r="F1021" s="5" t="s">
-        <v>3964</v>
+        <v>6354</v>
       </c>
       <c r="G1021" s="5" t="s">
-        <v>3964</v>
+        <v>6354</v>
       </c>
       <c r="H1021" s="5" t="s">
-        <v>5313</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="1022">
       <c r="B1022" s="6" t="s">
-        <v>6349</v>
+        <v>6356</v>
       </c>
       <c r="C1022" s="6" t="s">
-        <v>6350</v>
+        <v>6357</v>
       </c>
       <c r="D1022" s="6" t="s">
-        <v>6351</v>
+        <v>5948</v>
       </c>
       <c r="E1022" s="6" t="s">
-        <v>6352</v>
+        <v>6358</v>
       </c>
       <c r="F1022" s="6" t="s">
-        <v>6353</v>
+        <v>5950</v>
       </c>
       <c r="G1022" s="6" t="s">
-        <v>6354</v>
+        <v>5951</v>
       </c>
       <c r="H1022" s="6" t="s">
-        <v>6351</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="1023">
       <c r="B1023" s="5" t="s">
-        <v>6355</v>
+        <v>6360</v>
       </c>
       <c r="C1023" s="5" t="s">
-        <v>6356</v>
+        <v>6361</v>
       </c>
       <c r="D1023" s="5" t="s">
-        <v>6357</v>
+        <v>6362</v>
       </c>
       <c r="E1023" s="5" t="s">
-        <v>6358</v>
+        <v>3963</v>
       </c>
       <c r="F1023" s="5" t="s">
-        <v>6359</v>
+        <v>3964</v>
       </c>
       <c r="G1023" s="5" t="s">
-        <v>6360</v>
+        <v>3964</v>
       </c>
       <c r="H1023" s="5" t="s">
-        <v>6361</v>
+        <v>5313</v>
       </c>
     </row>
     <row r="1024">
       <c r="B1024" s="6" t="s">
-        <v>6362</v>
+        <v>6363</v>
       </c>
       <c r="C1024" s="6" t="s">
-        <v>6363</v>
+        <v>6364</v>
       </c>
       <c r="D1024" s="6" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="E1024" s="6" t="s">
+        <v>6366</v>
+      </c>
+      <c r="F1024" s="6" t="s">
+        <v>6367</v>
+      </c>
+      <c r="G1024" s="6" t="s">
+        <v>6368</v>
+      </c>
+      <c r="H1024" s="6" t="s">
         <v>6365</v>
-      </c>
-      <c r="F1024" s="6" t="s">
-        <v>6366</v>
-      </c>
-      <c r="G1024" s="6" t="s">
-        <v>6366</v>
-      </c>
-      <c r="H1024" s="6" t="s">
-        <v>6367</v>
       </c>
     </row>
     <row r="1025">
       <c r="B1025" s="5" t="s">
-        <v>6368</v>
+        <v>6369</v>
       </c>
       <c r="C1025" s="5" t="s">
-        <v>6369</v>
+        <v>6370</v>
       </c>
       <c r="D1025" s="5" t="s">
-        <v>6370</v>
+        <v>6371</v>
       </c>
       <c r="E1025" s="5" t="s">
-        <v>6371</v>
+        <v>6372</v>
       </c>
       <c r="F1025" s="5" t="s">
-        <v>6372</v>
+        <v>6373</v>
       </c>
       <c r="G1025" s="5" t="s">
-        <v>6373</v>
+        <v>6374</v>
       </c>
       <c r="H1025" s="5" t="s">
-        <v>6374</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="1026">
       <c r="B1026" s="6" t="s">
-        <v>6375</v>
+        <v>6376</v>
       </c>
       <c r="C1026" s="6" t="s">
-        <v>6376</v>
+        <v>6377</v>
       </c>
       <c r="D1026" s="6" t="s">
-        <v>6377</v>
+        <v>6378</v>
       </c>
       <c r="E1026" s="6" t="s">
-        <v>6378</v>
+        <v>6379</v>
       </c>
       <c r="F1026" s="6" t="s">
-        <v>6379</v>
+        <v>6380</v>
       </c>
       <c r="G1026" s="6" t="s">
         <v>6380</v>
@@ -47320,96 +47362,96 @@
         <v>6386</v>
       </c>
       <c r="G1027" s="5" t="s">
-        <v>6386</v>
+        <v>6387</v>
       </c>
       <c r="H1027" s="5" t="s">
-        <v>6387</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="1028">
       <c r="B1028" s="6" t="s">
-        <v>6388</v>
+        <v>6389</v>
       </c>
       <c r="C1028" s="6" t="s">
-        <v>6389</v>
+        <v>6390</v>
       </c>
       <c r="D1028" s="6" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="E1028" s="6" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="F1028" s="6" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
       <c r="G1028" s="6" t="s">
-        <v>6392</v>
+        <v>6394</v>
       </c>
       <c r="H1028" s="6" t="s">
-        <v>6393</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="1029">
       <c r="B1029" s="5" t="s">
-        <v>6394</v>
+        <v>6396</v>
       </c>
       <c r="C1029" s="5" t="s">
-        <v>6395</v>
+        <v>6397</v>
       </c>
       <c r="D1029" s="5" t="s">
-        <v>6396</v>
+        <v>6398</v>
       </c>
       <c r="E1029" s="5" t="s">
-        <v>6397</v>
+        <v>6399</v>
       </c>
       <c r="F1029" s="5" t="s">
-        <v>6398</v>
+        <v>6400</v>
       </c>
       <c r="G1029" s="5" t="s">
-        <v>6398</v>
+        <v>6400</v>
       </c>
       <c r="H1029" s="5" t="s">
-        <v>6399</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="1030">
       <c r="B1030" s="6" t="s">
-        <v>6400</v>
+        <v>6402</v>
       </c>
       <c r="C1030" s="6" t="s">
-        <v>6401</v>
+        <v>6403</v>
       </c>
       <c r="D1030" s="6" t="s">
-        <v>6402</v>
+        <v>6404</v>
       </c>
       <c r="E1030" s="6" t="s">
-        <v>6403</v>
+        <v>6405</v>
       </c>
       <c r="F1030" s="6" t="s">
-        <v>6404</v>
+        <v>6406</v>
       </c>
       <c r="G1030" s="6" t="s">
-        <v>6405</v>
+        <v>6406</v>
       </c>
       <c r="H1030" s="6" t="s">
-        <v>6406</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="1031">
       <c r="B1031" s="5" t="s">
-        <v>6407</v>
+        <v>6408</v>
       </c>
       <c r="C1031" s="5" t="s">
-        <v>6408</v>
+        <v>6409</v>
       </c>
       <c r="D1031" s="5" t="s">
-        <v>6409</v>
+        <v>6410</v>
       </c>
       <c r="E1031" s="5" t="s">
-        <v>6410</v>
+        <v>6411</v>
       </c>
       <c r="F1031" s="5" t="s">
-        <v>6411</v>
+        <v>6412</v>
       </c>
       <c r="G1031" s="5" t="s">
         <v>6412</v>
@@ -47435,303 +47477,303 @@
         <v>6418</v>
       </c>
       <c r="G1032" s="6" t="s">
-        <v>6418</v>
+        <v>6419</v>
       </c>
       <c r="H1032" s="6" t="s">
-        <v>6419</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="1033">
       <c r="B1033" s="5" t="s">
-        <v>6420</v>
+        <v>6421</v>
       </c>
       <c r="C1033" s="5" t="s">
-        <v>6421</v>
+        <v>6422</v>
       </c>
       <c r="D1033" s="5" t="s">
-        <v>6422</v>
+        <v>6423</v>
       </c>
       <c r="E1033" s="5" t="s">
-        <v>6423</v>
+        <v>6424</v>
       </c>
       <c r="F1033" s="5" t="s">
-        <v>6424</v>
+        <v>6425</v>
       </c>
       <c r="G1033" s="5" t="s">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="H1033" s="5" t="s">
-        <v>6426</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="1034">
       <c r="B1034" s="6" t="s">
-        <v>6427</v>
+        <v>6428</v>
       </c>
       <c r="C1034" s="6" t="s">
-        <v>6428</v>
+        <v>6429</v>
       </c>
       <c r="D1034" s="6" t="s">
-        <v>6429</v>
+        <v>6430</v>
       </c>
       <c r="E1034" s="6" t="s">
-        <v>6430</v>
+        <v>6431</v>
       </c>
       <c r="F1034" s="6" t="s">
-        <v>6431</v>
+        <v>6432</v>
       </c>
       <c r="G1034" s="6" t="s">
-        <v>6431</v>
+        <v>6432</v>
       </c>
       <c r="H1034" s="6" t="s">
-        <v>6432</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="1035">
       <c r="B1035" s="5" t="s">
-        <v>6433</v>
+        <v>6434</v>
       </c>
       <c r="C1035" s="5" t="s">
-        <v>6434</v>
+        <v>6435</v>
       </c>
       <c r="D1035" s="5" t="s">
-        <v>6435</v>
+        <v>6436</v>
       </c>
       <c r="E1035" s="5" t="s">
-        <v>6436</v>
+        <v>6437</v>
       </c>
       <c r="F1035" s="5" t="s">
-        <v>6437</v>
+        <v>6438</v>
       </c>
       <c r="G1035" s="5" t="s">
-        <v>6438</v>
+        <v>6439</v>
       </c>
       <c r="H1035" s="5" t="s">
-        <v>6439</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="1036">
       <c r="B1036" s="6" t="s">
-        <v>6440</v>
+        <v>6441</v>
       </c>
       <c r="C1036" s="6" t="s">
-        <v>6441</v>
+        <v>6442</v>
       </c>
       <c r="D1036" s="6" t="s">
-        <v>6442</v>
+        <v>6443</v>
       </c>
       <c r="E1036" s="6" t="s">
-        <v>6443</v>
+        <v>6444</v>
       </c>
       <c r="F1036" s="6" t="s">
-        <v>6444</v>
+        <v>6445</v>
       </c>
       <c r="G1036" s="6" t="s">
-        <v>6444</v>
+        <v>6445</v>
       </c>
       <c r="H1036" s="6" t="s">
-        <v>6445</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="1037">
       <c r="B1037" s="5" t="s">
-        <v>6446</v>
+        <v>6447</v>
       </c>
       <c r="C1037" s="5" t="s">
-        <v>6447</v>
+        <v>6448</v>
       </c>
       <c r="D1037" s="5" t="s">
-        <v>6448</v>
+        <v>6449</v>
       </c>
       <c r="E1037" s="5" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="F1037" s="5" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="G1037" s="5" t="s">
-        <v>6450</v>
+        <v>6452</v>
       </c>
       <c r="H1037" s="5" t="s">
-        <v>6451</v>
+        <v>6453</v>
       </c>
     </row>
     <row r="1038">
       <c r="B1038" s="6" t="s">
-        <v>6452</v>
+        <v>6454</v>
       </c>
       <c r="C1038" s="6" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D1038" s="6" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E1038" s="6" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
       <c r="F1038" s="6" t="s">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="G1038" s="6" t="s">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="H1038" s="6" t="s">
-        <v>6457</v>
+        <v>6459</v>
       </c>
     </row>
     <row r="1039">
       <c r="B1039" s="5" t="s">
-        <v>6458</v>
+        <v>6460</v>
       </c>
       <c r="C1039" s="5" t="s">
-        <v>6459</v>
+        <v>6461</v>
       </c>
       <c r="D1039" s="5" t="s">
-        <v>6460</v>
+        <v>6462</v>
       </c>
       <c r="E1039" s="5" t="s">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F1039" s="5" t="s">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="G1039" s="5" t="s">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="H1039" s="5" t="s">
-        <v>6463</v>
+        <v>6465</v>
       </c>
     </row>
     <row r="1040">
       <c r="B1040" s="6" t="s">
-        <v>6464</v>
+        <v>6466</v>
       </c>
       <c r="C1040" s="6" t="s">
-        <v>6465</v>
+        <v>6467</v>
       </c>
       <c r="D1040" s="6" t="s">
-        <v>6466</v>
+        <v>6468</v>
       </c>
       <c r="E1040" s="6" t="s">
-        <v>6467</v>
+        <v>6469</v>
       </c>
       <c r="F1040" s="6" t="s">
-        <v>6468</v>
+        <v>6470</v>
       </c>
       <c r="G1040" s="6" t="s">
-        <v>6467</v>
+        <v>6470</v>
       </c>
       <c r="H1040" s="6" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="1041">
       <c r="B1041" s="5" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="C1041" s="5" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
       <c r="D1041" s="5" t="s">
-        <v>6472</v>
+        <v>6474</v>
       </c>
       <c r="E1041" s="5" t="s">
-        <v>6473</v>
+        <v>6475</v>
       </c>
       <c r="F1041" s="5" t="s">
-        <v>6474</v>
+        <v>6476</v>
       </c>
       <c r="G1041" s="5" t="s">
-        <v>6475</v>
+        <v>6476</v>
       </c>
       <c r="H1041" s="5" t="s">
-        <v>6476</v>
+        <v>6477</v>
       </c>
     </row>
     <row r="1042">
       <c r="B1042" s="6" t="s">
-        <v>6477</v>
+        <v>6478</v>
       </c>
       <c r="C1042" s="6" t="s">
-        <v>6478</v>
+        <v>6479</v>
       </c>
       <c r="D1042" s="6" t="s">
-        <v>6479</v>
+        <v>6480</v>
       </c>
       <c r="E1042" s="6" t="s">
-        <v>6480</v>
+        <v>6481</v>
       </c>
       <c r="F1042" s="6" t="s">
-        <v>6481</v>
+        <v>6482</v>
       </c>
       <c r="G1042" s="6" t="s">
         <v>6481</v>
       </c>
       <c r="H1042" s="6" t="s">
-        <v>6482</v>
+        <v>6483</v>
       </c>
     </row>
     <row r="1043">
       <c r="B1043" s="5" t="s">
-        <v>6483</v>
+        <v>6484</v>
       </c>
       <c r="C1043" s="5" t="s">
-        <v>6484</v>
+        <v>6485</v>
       </c>
       <c r="D1043" s="5" t="s">
-        <v>6485</v>
+        <v>6486</v>
       </c>
       <c r="E1043" s="5" t="s">
-        <v>6486</v>
+        <v>6487</v>
       </c>
       <c r="F1043" s="5" t="s">
-        <v>6487</v>
+        <v>6488</v>
       </c>
       <c r="G1043" s="5" t="s">
-        <v>6487</v>
+        <v>6489</v>
       </c>
       <c r="H1043" s="5" t="s">
-        <v>6488</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="1044">
       <c r="B1044" s="6" t="s">
-        <v>6489</v>
+        <v>6491</v>
       </c>
       <c r="C1044" s="6" t="s">
-        <v>6490</v>
+        <v>6492</v>
       </c>
       <c r="D1044" s="6" t="s">
-        <v>6491</v>
+        <v>6493</v>
       </c>
       <c r="E1044" s="6" t="s">
-        <v>6492</v>
+        <v>6494</v>
       </c>
       <c r="F1044" s="6" t="s">
-        <v>6493</v>
+        <v>6495</v>
       </c>
       <c r="G1044" s="6" t="s">
-        <v>6494</v>
+        <v>6495</v>
       </c>
       <c r="H1044" s="6" t="s">
-        <v>6495</v>
+        <v>6496</v>
       </c>
     </row>
     <row r="1045">
       <c r="B1045" s="5" t="s">
-        <v>6496</v>
+        <v>6497</v>
       </c>
       <c r="C1045" s="5" t="s">
-        <v>6497</v>
+        <v>6498</v>
       </c>
       <c r="D1045" s="5" t="s">
-        <v>6498</v>
+        <v>6499</v>
       </c>
       <c r="E1045" s="5" t="s">
-        <v>6499</v>
+        <v>6500</v>
       </c>
       <c r="F1045" s="5" t="s">
-        <v>6500</v>
+        <v>6501</v>
       </c>
       <c r="G1045" s="5" t="s">
         <v>6501</v>
@@ -47745,200 +47787,200 @@
         <v>6503</v>
       </c>
       <c r="C1046" s="6" t="s">
-        <v>5912</v>
+        <v>6504</v>
       </c>
       <c r="D1046" s="6" t="s">
-        <v>5913</v>
+        <v>6505</v>
       </c>
       <c r="E1046" s="6" t="s">
-        <v>5914</v>
+        <v>6506</v>
       </c>
       <c r="F1046" s="6" t="s">
-        <v>5915</v>
+        <v>6507</v>
       </c>
       <c r="G1046" s="6" t="s">
-        <v>5916</v>
+        <v>6508</v>
       </c>
       <c r="H1046" s="6" t="s">
-        <v>5917</v>
+        <v>6509</v>
       </c>
     </row>
     <row r="1047">
       <c r="B1047" s="5" t="s">
-        <v>6504</v>
+        <v>6510</v>
       </c>
       <c r="C1047" s="5" t="s">
-        <v>4791</v>
+        <v>6511</v>
       </c>
       <c r="D1047" s="5" t="s">
-        <v>6505</v>
+        <v>6512</v>
       </c>
       <c r="E1047" s="5" t="s">
-        <v>4792</v>
+        <v>6513</v>
       </c>
       <c r="F1047" s="5" t="s">
-        <v>4793</v>
+        <v>6514</v>
       </c>
       <c r="G1047" s="5" t="s">
-        <v>4794</v>
+        <v>6515</v>
       </c>
       <c r="H1047" s="5" t="s">
-        <v>6505</v>
+        <v>6516</v>
       </c>
     </row>
     <row r="1048">
       <c r="B1048" s="6" t="s">
-        <v>6506</v>
+        <v>6517</v>
       </c>
       <c r="C1048" s="6" t="s">
-        <v>4624</v>
+        <v>5926</v>
       </c>
       <c r="D1048" s="6" t="s">
-        <v>6507</v>
+        <v>5927</v>
       </c>
       <c r="E1048" s="6" t="s">
-        <v>4626</v>
+        <v>5928</v>
       </c>
       <c r="F1048" s="6" t="s">
-        <v>6508</v>
+        <v>5929</v>
       </c>
       <c r="G1048" s="6" t="s">
-        <v>6509</v>
+        <v>5930</v>
       </c>
       <c r="H1048" s="6" t="s">
-        <v>6510</v>
+        <v>5931</v>
       </c>
     </row>
     <row r="1049">
       <c r="B1049" s="5" t="s">
-        <v>6511</v>
+        <v>6518</v>
       </c>
       <c r="C1049" s="5" t="s">
-        <v>6512</v>
+        <v>4791</v>
       </c>
       <c r="D1049" s="5" t="s">
-        <v>6513</v>
+        <v>6519</v>
       </c>
       <c r="E1049" s="5" t="s">
-        <v>6514</v>
+        <v>4792</v>
       </c>
       <c r="F1049" s="5" t="s">
-        <v>6515</v>
+        <v>4793</v>
       </c>
       <c r="G1049" s="5" t="s">
-        <v>6516</v>
+        <v>4794</v>
       </c>
       <c r="H1049" s="5" t="s">
-        <v>6517</v>
+        <v>6519</v>
       </c>
     </row>
     <row r="1050">
       <c r="B1050" s="6" t="s">
-        <v>6518</v>
+        <v>6520</v>
       </c>
       <c r="C1050" s="6" t="s">
-        <v>6519</v>
+        <v>4624</v>
       </c>
       <c r="D1050" s="6" t="s">
-        <v>6520</v>
+        <v>6521</v>
       </c>
       <c r="E1050" s="6" t="s">
-        <v>6499</v>
+        <v>4626</v>
       </c>
       <c r="F1050" s="6" t="s">
-        <v>6500</v>
+        <v>6522</v>
       </c>
       <c r="G1050" s="6" t="s">
-        <v>6501</v>
+        <v>6523</v>
       </c>
       <c r="H1050" s="6" t="s">
-        <v>6521</v>
+        <v>6524</v>
       </c>
     </row>
     <row r="1051">
       <c r="B1051" s="5" t="s">
-        <v>6522</v>
+        <v>6525</v>
       </c>
       <c r="C1051" s="5" t="s">
-        <v>6523</v>
+        <v>6526</v>
       </c>
       <c r="D1051" s="5" t="s">
-        <v>6524</v>
+        <v>6527</v>
       </c>
       <c r="E1051" s="5" t="s">
-        <v>6525</v>
+        <v>6528</v>
       </c>
       <c r="F1051" s="5" t="s">
-        <v>6526</v>
+        <v>6529</v>
       </c>
       <c r="G1051" s="5" t="s">
-        <v>6527</v>
+        <v>6530</v>
       </c>
       <c r="H1051" s="5" t="s">
-        <v>6528</v>
+        <v>6531</v>
       </c>
     </row>
     <row r="1052">
       <c r="B1052" s="6" t="s">
-        <v>6529</v>
+        <v>6532</v>
       </c>
       <c r="C1052" s="6" t="s">
-        <v>6530</v>
+        <v>6533</v>
       </c>
       <c r="D1052" s="6" t="s">
-        <v>6531</v>
+        <v>6534</v>
       </c>
       <c r="E1052" s="6" t="s">
-        <v>6532</v>
+        <v>6513</v>
       </c>
       <c r="F1052" s="6" t="s">
-        <v>6533</v>
+        <v>6514</v>
       </c>
       <c r="G1052" s="6" t="s">
-        <v>6533</v>
+        <v>6515</v>
       </c>
       <c r="H1052" s="6" t="s">
-        <v>6534</v>
+        <v>6535</v>
       </c>
     </row>
     <row r="1053">
       <c r="B1053" s="5" t="s">
-        <v>6535</v>
+        <v>6536</v>
       </c>
       <c r="C1053" s="5" t="s">
-        <v>6536</v>
+        <v>6537</v>
       </c>
       <c r="D1053" s="5" t="s">
-        <v>6537</v>
+        <v>6538</v>
       </c>
       <c r="E1053" s="5" t="s">
-        <v>6538</v>
+        <v>6539</v>
       </c>
       <c r="F1053" s="5" t="s">
-        <v>6539</v>
+        <v>6540</v>
       </c>
       <c r="G1053" s="5" t="s">
-        <v>6540</v>
+        <v>6541</v>
       </c>
       <c r="H1053" s="5" t="s">
-        <v>6541</v>
+        <v>6542</v>
       </c>
     </row>
     <row r="1054">
       <c r="B1054" s="6" t="s">
-        <v>6542</v>
+        <v>6543</v>
       </c>
       <c r="C1054" s="6" t="s">
-        <v>6543</v>
+        <v>6544</v>
       </c>
       <c r="D1054" s="6" t="s">
-        <v>6544</v>
+        <v>6545</v>
       </c>
       <c r="E1054" s="6" t="s">
-        <v>6545</v>
+        <v>6546</v>
       </c>
       <c r="F1054" s="6" t="s">
-        <v>6546</v>
+        <v>6547</v>
       </c>
       <c r="G1054" s="6" t="s">
         <v>6547</v>
@@ -47961,335 +48003,335 @@
         <v>6552</v>
       </c>
       <c r="F1055" s="5" t="s">
-        <v>5701</v>
+        <v>6553</v>
       </c>
       <c r="G1055" s="5" t="s">
-        <v>5702</v>
+        <v>6554</v>
       </c>
       <c r="H1055" s="5" t="s">
-        <v>6553</v>
+        <v>6555</v>
       </c>
     </row>
     <row r="1056">
       <c r="B1056" s="6" t="s">
-        <v>6554</v>
+        <v>6556</v>
       </c>
       <c r="C1056" s="6" t="s">
-        <v>6555</v>
+        <v>6557</v>
       </c>
       <c r="D1056" s="6" t="s">
-        <v>6556</v>
+        <v>6558</v>
       </c>
       <c r="E1056" s="6" t="s">
-        <v>6557</v>
+        <v>6559</v>
       </c>
       <c r="F1056" s="6" t="s">
-        <v>6558</v>
+        <v>6560</v>
       </c>
       <c r="G1056" s="6" t="s">
-        <v>6559</v>
+        <v>6561</v>
       </c>
       <c r="H1056" s="6" t="s">
-        <v>6560</v>
+        <v>6562</v>
       </c>
     </row>
     <row r="1057">
       <c r="B1057" s="5" t="s">
-        <v>6561</v>
+        <v>6563</v>
       </c>
       <c r="C1057" s="5" t="s">
-        <v>6562</v>
+        <v>6564</v>
       </c>
       <c r="D1057" s="5" t="s">
-        <v>6563</v>
+        <v>6565</v>
       </c>
       <c r="E1057" s="5" t="s">
-        <v>6564</v>
+        <v>6566</v>
       </c>
       <c r="F1057" s="5" t="s">
-        <v>6565</v>
+        <v>5715</v>
       </c>
       <c r="G1057" s="5" t="s">
-        <v>6564</v>
+        <v>5716</v>
       </c>
       <c r="H1057" s="5" t="s">
-        <v>6563</v>
+        <v>6567</v>
       </c>
     </row>
     <row r="1058">
       <c r="B1058" s="6" t="s">
-        <v>6566</v>
+        <v>6568</v>
       </c>
       <c r="C1058" s="6" t="s">
-        <v>3751</v>
+        <v>6569</v>
       </c>
       <c r="D1058" s="6" t="s">
-        <v>4796</v>
+        <v>6570</v>
       </c>
       <c r="E1058" s="6" t="s">
-        <v>3753</v>
+        <v>6571</v>
       </c>
       <c r="F1058" s="6" t="s">
-        <v>5942</v>
+        <v>6572</v>
       </c>
       <c r="G1058" s="6" t="s">
-        <v>5942</v>
+        <v>6573</v>
       </c>
       <c r="H1058" s="6" t="s">
-        <v>3123</v>
+        <v>6574</v>
       </c>
     </row>
     <row r="1059">
       <c r="B1059" s="5" t="s">
-        <v>6567</v>
+        <v>6575</v>
       </c>
       <c r="C1059" s="5" t="s">
-        <v>3798</v>
+        <v>6576</v>
       </c>
       <c r="D1059" s="5" t="s">
-        <v>6568</v>
+        <v>6577</v>
       </c>
       <c r="E1059" s="5" t="s">
-        <v>3800</v>
+        <v>6578</v>
       </c>
       <c r="F1059" s="5" t="s">
-        <v>6569</v>
+        <v>6579</v>
       </c>
       <c r="G1059" s="5" t="s">
-        <v>6570</v>
+        <v>6578</v>
       </c>
       <c r="H1059" s="5" t="s">
-        <v>6571</v>
+        <v>6577</v>
       </c>
     </row>
     <row r="1060">
       <c r="B1060" s="6" t="s">
-        <v>6572</v>
+        <v>6580</v>
       </c>
       <c r="C1060" s="6" t="s">
-        <v>5253</v>
+        <v>3751</v>
       </c>
       <c r="D1060" s="6" t="s">
-        <v>6573</v>
+        <v>4796</v>
       </c>
       <c r="E1060" s="6" t="s">
-        <v>5255</v>
+        <v>3753</v>
       </c>
       <c r="F1060" s="6" t="s">
-        <v>3734</v>
+        <v>5956</v>
       </c>
       <c r="G1060" s="6" t="s">
-        <v>3735</v>
+        <v>5956</v>
       </c>
       <c r="H1060" s="6" t="s">
-        <v>5254</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="1061">
       <c r="B1061" s="5" t="s">
-        <v>6574</v>
+        <v>6581</v>
       </c>
       <c r="C1061" s="5" t="s">
-        <v>5259</v>
+        <v>3798</v>
       </c>
       <c r="D1061" s="5" t="s">
-        <v>6575</v>
+        <v>6582</v>
       </c>
       <c r="E1061" s="5" t="s">
-        <v>5261</v>
+        <v>3800</v>
       </c>
       <c r="F1061" s="5" t="s">
-        <v>3741</v>
+        <v>6583</v>
       </c>
       <c r="G1061" s="5" t="s">
-        <v>3741</v>
+        <v>6584</v>
       </c>
       <c r="H1061" s="5" t="s">
-        <v>6576</v>
+        <v>6585</v>
       </c>
     </row>
     <row r="1062">
       <c r="B1062" s="6" t="s">
-        <v>6577</v>
+        <v>6586</v>
       </c>
       <c r="C1062" s="6" t="s">
-        <v>5264</v>
+        <v>5253</v>
       </c>
       <c r="D1062" s="6" t="s">
-        <v>6578</v>
+        <v>6587</v>
       </c>
       <c r="E1062" s="6" t="s">
-        <v>5266</v>
+        <v>5255</v>
       </c>
       <c r="F1062" s="6" t="s">
-        <v>3747</v>
+        <v>3734</v>
       </c>
       <c r="G1062" s="6" t="s">
-        <v>3748</v>
+        <v>3735</v>
       </c>
       <c r="H1062" s="6" t="s">
-        <v>5269</v>
+        <v>5254</v>
       </c>
     </row>
     <row r="1063">
       <c r="B1063" s="5" t="s">
-        <v>6579</v>
+        <v>6588</v>
       </c>
       <c r="C1063" s="5" t="s">
-        <v>3764</v>
+        <v>5259</v>
       </c>
       <c r="D1063" s="5" t="s">
-        <v>6580</v>
+        <v>6589</v>
       </c>
       <c r="E1063" s="5" t="s">
-        <v>3766</v>
+        <v>5261</v>
       </c>
       <c r="F1063" s="5" t="s">
-        <v>3767</v>
+        <v>3741</v>
       </c>
       <c r="G1063" s="5" t="s">
-        <v>3768</v>
+        <v>3741</v>
       </c>
       <c r="H1063" s="5" t="s">
-        <v>6581</v>
+        <v>6590</v>
       </c>
     </row>
     <row r="1064">
       <c r="B1064" s="6" t="s">
-        <v>6582</v>
+        <v>6591</v>
       </c>
       <c r="C1064" s="6" t="s">
-        <v>6583</v>
+        <v>5264</v>
       </c>
       <c r="D1064" s="6" t="s">
-        <v>6584</v>
+        <v>6592</v>
       </c>
       <c r="E1064" s="6" t="s">
-        <v>3794</v>
+        <v>5266</v>
       </c>
       <c r="F1064" s="6" t="s">
-        <v>6585</v>
+        <v>3747</v>
       </c>
       <c r="G1064" s="6" t="s">
-        <v>6586</v>
+        <v>3748</v>
       </c>
       <c r="H1064" s="6" t="s">
-        <v>5251</v>
+        <v>5269</v>
       </c>
     </row>
     <row r="1065">
       <c r="B1065" s="5" t="s">
-        <v>6587</v>
+        <v>6593</v>
       </c>
       <c r="C1065" s="5" t="s">
-        <v>5239</v>
+        <v>3764</v>
       </c>
       <c r="D1065" s="5" t="s">
-        <v>6588</v>
+        <v>6594</v>
       </c>
       <c r="E1065" s="5" t="s">
-        <v>5241</v>
+        <v>3766</v>
       </c>
       <c r="F1065" s="5" t="s">
-        <v>6589</v>
+        <v>3767</v>
       </c>
       <c r="G1065" s="5" t="s">
-        <v>6589</v>
+        <v>3768</v>
       </c>
       <c r="H1065" s="5" t="s">
-        <v>6590</v>
+        <v>6595</v>
       </c>
     </row>
     <row r="1066">
       <c r="B1066" s="6" t="s">
-        <v>6591</v>
+        <v>6596</v>
       </c>
       <c r="C1066" s="6" t="s">
-        <v>6592</v>
+        <v>6597</v>
       </c>
       <c r="D1066" s="6" t="s">
-        <v>6593</v>
+        <v>6598</v>
       </c>
       <c r="E1066" s="6" t="s">
-        <v>6594</v>
+        <v>3794</v>
       </c>
       <c r="F1066" s="6" t="s">
-        <v>6595</v>
+        <v>6599</v>
       </c>
       <c r="G1066" s="6" t="s">
-        <v>6596</v>
+        <v>6600</v>
       </c>
       <c r="H1066" s="6" t="s">
-        <v>6597</v>
+        <v>5251</v>
       </c>
     </row>
     <row r="1067">
       <c r="B1067" s="5" t="s">
-        <v>6598</v>
+        <v>6601</v>
       </c>
       <c r="C1067" s="5" t="s">
-        <v>6490</v>
+        <v>5239</v>
       </c>
       <c r="D1067" s="5" t="s">
-        <v>6491</v>
+        <v>6602</v>
       </c>
       <c r="E1067" s="5" t="s">
-        <v>6492</v>
+        <v>5241</v>
       </c>
       <c r="F1067" s="5" t="s">
-        <v>6493</v>
+        <v>6603</v>
       </c>
       <c r="G1067" s="5" t="s">
-        <v>6494</v>
+        <v>6603</v>
       </c>
       <c r="H1067" s="5" t="s">
-        <v>6495</v>
+        <v>6604</v>
       </c>
     </row>
     <row r="1068">
       <c r="B1068" s="6" t="s">
-        <v>6599</v>
+        <v>6605</v>
       </c>
       <c r="C1068" s="6" t="s">
-        <v>6600</v>
+        <v>6606</v>
       </c>
       <c r="D1068" s="6" t="s">
-        <v>6601</v>
+        <v>6607</v>
       </c>
       <c r="E1068" s="6" t="s">
-        <v>6602</v>
+        <v>6608</v>
       </c>
       <c r="F1068" s="6" t="s">
-        <v>6603</v>
+        <v>6609</v>
       </c>
       <c r="G1068" s="6" t="s">
-        <v>6604</v>
+        <v>6610</v>
       </c>
       <c r="H1068" s="6" t="s">
-        <v>6605</v>
+        <v>6611</v>
       </c>
     </row>
     <row r="1069">
       <c r="B1069" s="5" t="s">
-        <v>6606</v>
+        <v>6612</v>
       </c>
       <c r="C1069" s="5" t="s">
-        <v>6607</v>
+        <v>6504</v>
       </c>
       <c r="D1069" s="5" t="s">
-        <v>6608</v>
+        <v>6505</v>
       </c>
       <c r="E1069" s="5" t="s">
-        <v>6609</v>
+        <v>6506</v>
       </c>
       <c r="F1069" s="5" t="s">
-        <v>6610</v>
+        <v>6507</v>
       </c>
       <c r="G1069" s="5" t="s">
-        <v>6611</v>
+        <v>6508</v>
       </c>
       <c r="H1069" s="5" t="s">
-        <v>6612</v>
+        <v>6509</v>
       </c>
     </row>
     <row r="1070">
@@ -48401,50 +48443,50 @@
         <v>6645</v>
       </c>
       <c r="G1074" s="6" t="s">
-        <v>6645</v>
+        <v>6646</v>
       </c>
       <c r="H1074" s="6" t="s">
-        <v>6646</v>
+        <v>6647</v>
       </c>
     </row>
     <row r="1075">
       <c r="B1075" s="5" t="s">
-        <v>6647</v>
+        <v>6648</v>
       </c>
       <c r="C1075" s="5" t="s">
-        <v>6648</v>
+        <v>6649</v>
       </c>
       <c r="D1075" s="5" t="s">
-        <v>6649</v>
+        <v>6650</v>
       </c>
       <c r="E1075" s="5" t="s">
-        <v>6650</v>
+        <v>6651</v>
       </c>
       <c r="F1075" s="5" t="s">
-        <v>6651</v>
+        <v>6652</v>
       </c>
       <c r="G1075" s="5" t="s">
-        <v>6652</v>
+        <v>6653</v>
       </c>
       <c r="H1075" s="5" t="s">
-        <v>6653</v>
+        <v>6654</v>
       </c>
     </row>
     <row r="1076">
       <c r="B1076" s="6" t="s">
-        <v>6654</v>
+        <v>6655</v>
       </c>
       <c r="C1076" s="6" t="s">
-        <v>6655</v>
+        <v>6656</v>
       </c>
       <c r="D1076" s="6" t="s">
-        <v>6656</v>
+        <v>6657</v>
       </c>
       <c r="E1076" s="6" t="s">
-        <v>6657</v>
+        <v>6658</v>
       </c>
       <c r="F1076" s="6" t="s">
-        <v>6658</v>
+        <v>6659</v>
       </c>
       <c r="G1076" s="6" t="s">
         <v>6659</v>
@@ -48654,99 +48696,99 @@
         <v>6721</v>
       </c>
       <c r="G1085" s="5" t="s">
-        <v>6721</v>
+        <v>6722</v>
       </c>
       <c r="H1085" s="5" t="s">
-        <v>6722</v>
+        <v>6723</v>
       </c>
     </row>
     <row r="1086">
       <c r="B1086" s="6" t="s">
-        <v>6723</v>
+        <v>6724</v>
       </c>
       <c r="C1086" s="6" t="s">
-        <v>6724</v>
+        <v>6725</v>
       </c>
       <c r="D1086" s="6" t="s">
-        <v>6725</v>
+        <v>6726</v>
       </c>
       <c r="E1086" s="6" t="s">
-        <v>6726</v>
+        <v>6727</v>
       </c>
       <c r="F1086" s="6" t="s">
-        <v>6727</v>
+        <v>6728</v>
       </c>
       <c r="G1086" s="6" t="s">
-        <v>6728</v>
+        <v>6729</v>
       </c>
       <c r="H1086" s="6" t="s">
-        <v>6729</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="1087">
       <c r="B1087" s="5" t="s">
-        <v>6730</v>
+        <v>6731</v>
       </c>
       <c r="C1087" s="5" t="s">
-        <v>6731</v>
+        <v>6732</v>
       </c>
       <c r="D1087" s="5" t="s">
-        <v>6732</v>
+        <v>6733</v>
       </c>
       <c r="E1087" s="5" t="s">
-        <v>6733</v>
+        <v>6734</v>
       </c>
       <c r="F1087" s="5" t="s">
-        <v>6651</v>
+        <v>6735</v>
       </c>
       <c r="G1087" s="5" t="s">
-        <v>6652</v>
+        <v>6735</v>
       </c>
       <c r="H1087" s="5" t="s">
-        <v>6734</v>
+        <v>6736</v>
       </c>
     </row>
     <row r="1088">
       <c r="B1088" s="6" t="s">
-        <v>6735</v>
+        <v>6737</v>
       </c>
       <c r="C1088" s="6" t="s">
-        <v>6736</v>
+        <v>6738</v>
       </c>
       <c r="D1088" s="6" t="s">
-        <v>6737</v>
+        <v>6739</v>
       </c>
       <c r="E1088" s="6" t="s">
-        <v>6738</v>
+        <v>6740</v>
       </c>
       <c r="F1088" s="6" t="s">
-        <v>6739</v>
+        <v>6741</v>
       </c>
       <c r="G1088" s="6" t="s">
-        <v>6740</v>
+        <v>6742</v>
       </c>
       <c r="H1088" s="6" t="s">
-        <v>6741</v>
+        <v>6743</v>
       </c>
     </row>
     <row r="1089">
       <c r="B1089" s="5" t="s">
-        <v>6742</v>
+        <v>6744</v>
       </c>
       <c r="C1089" s="5" t="s">
-        <v>6743</v>
+        <v>6745</v>
       </c>
       <c r="D1089" s="5" t="s">
-        <v>6744</v>
+        <v>6746</v>
       </c>
       <c r="E1089" s="5" t="s">
-        <v>6745</v>
+        <v>6747</v>
       </c>
       <c r="F1089" s="5" t="s">
-        <v>6746</v>
+        <v>6665</v>
       </c>
       <c r="G1089" s="5" t="s">
-        <v>6747</v>
+        <v>6666</v>
       </c>
       <c r="H1089" s="5" t="s">
         <v>6748</v>
@@ -48769,142 +48811,142 @@
         <v>6753</v>
       </c>
       <c r="G1090" s="6" t="s">
-        <v>6753</v>
+        <v>6754</v>
       </c>
       <c r="H1090" s="6" t="s">
-        <v>6754</v>
+        <v>6755</v>
       </c>
     </row>
     <row r="1091">
       <c r="B1091" s="5" t="s">
-        <v>6755</v>
+        <v>6756</v>
       </c>
       <c r="C1091" s="5" t="s">
-        <v>6756</v>
+        <v>6757</v>
       </c>
       <c r="D1091" s="5" t="s">
-        <v>6757</v>
+        <v>6758</v>
       </c>
       <c r="E1091" s="5" t="s">
-        <v>6758</v>
+        <v>6759</v>
       </c>
       <c r="F1091" s="5" t="s">
-        <v>6759</v>
+        <v>6760</v>
       </c>
       <c r="G1091" s="5" t="s">
-        <v>6760</v>
+        <v>6761</v>
       </c>
       <c r="H1091" s="5" t="s">
-        <v>6761</v>
+        <v>6762</v>
       </c>
     </row>
     <row r="1092">
       <c r="B1092" s="6" t="s">
-        <v>6762</v>
+        <v>6763</v>
       </c>
       <c r="C1092" s="6" t="s">
-        <v>6763</v>
+        <v>6764</v>
       </c>
       <c r="D1092" s="6" t="s">
-        <v>6764</v>
+        <v>6765</v>
       </c>
       <c r="E1092" s="6" t="s">
-        <v>6765</v>
+        <v>6766</v>
       </c>
       <c r="F1092" s="6" t="s">
-        <v>6766</v>
+        <v>6767</v>
       </c>
       <c r="G1092" s="6" t="s">
-        <v>6766</v>
+        <v>6767</v>
       </c>
       <c r="H1092" s="6" t="s">
-        <v>6767</v>
+        <v>6768</v>
       </c>
     </row>
     <row r="1093">
       <c r="B1093" s="5" t="s">
-        <v>6768</v>
+        <v>6769</v>
       </c>
       <c r="C1093" s="5" t="s">
-        <v>4517</v>
+        <v>6770</v>
       </c>
       <c r="D1093" s="5" t="s">
-        <v>6769</v>
+        <v>6771</v>
       </c>
       <c r="E1093" s="5" t="s">
-        <v>4519</v>
+        <v>6772</v>
       </c>
       <c r="F1093" s="5" t="s">
-        <v>4520</v>
+        <v>6773</v>
       </c>
       <c r="G1093" s="5" t="s">
-        <v>4521</v>
+        <v>6774</v>
       </c>
       <c r="H1093" s="5" t="s">
-        <v>4522</v>
+        <v>6775</v>
       </c>
     </row>
     <row r="1094">
       <c r="B1094" s="6" t="s">
-        <v>6770</v>
+        <v>6776</v>
       </c>
       <c r="C1094" s="6" t="s">
-        <v>6771</v>
+        <v>6777</v>
       </c>
       <c r="D1094" s="6" t="s">
-        <v>6772</v>
+        <v>6778</v>
       </c>
       <c r="E1094" s="6" t="s">
-        <v>6773</v>
+        <v>6779</v>
       </c>
       <c r="F1094" s="6" t="s">
-        <v>6774</v>
+        <v>6780</v>
       </c>
       <c r="G1094" s="6" t="s">
-        <v>6774</v>
+        <v>6780</v>
       </c>
       <c r="H1094" s="6" t="s">
-        <v>6775</v>
+        <v>6781</v>
       </c>
     </row>
     <row r="1095">
       <c r="B1095" s="5" t="s">
-        <v>6776</v>
+        <v>6782</v>
       </c>
       <c r="C1095" s="5" t="s">
-        <v>6777</v>
+        <v>4517</v>
       </c>
       <c r="D1095" s="5" t="s">
-        <v>6778</v>
+        <v>6783</v>
       </c>
       <c r="E1095" s="5" t="s">
-        <v>6779</v>
+        <v>4519</v>
       </c>
       <c r="F1095" s="5" t="s">
-        <v>6780</v>
+        <v>4520</v>
       </c>
       <c r="G1095" s="5" t="s">
-        <v>6781</v>
+        <v>4521</v>
       </c>
       <c r="H1095" s="5" t="s">
-        <v>6782</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="1096">
       <c r="B1096" s="6" t="s">
-        <v>6783</v>
+        <v>6784</v>
       </c>
       <c r="C1096" s="6" t="s">
-        <v>6784</v>
+        <v>6785</v>
       </c>
       <c r="D1096" s="6" t="s">
-        <v>6785</v>
+        <v>6786</v>
       </c>
       <c r="E1096" s="6" t="s">
-        <v>6786</v>
+        <v>6787</v>
       </c>
       <c r="F1096" s="6" t="s">
-        <v>6787</v>
+        <v>6788</v>
       </c>
       <c r="G1096" s="6" t="s">
         <v>6788</v>
@@ -48930,50 +48972,50 @@
         <v>6794</v>
       </c>
       <c r="G1097" s="5" t="s">
-        <v>6794</v>
+        <v>6795</v>
       </c>
       <c r="H1097" s="5" t="s">
-        <v>6795</v>
+        <v>6796</v>
       </c>
     </row>
     <row r="1098">
       <c r="B1098" s="6" t="s">
-        <v>6796</v>
+        <v>6797</v>
       </c>
       <c r="C1098" s="6" t="s">
-        <v>6797</v>
+        <v>6798</v>
       </c>
       <c r="D1098" s="6" t="s">
-        <v>6798</v>
+        <v>6799</v>
       </c>
       <c r="E1098" s="6" t="s">
-        <v>6799</v>
+        <v>6800</v>
       </c>
       <c r="F1098" s="6" t="s">
-        <v>6800</v>
+        <v>6801</v>
       </c>
       <c r="G1098" s="6" t="s">
-        <v>6801</v>
+        <v>6802</v>
       </c>
       <c r="H1098" s="6" t="s">
-        <v>6802</v>
+        <v>6803</v>
       </c>
     </row>
     <row r="1099">
       <c r="B1099" s="5" t="s">
-        <v>6803</v>
+        <v>6804</v>
       </c>
       <c r="C1099" s="5" t="s">
-        <v>6804</v>
+        <v>6805</v>
       </c>
       <c r="D1099" s="5" t="s">
-        <v>6805</v>
+        <v>6806</v>
       </c>
       <c r="E1099" s="5" t="s">
-        <v>6806</v>
+        <v>6807</v>
       </c>
       <c r="F1099" s="5" t="s">
-        <v>6807</v>
+        <v>6808</v>
       </c>
       <c r="G1099" s="5" t="s">
         <v>6808</v>
@@ -49010,68 +49052,68 @@
         <v>6817</v>
       </c>
       <c r="C1101" s="5" t="s">
-        <v>6771</v>
+        <v>6818</v>
       </c>
       <c r="D1101" s="5" t="s">
-        <v>6772</v>
+        <v>6819</v>
       </c>
       <c r="E1101" s="5" t="s">
-        <v>6773</v>
+        <v>6820</v>
       </c>
       <c r="F1101" s="5" t="s">
-        <v>6774</v>
+        <v>6821</v>
       </c>
       <c r="G1101" s="5" t="s">
-        <v>6774</v>
+        <v>6822</v>
       </c>
       <c r="H1101" s="5" t="s">
-        <v>6775</v>
+        <v>6823</v>
       </c>
     </row>
     <row r="1102">
       <c r="B1102" s="6" t="s">
-        <v>6818</v>
+        <v>6824</v>
       </c>
       <c r="C1102" s="6" t="s">
-        <v>6819</v>
+        <v>6825</v>
       </c>
       <c r="D1102" s="6" t="s">
-        <v>6820</v>
+        <v>6826</v>
       </c>
       <c r="E1102" s="6" t="s">
-        <v>6821</v>
+        <v>6827</v>
       </c>
       <c r="F1102" s="6" t="s">
-        <v>6822</v>
+        <v>6828</v>
       </c>
       <c r="G1102" s="6" t="s">
-        <v>6823</v>
+        <v>6829</v>
       </c>
       <c r="H1102" s="6" t="s">
-        <v>6824</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="1103">
       <c r="B1103" s="5" t="s">
-        <v>6825</v>
+        <v>6831</v>
       </c>
       <c r="C1103" s="5" t="s">
-        <v>6826</v>
+        <v>6785</v>
       </c>
       <c r="D1103" s="5" t="s">
-        <v>6827</v>
+        <v>6786</v>
       </c>
       <c r="E1103" s="5" t="s">
-        <v>6828</v>
+        <v>6787</v>
       </c>
       <c r="F1103" s="5" t="s">
-        <v>6829</v>
+        <v>6788</v>
       </c>
       <c r="G1103" s="5" t="s">
-        <v>6830</v>
+        <v>6788</v>
       </c>
       <c r="H1103" s="5" t="s">
-        <v>6831</v>
+        <v>6789</v>
       </c>
     </row>
     <row r="1104">
@@ -49171,134 +49213,134 @@
         <v>6860</v>
       </c>
       <c r="C1108" s="6" t="s">
-        <v>4624</v>
+        <v>6861</v>
       </c>
       <c r="D1108" s="6" t="s">
-        <v>6861</v>
+        <v>6862</v>
       </c>
       <c r="E1108" s="6" t="s">
-        <v>4626</v>
+        <v>6863</v>
       </c>
       <c r="F1108" s="6" t="s">
-        <v>6508</v>
+        <v>6864</v>
       </c>
       <c r="G1108" s="6" t="s">
-        <v>6509</v>
+        <v>6865</v>
       </c>
       <c r="H1108" s="6" t="s">
-        <v>6862</v>
+        <v>6866</v>
       </c>
     </row>
     <row r="1109">
       <c r="B1109" s="5" t="s">
-        <v>6863</v>
+        <v>6867</v>
       </c>
       <c r="C1109" s="5" t="s">
-        <v>4791</v>
+        <v>6868</v>
       </c>
       <c r="D1109" s="5" t="s">
-        <v>4568</v>
+        <v>6869</v>
       </c>
       <c r="E1109" s="5" t="s">
-        <v>4792</v>
+        <v>6870</v>
       </c>
       <c r="F1109" s="5" t="s">
-        <v>4793</v>
+        <v>6871</v>
       </c>
       <c r="G1109" s="5" t="s">
-        <v>4794</v>
+        <v>6872</v>
       </c>
       <c r="H1109" s="5" t="s">
-        <v>4568</v>
+        <v>6873</v>
       </c>
     </row>
     <row r="1110">
       <c r="B1110" s="6" t="s">
-        <v>6864</v>
+        <v>6874</v>
       </c>
       <c r="C1110" s="6" t="s">
-        <v>6490</v>
+        <v>4624</v>
       </c>
       <c r="D1110" s="6" t="s">
-        <v>6865</v>
+        <v>6875</v>
       </c>
       <c r="E1110" s="6" t="s">
-        <v>6492</v>
+        <v>4626</v>
       </c>
       <c r="F1110" s="6" t="s">
-        <v>6493</v>
+        <v>6522</v>
       </c>
       <c r="G1110" s="6" t="s">
-        <v>6494</v>
+        <v>6523</v>
       </c>
       <c r="H1110" s="6" t="s">
-        <v>6866</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="1111">
       <c r="B1111" s="5" t="s">
-        <v>6867</v>
+        <v>6877</v>
       </c>
       <c r="C1111" s="5" t="s">
-        <v>6868</v>
+        <v>4791</v>
       </c>
       <c r="D1111" s="5" t="s">
-        <v>6869</v>
+        <v>4568</v>
       </c>
       <c r="E1111" s="5" t="s">
-        <v>6870</v>
+        <v>4792</v>
       </c>
       <c r="F1111" s="5" t="s">
-        <v>6871</v>
+        <v>4793</v>
       </c>
       <c r="G1111" s="5" t="s">
-        <v>6870</v>
+        <v>4794</v>
       </c>
       <c r="H1111" s="5" t="s">
-        <v>6872</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="1112">
       <c r="B1112" s="6" t="s">
-        <v>6873</v>
+        <v>6878</v>
       </c>
       <c r="C1112" s="6" t="s">
-        <v>6874</v>
+        <v>6504</v>
       </c>
       <c r="D1112" s="6" t="s">
-        <v>6875</v>
+        <v>6879</v>
       </c>
       <c r="E1112" s="6" t="s">
-        <v>6876</v>
+        <v>6506</v>
       </c>
       <c r="F1112" s="6" t="s">
-        <v>6877</v>
+        <v>6507</v>
       </c>
       <c r="G1112" s="6" t="s">
-        <v>6878</v>
+        <v>6508</v>
       </c>
       <c r="H1112" s="6" t="s">
-        <v>6879</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="1113">
       <c r="B1113" s="5" t="s">
-        <v>6880</v>
+        <v>6881</v>
       </c>
       <c r="C1113" s="5" t="s">
-        <v>6881</v>
+        <v>6882</v>
       </c>
       <c r="D1113" s="5" t="s">
-        <v>6882</v>
+        <v>6883</v>
       </c>
       <c r="E1113" s="5" t="s">
-        <v>6883</v>
+        <v>6884</v>
       </c>
       <c r="F1113" s="5" t="s">
+        <v>6885</v>
+      </c>
+      <c r="G1113" s="5" t="s">
         <v>6884</v>
-      </c>
-      <c r="G1113" s="5" t="s">
-        <v>6885</v>
       </c>
       <c r="H1113" s="5" t="s">
         <v>6886</v>
@@ -49361,53 +49403,53 @@
         <v>6903</v>
       </c>
       <c r="E1116" s="6" t="s">
-        <v>3172</v>
+        <v>6904</v>
       </c>
       <c r="F1116" s="6" t="s">
-        <v>6904</v>
+        <v>6905</v>
       </c>
       <c r="G1116" s="6" t="s">
-        <v>6905</v>
+        <v>6906</v>
       </c>
       <c r="H1116" s="6" t="s">
-        <v>6906</v>
+        <v>6907</v>
       </c>
     </row>
     <row r="1117">
       <c r="B1117" s="5" t="s">
-        <v>6907</v>
+        <v>6908</v>
       </c>
       <c r="C1117" s="5" t="s">
-        <v>6908</v>
+        <v>6909</v>
       </c>
       <c r="D1117" s="5" t="s">
-        <v>6909</v>
+        <v>6910</v>
       </c>
       <c r="E1117" s="5" t="s">
-        <v>6910</v>
+        <v>6911</v>
       </c>
       <c r="F1117" s="5" t="s">
-        <v>6911</v>
+        <v>6912</v>
       </c>
       <c r="G1117" s="5" t="s">
-        <v>6912</v>
+        <v>6913</v>
       </c>
       <c r="H1117" s="5" t="s">
-        <v>6913</v>
+        <v>6914</v>
       </c>
     </row>
     <row r="1118">
       <c r="B1118" s="6" t="s">
-        <v>6914</v>
+        <v>6915</v>
       </c>
       <c r="C1118" s="6" t="s">
-        <v>6915</v>
+        <v>6916</v>
       </c>
       <c r="D1118" s="6" t="s">
-        <v>6916</v>
+        <v>6917</v>
       </c>
       <c r="E1118" s="6" t="s">
-        <v>6917</v>
+        <v>3172</v>
       </c>
       <c r="F1118" s="6" t="s">
         <v>6918</v>
@@ -49469,138 +49511,138 @@
       <c r="B1121" s="5" t="s">
         <v>6935</v>
       </c>
-      <c r="C1121" s="7" t="s">
+      <c r="C1121" s="5" t="s">
         <v>6936</v>
       </c>
-      <c r="D1121" s="7" t="s">
-        <v>6936</v>
-      </c>
-      <c r="E1121" s="7" t="s">
-        <v>6936</v>
-      </c>
-      <c r="F1121" s="7" t="s">
-        <v>6936</v>
-      </c>
-      <c r="G1121" s="7" t="s">
-        <v>6936</v>
-      </c>
-      <c r="H1121" s="7" t="s">
-        <v>6936</v>
+      <c r="D1121" s="5" t="s">
+        <v>6937</v>
+      </c>
+      <c r="E1121" s="5" t="s">
+        <v>6938</v>
+      </c>
+      <c r="F1121" s="5" t="s">
+        <v>6939</v>
+      </c>
+      <c r="G1121" s="5" t="s">
+        <v>6940</v>
+      </c>
+      <c r="H1121" s="5" t="s">
+        <v>6941</v>
       </c>
     </row>
     <row r="1122">
       <c r="B1122" s="6" t="s">
-        <v>6937</v>
+        <v>6942</v>
       </c>
       <c r="C1122" s="6" t="s">
-        <v>6350</v>
+        <v>6943</v>
       </c>
       <c r="D1122" s="6" t="s">
-        <v>6351</v>
+        <v>6944</v>
       </c>
       <c r="E1122" s="6" t="s">
-        <v>6352</v>
+        <v>6945</v>
       </c>
       <c r="F1122" s="6" t="s">
-        <v>6353</v>
+        <v>6946</v>
       </c>
       <c r="G1122" s="6" t="s">
-        <v>6354</v>
+        <v>6947</v>
       </c>
       <c r="H1122" s="6" t="s">
-        <v>6351</v>
+        <v>6948</v>
       </c>
     </row>
     <row r="1123">
       <c r="B1123" s="5" t="s">
-        <v>6938</v>
-      </c>
-      <c r="C1123" s="5" t="s">
-        <v>6939</v>
-      </c>
-      <c r="D1123" s="5" t="s">
-        <v>6940</v>
-      </c>
-      <c r="E1123" s="5" t="s">
-        <v>6941</v>
-      </c>
-      <c r="F1123" s="5" t="s">
-        <v>6942</v>
-      </c>
-      <c r="G1123" s="5" t="s">
-        <v>6942</v>
-      </c>
-      <c r="H1123" s="5" t="s">
-        <v>4649</v>
+        <v>6949</v>
+      </c>
+      <c r="C1123" s="7" t="s">
+        <v>6950</v>
+      </c>
+      <c r="D1123" s="7" t="s">
+        <v>6950</v>
+      </c>
+      <c r="E1123" s="7" t="s">
+        <v>6950</v>
+      </c>
+      <c r="F1123" s="7" t="s">
+        <v>6950</v>
+      </c>
+      <c r="G1123" s="7" t="s">
+        <v>6950</v>
+      </c>
+      <c r="H1123" s="7" t="s">
+        <v>6950</v>
       </c>
     </row>
     <row r="1124">
       <c r="B1124" s="6" t="s">
-        <v>6943</v>
+        <v>6951</v>
       </c>
       <c r="C1124" s="6" t="s">
-        <v>6944</v>
+        <v>6364</v>
       </c>
       <c r="D1124" s="6" t="s">
-        <v>6945</v>
+        <v>6365</v>
       </c>
       <c r="E1124" s="6" t="s">
-        <v>6946</v>
+        <v>6366</v>
       </c>
       <c r="F1124" s="6" t="s">
-        <v>6947</v>
+        <v>6367</v>
       </c>
       <c r="G1124" s="6" t="s">
-        <v>6948</v>
+        <v>6368</v>
       </c>
       <c r="H1124" s="6" t="s">
-        <v>3835</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="1125">
       <c r="B1125" s="5" t="s">
-        <v>6949</v>
+        <v>6952</v>
       </c>
       <c r="C1125" s="5" t="s">
-        <v>6950</v>
+        <v>6953</v>
       </c>
       <c r="D1125" s="5" t="s">
-        <v>6951</v>
+        <v>6954</v>
       </c>
       <c r="E1125" s="5" t="s">
-        <v>6952</v>
+        <v>6955</v>
       </c>
       <c r="F1125" s="5" t="s">
-        <v>6953</v>
+        <v>6956</v>
       </c>
       <c r="G1125" s="5" t="s">
-        <v>6954</v>
+        <v>6956</v>
       </c>
       <c r="H1125" s="5" t="s">
-        <v>6955</v>
+        <v>4649</v>
       </c>
     </row>
     <row r="1126">
       <c r="B1126" s="6" t="s">
-        <v>6956</v>
+        <v>6957</v>
       </c>
       <c r="C1126" s="6" t="s">
-        <v>6957</v>
+        <v>6958</v>
       </c>
       <c r="D1126" s="6" t="s">
-        <v>6958</v>
+        <v>6959</v>
       </c>
       <c r="E1126" s="6" t="s">
-        <v>6959</v>
+        <v>6960</v>
       </c>
       <c r="F1126" s="6" t="s">
-        <v>6960</v>
+        <v>6961</v>
       </c>
       <c r="G1126" s="6" t="s">
-        <v>6961</v>
+        <v>6962</v>
       </c>
       <c r="H1126" s="6" t="s">
-        <v>6962</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="1127">
@@ -49620,171 +49662,171 @@
         <v>6967</v>
       </c>
       <c r="G1127" s="5" t="s">
-        <v>6967</v>
+        <v>6968</v>
       </c>
       <c r="H1127" s="5" t="s">
-        <v>6968</v>
+        <v>6969</v>
       </c>
     </row>
     <row r="1128">
       <c r="B1128" s="6" t="s">
-        <v>6969</v>
+        <v>6970</v>
       </c>
       <c r="C1128" s="6" t="s">
-        <v>6970</v>
+        <v>6971</v>
       </c>
       <c r="D1128" s="6" t="s">
-        <v>6971</v>
+        <v>6972</v>
       </c>
       <c r="E1128" s="6" t="s">
-        <v>6972</v>
+        <v>6973</v>
       </c>
       <c r="F1128" s="6" t="s">
-        <v>6973</v>
+        <v>6974</v>
       </c>
       <c r="G1128" s="6" t="s">
-        <v>6974</v>
+        <v>6975</v>
       </c>
       <c r="H1128" s="6" t="s">
-        <v>6975</v>
+        <v>6976</v>
       </c>
     </row>
     <row r="1129">
       <c r="B1129" s="5" t="s">
-        <v>6976</v>
+        <v>6977</v>
       </c>
       <c r="C1129" s="5" t="s">
-        <v>6977</v>
+        <v>6978</v>
       </c>
       <c r="D1129" s="5" t="s">
-        <v>6978</v>
+        <v>6979</v>
       </c>
       <c r="E1129" s="5" t="s">
-        <v>6979</v>
+        <v>6980</v>
       </c>
       <c r="F1129" s="5" t="s">
-        <v>6980</v>
+        <v>6981</v>
       </c>
       <c r="G1129" s="5" t="s">
-        <v>6980</v>
+        <v>6981</v>
       </c>
       <c r="H1129" s="5" t="s">
-        <v>6981</v>
+        <v>6982</v>
       </c>
     </row>
     <row r="1130">
       <c r="B1130" s="6" t="s">
-        <v>6982</v>
+        <v>6983</v>
       </c>
       <c r="C1130" s="6" t="s">
-        <v>6983</v>
+        <v>6984</v>
       </c>
       <c r="D1130" s="6" t="s">
-        <v>6983</v>
+        <v>6985</v>
       </c>
       <c r="E1130" s="6" t="s">
-        <v>6983</v>
+        <v>6986</v>
       </c>
       <c r="F1130" s="6" t="s">
-        <v>6983</v>
+        <v>6987</v>
       </c>
       <c r="G1130" s="6" t="s">
-        <v>6983</v>
+        <v>6988</v>
       </c>
       <c r="H1130" s="6" t="s">
-        <v>6983</v>
+        <v>6989</v>
       </c>
     </row>
     <row r="1131">
       <c r="B1131" s="5" t="s">
-        <v>6984</v>
+        <v>6990</v>
       </c>
       <c r="C1131" s="5" t="s">
-        <v>6985</v>
+        <v>6991</v>
       </c>
       <c r="D1131" s="5" t="s">
-        <v>6986</v>
+        <v>6992</v>
       </c>
       <c r="E1131" s="5" t="s">
-        <v>6987</v>
+        <v>6993</v>
       </c>
       <c r="F1131" s="5" t="s">
-        <v>6988</v>
+        <v>6994</v>
       </c>
       <c r="G1131" s="5" t="s">
-        <v>6988</v>
+        <v>6994</v>
       </c>
       <c r="H1131" s="5" t="s">
-        <v>6989</v>
+        <v>6995</v>
       </c>
     </row>
     <row r="1132">
       <c r="B1132" s="6" t="s">
-        <v>6990</v>
+        <v>6996</v>
       </c>
       <c r="C1132" s="6" t="s">
-        <v>6983</v>
+        <v>6997</v>
       </c>
       <c r="D1132" s="6" t="s">
-        <v>6983</v>
+        <v>6997</v>
       </c>
       <c r="E1132" s="6" t="s">
-        <v>6983</v>
+        <v>6997</v>
       </c>
       <c r="F1132" s="6" t="s">
-        <v>6983</v>
+        <v>6997</v>
       </c>
       <c r="G1132" s="6" t="s">
-        <v>6983</v>
+        <v>6997</v>
       </c>
       <c r="H1132" s="6" t="s">
-        <v>6983</v>
+        <v>6997</v>
       </c>
     </row>
     <row r="1133">
       <c r="B1133" s="5" t="s">
-        <v>6991</v>
+        <v>6998</v>
       </c>
       <c r="C1133" s="5" t="s">
-        <v>6992</v>
+        <v>6999</v>
       </c>
       <c r="D1133" s="5" t="s">
-        <v>6993</v>
+        <v>7000</v>
       </c>
       <c r="E1133" s="5" t="s">
-        <v>6994</v>
+        <v>7001</v>
       </c>
       <c r="F1133" s="5" t="s">
-        <v>6995</v>
+        <v>7002</v>
       </c>
       <c r="G1133" s="5" t="s">
-        <v>6996</v>
+        <v>7002</v>
       </c>
       <c r="H1133" s="5" t="s">
-        <v>6997</v>
+        <v>7003</v>
       </c>
     </row>
     <row r="1134">
       <c r="B1134" s="6" t="s">
-        <v>6998</v>
+        <v>7004</v>
       </c>
       <c r="C1134" s="6" t="s">
-        <v>6999</v>
+        <v>6997</v>
       </c>
       <c r="D1134" s="6" t="s">
-        <v>7000</v>
+        <v>6997</v>
       </c>
       <c r="E1134" s="6" t="s">
-        <v>7001</v>
+        <v>6997</v>
       </c>
       <c r="F1134" s="6" t="s">
-        <v>7002</v>
+        <v>6997</v>
       </c>
       <c r="G1134" s="6" t="s">
-        <v>7003</v>
+        <v>6997</v>
       </c>
       <c r="H1134" s="6" t="s">
-        <v>7004</v>
+        <v>6997</v>
       </c>
     </row>
     <row r="1135">
@@ -49838,62 +49880,62 @@
         <v>7019</v>
       </c>
       <c r="C1137" s="5" t="s">
-        <v>3830</v>
+        <v>7020</v>
       </c>
       <c r="D1137" s="5" t="s">
-        <v>7020</v>
+        <v>7021</v>
       </c>
       <c r="E1137" s="5" t="s">
-        <v>3832</v>
+        <v>7022</v>
       </c>
       <c r="F1137" s="5" t="s">
-        <v>7021</v>
+        <v>7023</v>
       </c>
       <c r="G1137" s="5" t="s">
-        <v>7021</v>
+        <v>7024</v>
       </c>
       <c r="H1137" s="5" t="s">
-        <v>7022</v>
+        <v>7025</v>
       </c>
     </row>
     <row r="1138">
       <c r="B1138" s="6" t="s">
-        <v>7023</v>
+        <v>7026</v>
       </c>
       <c r="C1138" s="6" t="s">
-        <v>7024</v>
+        <v>7027</v>
       </c>
       <c r="D1138" s="6" t="s">
-        <v>7025</v>
+        <v>7028</v>
       </c>
       <c r="E1138" s="6" t="s">
-        <v>7026</v>
+        <v>7029</v>
       </c>
       <c r="F1138" s="6" t="s">
-        <v>7027</v>
+        <v>7030</v>
       </c>
       <c r="G1138" s="6" t="s">
-        <v>7028</v>
+        <v>7031</v>
       </c>
       <c r="H1138" s="6" t="s">
-        <v>7029</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="1139">
       <c r="B1139" s="5" t="s">
-        <v>7030</v>
+        <v>7033</v>
       </c>
       <c r="C1139" s="5" t="s">
-        <v>7031</v>
+        <v>3830</v>
       </c>
       <c r="D1139" s="5" t="s">
-        <v>7032</v>
+        <v>7034</v>
       </c>
       <c r="E1139" s="5" t="s">
-        <v>7033</v>
+        <v>3832</v>
       </c>
       <c r="F1139" s="5" t="s">
-        <v>7034</v>
+        <v>7035</v>
       </c>
       <c r="G1139" s="5" t="s">
         <v>7035</v>
@@ -49979,82 +50021,82 @@
         <v>7059</v>
       </c>
       <c r="D1143" s="5" t="s">
-        <v>7059</v>
+        <v>7060</v>
       </c>
       <c r="E1143" s="5" t="s">
-        <v>7059</v>
+        <v>7061</v>
       </c>
       <c r="F1143" s="5" t="s">
-        <v>7059</v>
+        <v>7062</v>
       </c>
       <c r="G1143" s="5" t="s">
-        <v>7059</v>
+        <v>7063</v>
       </c>
       <c r="H1143" s="5" t="s">
-        <v>7059</v>
+        <v>7064</v>
       </c>
     </row>
     <row r="1144">
       <c r="B1144" s="6" t="s">
-        <v>7060</v>
+        <v>7065</v>
       </c>
       <c r="C1144" s="6" t="s">
-        <v>7061</v>
+        <v>7066</v>
       </c>
       <c r="D1144" s="6" t="s">
-        <v>7062</v>
+        <v>7067</v>
       </c>
       <c r="E1144" s="6" t="s">
-        <v>7063</v>
+        <v>7068</v>
       </c>
       <c r="F1144" s="6" t="s">
-        <v>7064</v>
+        <v>7069</v>
       </c>
       <c r="G1144" s="6" t="s">
-        <v>7064</v>
+        <v>7070</v>
       </c>
       <c r="H1144" s="6" t="s">
-        <v>7065</v>
+        <v>7071</v>
       </c>
     </row>
     <row r="1145">
       <c r="B1145" s="5" t="s">
-        <v>7066</v>
+        <v>7072</v>
       </c>
       <c r="C1145" s="5" t="s">
-        <v>7067</v>
+        <v>7073</v>
       </c>
       <c r="D1145" s="5" t="s">
-        <v>7068</v>
+        <v>7073</v>
       </c>
       <c r="E1145" s="5" t="s">
-        <v>7069</v>
+        <v>7073</v>
       </c>
       <c r="F1145" s="5" t="s">
-        <v>7070</v>
+        <v>7073</v>
       </c>
       <c r="G1145" s="5" t="s">
-        <v>7071</v>
+        <v>7073</v>
       </c>
       <c r="H1145" s="5" t="s">
-        <v>7072</v>
+        <v>7073</v>
       </c>
     </row>
     <row r="1146">
       <c r="B1146" s="6" t="s">
-        <v>7073</v>
+        <v>7074</v>
       </c>
       <c r="C1146" s="6" t="s">
-        <v>7074</v>
+        <v>7075</v>
       </c>
       <c r="D1146" s="6" t="s">
-        <v>7075</v>
+        <v>7076</v>
       </c>
       <c r="E1146" s="6" t="s">
-        <v>7076</v>
+        <v>7077</v>
       </c>
       <c r="F1146" s="6" t="s">
-        <v>7077</v>
+        <v>7078</v>
       </c>
       <c r="G1146" s="6" t="s">
         <v>7078</v>
@@ -50080,73 +50122,73 @@
         <v>7084</v>
       </c>
       <c r="G1147" s="5" t="s">
-        <v>7084</v>
+        <v>7085</v>
       </c>
       <c r="H1147" s="5" t="s">
-        <v>7085</v>
+        <v>7086</v>
       </c>
     </row>
     <row r="1148">
       <c r="B1148" s="6" t="s">
-        <v>7086</v>
+        <v>7087</v>
       </c>
       <c r="C1148" s="6" t="s">
-        <v>7087</v>
+        <v>7088</v>
       </c>
       <c r="D1148" s="6" t="s">
-        <v>7088</v>
+        <v>7089</v>
       </c>
       <c r="E1148" s="6" t="s">
-        <v>7089</v>
+        <v>7090</v>
       </c>
       <c r="F1148" s="6" t="s">
-        <v>7090</v>
+        <v>7091</v>
       </c>
       <c r="G1148" s="6" t="s">
-        <v>7090</v>
+        <v>7092</v>
       </c>
       <c r="H1148" s="6" t="s">
-        <v>7091</v>
+        <v>7093</v>
       </c>
     </row>
     <row r="1149">
       <c r="B1149" s="5" t="s">
-        <v>7092</v>
+        <v>7094</v>
       </c>
       <c r="C1149" s="5" t="s">
-        <v>7093</v>
+        <v>7095</v>
       </c>
       <c r="D1149" s="5" t="s">
-        <v>7094</v>
+        <v>7096</v>
       </c>
       <c r="E1149" s="5" t="s">
-        <v>7095</v>
+        <v>7097</v>
       </c>
       <c r="F1149" s="5" t="s">
-        <v>7096</v>
+        <v>7098</v>
       </c>
       <c r="G1149" s="5" t="s">
-        <v>7097</v>
+        <v>7098</v>
       </c>
       <c r="H1149" s="5" t="s">
-        <v>7098</v>
+        <v>7099</v>
       </c>
     </row>
     <row r="1150">
       <c r="B1150" s="6" t="s">
-        <v>7099</v>
+        <v>7100</v>
       </c>
       <c r="C1150" s="6" t="s">
-        <v>7100</v>
+        <v>7101</v>
       </c>
       <c r="D1150" s="6" t="s">
-        <v>7101</v>
+        <v>7102</v>
       </c>
       <c r="E1150" s="6" t="s">
-        <v>7102</v>
+        <v>7103</v>
       </c>
       <c r="F1150" s="6" t="s">
-        <v>7103</v>
+        <v>7104</v>
       </c>
       <c r="G1150" s="6" t="s">
         <v>7104</v>
@@ -50390,59 +50432,59 @@
         <v>7176</v>
       </c>
       <c r="C1161" s="5" t="s">
-        <v>2300</v>
+        <v>7177</v>
       </c>
       <c r="D1161" s="5" t="s">
-        <v>7177</v>
+        <v>7178</v>
       </c>
       <c r="E1161" s="5" t="s">
-        <v>2302</v>
+        <v>7179</v>
       </c>
       <c r="F1161" s="5" t="s">
-        <v>7178</v>
+        <v>7180</v>
       </c>
       <c r="G1161" s="5" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="H1161" s="5" t="s">
-        <v>7180</v>
+        <v>7182</v>
       </c>
     </row>
     <row r="1162">
       <c r="B1162" s="6" t="s">
-        <v>7181</v>
+        <v>7183</v>
       </c>
       <c r="C1162" s="6" t="s">
-        <v>7182</v>
+        <v>7184</v>
       </c>
       <c r="D1162" s="6" t="s">
-        <v>7183</v>
+        <v>7185</v>
       </c>
       <c r="E1162" s="6" t="s">
-        <v>7184</v>
+        <v>7186</v>
       </c>
       <c r="F1162" s="6" t="s">
-        <v>7185</v>
+        <v>7187</v>
       </c>
       <c r="G1162" s="6" t="s">
-        <v>7186</v>
+        <v>7188</v>
       </c>
       <c r="H1162" s="6" t="s">
-        <v>7187</v>
+        <v>7189</v>
       </c>
     </row>
     <row r="1163">
       <c r="B1163" s="5" t="s">
-        <v>7188</v>
+        <v>7190</v>
       </c>
       <c r="C1163" s="5" t="s">
-        <v>7189</v>
+        <v>2300</v>
       </c>
       <c r="D1163" s="5" t="s">
-        <v>7190</v>
+        <v>7191</v>
       </c>
       <c r="E1163" s="5" t="s">
-        <v>7191</v>
+        <v>2302</v>
       </c>
       <c r="F1163" s="5" t="s">
         <v>7192</v>
@@ -50494,50 +50536,50 @@
         <v>7206</v>
       </c>
       <c r="G1165" s="5" t="s">
-        <v>7206</v>
+        <v>7207</v>
       </c>
       <c r="H1165" s="5" t="s">
-        <v>7207</v>
+        <v>7208</v>
       </c>
     </row>
     <row r="1166">
       <c r="B1166" s="6" t="s">
-        <v>7208</v>
+        <v>7209</v>
       </c>
       <c r="C1166" s="6" t="s">
-        <v>7209</v>
+        <v>7210</v>
       </c>
       <c r="D1166" s="6" t="s">
-        <v>7210</v>
+        <v>7211</v>
       </c>
       <c r="E1166" s="6" t="s">
-        <v>7211</v>
+        <v>7212</v>
       </c>
       <c r="F1166" s="6" t="s">
-        <v>7212</v>
+        <v>7213</v>
       </c>
       <c r="G1166" s="6" t="s">
-        <v>7213</v>
+        <v>7214</v>
       </c>
       <c r="H1166" s="6" t="s">
-        <v>7214</v>
+        <v>7215</v>
       </c>
     </row>
     <row r="1167">
       <c r="B1167" s="5" t="s">
-        <v>7215</v>
+        <v>7216</v>
       </c>
       <c r="C1167" s="5" t="s">
-        <v>7216</v>
+        <v>7217</v>
       </c>
       <c r="D1167" s="5" t="s">
-        <v>7217</v>
+        <v>7218</v>
       </c>
       <c r="E1167" s="5" t="s">
-        <v>7218</v>
+        <v>7219</v>
       </c>
       <c r="F1167" s="5" t="s">
-        <v>7219</v>
+        <v>7220</v>
       </c>
       <c r="G1167" s="5" t="s">
         <v>7220</v>
@@ -50586,50 +50628,50 @@
         <v>7233</v>
       </c>
       <c r="G1169" s="5" t="s">
-        <v>7233</v>
+        <v>7234</v>
       </c>
       <c r="H1169" s="5" t="s">
-        <v>7234</v>
+        <v>7235</v>
       </c>
     </row>
     <row r="1170">
       <c r="B1170" s="6" t="s">
-        <v>7235</v>
+        <v>7236</v>
       </c>
       <c r="C1170" s="6" t="s">
-        <v>7236</v>
+        <v>7237</v>
       </c>
       <c r="D1170" s="6" t="s">
-        <v>7237</v>
+        <v>7238</v>
       </c>
       <c r="E1170" s="6" t="s">
-        <v>7238</v>
+        <v>7239</v>
       </c>
       <c r="F1170" s="6" t="s">
-        <v>7239</v>
+        <v>7240</v>
       </c>
       <c r="G1170" s="6" t="s">
-        <v>7240</v>
+        <v>7241</v>
       </c>
       <c r="H1170" s="6" t="s">
-        <v>7241</v>
+        <v>7242</v>
       </c>
     </row>
     <row r="1171">
       <c r="B1171" s="5" t="s">
-        <v>7242</v>
+        <v>7243</v>
       </c>
       <c r="C1171" s="5" t="s">
-        <v>7243</v>
+        <v>7244</v>
       </c>
       <c r="D1171" s="5" t="s">
-        <v>7244</v>
+        <v>7245</v>
       </c>
       <c r="E1171" s="5" t="s">
-        <v>7245</v>
+        <v>7246</v>
       </c>
       <c r="F1171" s="5" t="s">
-        <v>7246</v>
+        <v>7247</v>
       </c>
       <c r="G1171" s="5" t="s">
         <v>7247</v>
@@ -50689,108 +50731,108 @@
         <v>7263</v>
       </c>
       <c r="C1174" s="6" t="s">
-        <v>3830</v>
+        <v>7264</v>
       </c>
       <c r="D1174" s="6" t="s">
-        <v>7020</v>
+        <v>7265</v>
       </c>
       <c r="E1174" s="6" t="s">
-        <v>7264</v>
+        <v>7266</v>
       </c>
       <c r="F1174" s="6" t="s">
-        <v>7021</v>
+        <v>7267</v>
       </c>
       <c r="G1174" s="6" t="s">
-        <v>7021</v>
+        <v>7268</v>
       </c>
       <c r="H1174" s="6" t="s">
-        <v>7022</v>
+        <v>7269</v>
       </c>
     </row>
     <row r="1175">
       <c r="B1175" s="5" t="s">
-        <v>7265</v>
+        <v>7270</v>
       </c>
       <c r="C1175" s="5" t="s">
-        <v>7266</v>
+        <v>7271</v>
       </c>
       <c r="D1175" s="5" t="s">
-        <v>7267</v>
+        <v>7272</v>
       </c>
       <c r="E1175" s="5" t="s">
-        <v>7268</v>
+        <v>7273</v>
       </c>
       <c r="F1175" s="5" t="s">
-        <v>7269</v>
+        <v>7274</v>
       </c>
       <c r="G1175" s="5" t="s">
-        <v>7269</v>
+        <v>7275</v>
       </c>
       <c r="H1175" s="5" t="s">
-        <v>7270</v>
+        <v>7276</v>
       </c>
     </row>
     <row r="1176">
       <c r="B1176" s="6" t="s">
-        <v>7271</v>
+        <v>7277</v>
       </c>
       <c r="C1176" s="6" t="s">
-        <v>7272</v>
+        <v>3830</v>
       </c>
       <c r="D1176" s="6" t="s">
-        <v>7273</v>
+        <v>7034</v>
       </c>
       <c r="E1176" s="6" t="s">
-        <v>7274</v>
+        <v>7278</v>
       </c>
       <c r="F1176" s="6" t="s">
-        <v>7275</v>
+        <v>7035</v>
       </c>
       <c r="G1176" s="6" t="s">
-        <v>7275</v>
+        <v>7035</v>
       </c>
       <c r="H1176" s="6" t="s">
-        <v>7276</v>
+        <v>7036</v>
       </c>
     </row>
     <row r="1177">
       <c r="B1177" s="5" t="s">
-        <v>7277</v>
+        <v>7279</v>
       </c>
       <c r="C1177" s="5" t="s">
-        <v>7278</v>
+        <v>7280</v>
       </c>
       <c r="D1177" s="5" t="s">
-        <v>7279</v>
+        <v>7281</v>
       </c>
       <c r="E1177" s="5" t="s">
-        <v>7280</v>
+        <v>7282</v>
       </c>
       <c r="F1177" s="5" t="s">
-        <v>7281</v>
+        <v>7283</v>
       </c>
       <c r="G1177" s="5" t="s">
-        <v>7282</v>
+        <v>7283</v>
       </c>
       <c r="H1177" s="5" t="s">
-        <v>7283</v>
+        <v>7284</v>
       </c>
     </row>
     <row r="1178">
       <c r="B1178" s="6" t="s">
-        <v>7284</v>
+        <v>7285</v>
       </c>
       <c r="C1178" s="6" t="s">
-        <v>7285</v>
+        <v>7286</v>
       </c>
       <c r="D1178" s="6" t="s">
-        <v>7286</v>
+        <v>7287</v>
       </c>
       <c r="E1178" s="6" t="s">
-        <v>7287</v>
+        <v>7288</v>
       </c>
       <c r="F1178" s="6" t="s">
-        <v>7288</v>
+        <v>7289</v>
       </c>
       <c r="G1178" s="6" t="s">
         <v>7289</v>
@@ -50862,171 +50904,171 @@
         <v>7309</v>
       </c>
       <c r="G1181" s="5" t="s">
-        <v>7309</v>
+        <v>7310</v>
       </c>
       <c r="H1181" s="5" t="s">
-        <v>7310</v>
+        <v>7311</v>
       </c>
     </row>
     <row r="1182">
       <c r="B1182" s="6" t="s">
-        <v>7311</v>
+        <v>7312</v>
       </c>
       <c r="C1182" s="6" t="s">
-        <v>7312</v>
+        <v>7313</v>
       </c>
       <c r="D1182" s="6" t="s">
-        <v>7313</v>
+        <v>7314</v>
       </c>
       <c r="E1182" s="6" t="s">
-        <v>7314</v>
+        <v>7315</v>
       </c>
       <c r="F1182" s="6" t="s">
-        <v>7315</v>
+        <v>7316</v>
       </c>
       <c r="G1182" s="6" t="s">
-        <v>7314</v>
+        <v>7317</v>
       </c>
       <c r="H1182" s="6" t="s">
-        <v>7316</v>
+        <v>7318</v>
       </c>
     </row>
     <row r="1183">
       <c r="B1183" s="5" t="s">
-        <v>7317</v>
+        <v>7319</v>
       </c>
       <c r="C1183" s="5" t="s">
-        <v>7318</v>
+        <v>7320</v>
       </c>
       <c r="D1183" s="5" t="s">
-        <v>7319</v>
+        <v>7321</v>
       </c>
       <c r="E1183" s="5" t="s">
-        <v>4667</v>
+        <v>7322</v>
       </c>
       <c r="F1183" s="5" t="s">
-        <v>7320</v>
+        <v>7323</v>
       </c>
       <c r="G1183" s="5" t="s">
-        <v>7320</v>
+        <v>7323</v>
       </c>
       <c r="H1183" s="5" t="s">
-        <v>4670</v>
+        <v>7324</v>
       </c>
     </row>
     <row r="1184">
       <c r="B1184" s="6" t="s">
-        <v>7321</v>
+        <v>7325</v>
       </c>
       <c r="C1184" s="6" t="s">
-        <v>7322</v>
+        <v>7326</v>
       </c>
       <c r="D1184" s="6" t="s">
-        <v>7323</v>
+        <v>7327</v>
       </c>
       <c r="E1184" s="6" t="s">
-        <v>7324</v>
+        <v>7328</v>
       </c>
       <c r="F1184" s="6" t="s">
-        <v>7325</v>
+        <v>7329</v>
       </c>
       <c r="G1184" s="6" t="s">
-        <v>7325</v>
+        <v>7328</v>
       </c>
       <c r="H1184" s="6" t="s">
-        <v>7326</v>
+        <v>7330</v>
       </c>
     </row>
     <row r="1185">
       <c r="B1185" s="5" t="s">
-        <v>7327</v>
+        <v>7331</v>
       </c>
       <c r="C1185" s="5" t="s">
-        <v>7328</v>
+        <v>7332</v>
       </c>
       <c r="D1185" s="5" t="s">
-        <v>6875</v>
+        <v>7333</v>
       </c>
       <c r="E1185" s="5" t="s">
-        <v>7329</v>
+        <v>4667</v>
       </c>
       <c r="F1185" s="5" t="s">
-        <v>7330</v>
+        <v>7334</v>
       </c>
       <c r="G1185" s="5" t="s">
-        <v>7330</v>
+        <v>7334</v>
       </c>
       <c r="H1185" s="5" t="s">
-        <v>6879</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="1186">
       <c r="B1186" s="6" t="s">
-        <v>7331</v>
+        <v>7335</v>
       </c>
       <c r="C1186" s="6" t="s">
-        <v>7332</v>
+        <v>7336</v>
       </c>
       <c r="D1186" s="6" t="s">
-        <v>5105</v>
+        <v>7337</v>
       </c>
       <c r="E1186" s="6" t="s">
-        <v>3653</v>
+        <v>7338</v>
       </c>
       <c r="F1186" s="6" t="s">
-        <v>7333</v>
+        <v>7339</v>
       </c>
       <c r="G1186" s="6" t="s">
-        <v>7333</v>
+        <v>7339</v>
       </c>
       <c r="H1186" s="6" t="s">
-        <v>3656</v>
+        <v>7340</v>
       </c>
     </row>
     <row r="1187">
       <c r="B1187" s="5" t="s">
-        <v>7334</v>
+        <v>7341</v>
       </c>
       <c r="C1187" s="5" t="s">
-        <v>7335</v>
+        <v>7342</v>
       </c>
       <c r="D1187" s="5" t="s">
-        <v>7336</v>
+        <v>6889</v>
       </c>
       <c r="E1187" s="5" t="s">
-        <v>7337</v>
+        <v>7343</v>
       </c>
       <c r="F1187" s="5" t="s">
-        <v>7338</v>
+        <v>7344</v>
       </c>
       <c r="G1187" s="5" t="s">
-        <v>7339</v>
+        <v>7344</v>
       </c>
       <c r="H1187" s="5" t="s">
-        <v>7340</v>
+        <v>6893</v>
       </c>
     </row>
     <row r="1188">
       <c r="B1188" s="6" t="s">
-        <v>7341</v>
+        <v>7345</v>
       </c>
       <c r="C1188" s="6" t="s">
-        <v>7342</v>
+        <v>7346</v>
       </c>
       <c r="D1188" s="6" t="s">
-        <v>7343</v>
+        <v>5105</v>
       </c>
       <c r="E1188" s="6" t="s">
-        <v>7344</v>
+        <v>3653</v>
       </c>
       <c r="F1188" s="6" t="s">
-        <v>7345</v>
+        <v>7347</v>
       </c>
       <c r="G1188" s="6" t="s">
-        <v>7346</v>
+        <v>7347</v>
       </c>
       <c r="H1188" s="6" t="s">
-        <v>7347</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="1189">
@@ -51046,50 +51088,50 @@
         <v>7352</v>
       </c>
       <c r="G1189" s="5" t="s">
-        <v>7352</v>
+        <v>7353</v>
       </c>
       <c r="H1189" s="5" t="s">
-        <v>7353</v>
+        <v>7354</v>
       </c>
     </row>
     <row r="1190">
       <c r="B1190" s="6" t="s">
-        <v>7354</v>
+        <v>7355</v>
       </c>
       <c r="C1190" s="6" t="s">
-        <v>7355</v>
+        <v>7356</v>
       </c>
       <c r="D1190" s="6" t="s">
-        <v>7356</v>
+        <v>7357</v>
       </c>
       <c r="E1190" s="6" t="s">
-        <v>7357</v>
+        <v>7358</v>
       </c>
       <c r="F1190" s="6" t="s">
-        <v>7358</v>
+        <v>7359</v>
       </c>
       <c r="G1190" s="6" t="s">
-        <v>7359</v>
+        <v>7360</v>
       </c>
       <c r="H1190" s="6" t="s">
-        <v>7360</v>
+        <v>7361</v>
       </c>
     </row>
     <row r="1191">
       <c r="B1191" s="5" t="s">
-        <v>7361</v>
+        <v>7362</v>
       </c>
       <c r="C1191" s="5" t="s">
-        <v>7362</v>
+        <v>7363</v>
       </c>
       <c r="D1191" s="5" t="s">
-        <v>7363</v>
+        <v>7364</v>
       </c>
       <c r="E1191" s="5" t="s">
-        <v>7364</v>
+        <v>7365</v>
       </c>
       <c r="F1191" s="5" t="s">
-        <v>7365</v>
+        <v>7366</v>
       </c>
       <c r="G1191" s="5" t="s">
         <v>7366</v>
@@ -51172,85 +51214,85 @@
         <v>7389</v>
       </c>
       <c r="C1195" s="5" t="s">
-        <v>2255</v>
+        <v>7390</v>
       </c>
       <c r="D1195" s="5" t="s">
-        <v>7390</v>
+        <v>7391</v>
       </c>
       <c r="E1195" s="5" t="s">
-        <v>5328</v>
+        <v>7392</v>
       </c>
       <c r="F1195" s="5" t="s">
-        <v>7391</v>
+        <v>7393</v>
       </c>
       <c r="G1195" s="5" t="s">
-        <v>7392</v>
+        <v>7394</v>
       </c>
       <c r="H1195" s="5" t="s">
-        <v>5325</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="1196">
       <c r="B1196" s="6" t="s">
-        <v>7393</v>
+        <v>7396</v>
       </c>
       <c r="C1196" s="6" t="s">
-        <v>7394</v>
+        <v>7397</v>
       </c>
       <c r="D1196" s="6" t="s">
-        <v>7395</v>
+        <v>7398</v>
       </c>
       <c r="E1196" s="6" t="s">
-        <v>7396</v>
+        <v>7399</v>
       </c>
       <c r="F1196" s="6" t="s">
-        <v>7397</v>
+        <v>7400</v>
       </c>
       <c r="G1196" s="6" t="s">
-        <v>7397</v>
+        <v>7401</v>
       </c>
       <c r="H1196" s="6" t="s">
-        <v>7398</v>
+        <v>7402</v>
       </c>
     </row>
     <row r="1197">
       <c r="B1197" s="5" t="s">
-        <v>7399</v>
+        <v>7403</v>
       </c>
       <c r="C1197" s="5" t="s">
-        <v>7400</v>
+        <v>2255</v>
       </c>
       <c r="D1197" s="5" t="s">
-        <v>7401</v>
+        <v>7404</v>
       </c>
       <c r="E1197" s="5" t="s">
-        <v>7402</v>
+        <v>5328</v>
       </c>
       <c r="F1197" s="5" t="s">
-        <v>7403</v>
+        <v>7405</v>
       </c>
       <c r="G1197" s="5" t="s">
-        <v>7404</v>
+        <v>7406</v>
       </c>
       <c r="H1197" s="5" t="s">
-        <v>7405</v>
+        <v>5325</v>
       </c>
     </row>
     <row r="1198">
       <c r="B1198" s="6" t="s">
-        <v>7406</v>
+        <v>7407</v>
       </c>
       <c r="C1198" s="6" t="s">
-        <v>7407</v>
+        <v>7408</v>
       </c>
       <c r="D1198" s="6" t="s">
-        <v>7408</v>
+        <v>7409</v>
       </c>
       <c r="E1198" s="6" t="s">
-        <v>7409</v>
+        <v>7410</v>
       </c>
       <c r="F1198" s="6" t="s">
-        <v>7410</v>
+        <v>7411</v>
       </c>
       <c r="G1198" s="6" t="s">
         <v>7411</v>
@@ -51322,171 +51364,171 @@
         <v>7431</v>
       </c>
       <c r="G1201" s="5" t="s">
-        <v>7431</v>
+        <v>7432</v>
       </c>
       <c r="H1201" s="5" t="s">
-        <v>7432</v>
+        <v>7433</v>
       </c>
     </row>
     <row r="1202">
       <c r="B1202" s="6" t="s">
-        <v>7433</v>
+        <v>7434</v>
       </c>
       <c r="C1202" s="6" t="s">
-        <v>7434</v>
+        <v>7435</v>
       </c>
       <c r="D1202" s="6" t="s">
-        <v>7435</v>
+        <v>7436</v>
       </c>
       <c r="E1202" s="6" t="s">
-        <v>7436</v>
+        <v>7437</v>
       </c>
       <c r="F1202" s="6" t="s">
-        <v>7437</v>
+        <v>7438</v>
       </c>
       <c r="G1202" s="6" t="s">
-        <v>7437</v>
+        <v>7439</v>
       </c>
       <c r="H1202" s="6" t="s">
-        <v>2253</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="1203">
       <c r="B1203" s="5" t="s">
-        <v>7438</v>
+        <v>7441</v>
       </c>
       <c r="C1203" s="5" t="s">
-        <v>7439</v>
+        <v>7442</v>
       </c>
       <c r="D1203" s="5" t="s">
-        <v>7440</v>
+        <v>7443</v>
       </c>
       <c r="E1203" s="5" t="s">
-        <v>7441</v>
+        <v>7444</v>
       </c>
       <c r="F1203" s="5" t="s">
-        <v>7442</v>
+        <v>7445</v>
       </c>
       <c r="G1203" s="5" t="s">
-        <v>7443</v>
+        <v>7445</v>
       </c>
       <c r="H1203" s="5" t="s">
-        <v>6521</v>
+        <v>7446</v>
       </c>
     </row>
     <row r="1204">
       <c r="B1204" s="6" t="s">
-        <v>7444</v>
+        <v>7447</v>
       </c>
       <c r="C1204" s="6" t="s">
-        <v>7445</v>
+        <v>7448</v>
       </c>
       <c r="D1204" s="6" t="s">
-        <v>4511</v>
+        <v>7449</v>
       </c>
       <c r="E1204" s="6" t="s">
-        <v>4512</v>
+        <v>7450</v>
       </c>
       <c r="F1204" s="6" t="s">
-        <v>7446</v>
+        <v>7451</v>
       </c>
       <c r="G1204" s="6" t="s">
-        <v>7446</v>
+        <v>7451</v>
       </c>
       <c r="H1204" s="6" t="s">
-        <v>7447</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="1205">
       <c r="B1205" s="5" t="s">
-        <v>7448</v>
+        <v>7452</v>
       </c>
       <c r="C1205" s="5" t="s">
-        <v>7449</v>
+        <v>7453</v>
       </c>
       <c r="D1205" s="5" t="s">
-        <v>7450</v>
+        <v>7454</v>
       </c>
       <c r="E1205" s="5" t="s">
-        <v>7451</v>
+        <v>7455</v>
       </c>
       <c r="F1205" s="5" t="s">
-        <v>7452</v>
+        <v>7456</v>
       </c>
       <c r="G1205" s="5" t="s">
-        <v>7453</v>
+        <v>7457</v>
       </c>
       <c r="H1205" s="5" t="s">
-        <v>7454</v>
+        <v>6535</v>
       </c>
     </row>
     <row r="1206">
       <c r="B1206" s="6" t="s">
-        <v>7455</v>
+        <v>7458</v>
       </c>
       <c r="C1206" s="6" t="s">
-        <v>6490</v>
+        <v>7459</v>
       </c>
       <c r="D1206" s="6" t="s">
-        <v>6865</v>
+        <v>4511</v>
       </c>
       <c r="E1206" s="6" t="s">
-        <v>6492</v>
+        <v>4512</v>
       </c>
       <c r="F1206" s="6" t="s">
-        <v>6493</v>
+        <v>7460</v>
       </c>
       <c r="G1206" s="6" t="s">
-        <v>6494</v>
+        <v>7460</v>
       </c>
       <c r="H1206" s="6" t="s">
-        <v>6866</v>
+        <v>7461</v>
       </c>
     </row>
     <row r="1207">
       <c r="B1207" s="5" t="s">
-        <v>7456</v>
+        <v>7462</v>
       </c>
       <c r="C1207" s="5" t="s">
-        <v>7457</v>
+        <v>7463</v>
       </c>
       <c r="D1207" s="5" t="s">
-        <v>7458</v>
+        <v>7464</v>
       </c>
       <c r="E1207" s="5" t="s">
-        <v>7459</v>
+        <v>7465</v>
       </c>
       <c r="F1207" s="5" t="s">
-        <v>7460</v>
+        <v>7466</v>
       </c>
       <c r="G1207" s="5" t="s">
-        <v>7461</v>
+        <v>7467</v>
       </c>
       <c r="H1207" s="5" t="s">
-        <v>7462</v>
+        <v>7468</v>
       </c>
     </row>
     <row r="1208">
       <c r="B1208" s="6" t="s">
-        <v>7463</v>
+        <v>7469</v>
       </c>
       <c r="C1208" s="6" t="s">
-        <v>7464</v>
+        <v>6504</v>
       </c>
       <c r="D1208" s="6" t="s">
-        <v>7465</v>
+        <v>6879</v>
       </c>
       <c r="E1208" s="6" t="s">
-        <v>7466</v>
+        <v>6506</v>
       </c>
       <c r="F1208" s="6" t="s">
-        <v>7467</v>
+        <v>6507</v>
       </c>
       <c r="G1208" s="6" t="s">
-        <v>7468</v>
+        <v>6508</v>
       </c>
       <c r="H1208" s="6" t="s">
-        <v>7469</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="1209">
@@ -51494,125 +51536,125 @@
         <v>7470</v>
       </c>
       <c r="C1209" s="5" t="s">
-        <v>4775</v>
+        <v>7471</v>
       </c>
       <c r="D1209" s="5" t="s">
-        <v>7471</v>
+        <v>7472</v>
       </c>
       <c r="E1209" s="5" t="s">
-        <v>4777</v>
+        <v>7473</v>
       </c>
       <c r="F1209" s="5" t="s">
-        <v>4778</v>
+        <v>7474</v>
       </c>
       <c r="G1209" s="5" t="s">
-        <v>4778</v>
+        <v>7475</v>
       </c>
       <c r="H1209" s="5" t="s">
-        <v>7472</v>
+        <v>7476</v>
       </c>
     </row>
     <row r="1210">
       <c r="B1210" s="6" t="s">
-        <v>7473</v>
+        <v>7477</v>
       </c>
       <c r="C1210" s="6" t="s">
-        <v>5289</v>
+        <v>7478</v>
       </c>
       <c r="D1210" s="6" t="s">
-        <v>7474</v>
+        <v>7479</v>
       </c>
       <c r="E1210" s="6" t="s">
-        <v>5291</v>
+        <v>7480</v>
       </c>
       <c r="F1210" s="6" t="s">
-        <v>5292</v>
+        <v>7481</v>
       </c>
       <c r="G1210" s="6" t="s">
-        <v>5292</v>
+        <v>7482</v>
       </c>
       <c r="H1210" s="6" t="s">
-        <v>7475</v>
+        <v>7483</v>
       </c>
     </row>
     <row r="1211">
       <c r="B1211" s="5" t="s">
-        <v>7476</v>
+        <v>7484</v>
       </c>
       <c r="C1211" s="5" t="s">
-        <v>7477</v>
+        <v>4775</v>
       </c>
       <c r="D1211" s="5" t="s">
-        <v>7478</v>
+        <v>7485</v>
       </c>
       <c r="E1211" s="5" t="s">
-        <v>7451</v>
+        <v>4777</v>
       </c>
       <c r="F1211" s="5" t="s">
-        <v>7479</v>
+        <v>4778</v>
       </c>
       <c r="G1211" s="5" t="s">
-        <v>7480</v>
+        <v>4778</v>
       </c>
       <c r="H1211" s="5" t="s">
-        <v>7481</v>
+        <v>7486</v>
       </c>
     </row>
     <row r="1212">
       <c r="B1212" s="6" t="s">
-        <v>7482</v>
+        <v>7487</v>
       </c>
       <c r="C1212" s="6" t="s">
-        <v>5100</v>
+        <v>5289</v>
       </c>
       <c r="D1212" s="6" t="s">
-        <v>4530</v>
+        <v>7488</v>
       </c>
       <c r="E1212" s="6" t="s">
-        <v>7483</v>
+        <v>5291</v>
       </c>
       <c r="F1212" s="6" t="s">
-        <v>7484</v>
+        <v>5292</v>
       </c>
       <c r="G1212" s="6" t="s">
-        <v>7485</v>
+        <v>5292</v>
       </c>
       <c r="H1212" s="6" t="s">
-        <v>7486</v>
+        <v>7489</v>
       </c>
     </row>
     <row r="1213">
       <c r="B1213" s="5" t="s">
-        <v>7487</v>
+        <v>7490</v>
       </c>
       <c r="C1213" s="5" t="s">
-        <v>7488</v>
+        <v>7491</v>
       </c>
       <c r="D1213" s="5" t="s">
-        <v>7489</v>
+        <v>7492</v>
       </c>
       <c r="E1213" s="5" t="s">
-        <v>7490</v>
+        <v>7465</v>
       </c>
       <c r="F1213" s="5" t="s">
-        <v>7491</v>
+        <v>7493</v>
       </c>
       <c r="G1213" s="5" t="s">
-        <v>7492</v>
+        <v>7494</v>
       </c>
       <c r="H1213" s="5" t="s">
-        <v>7493</v>
+        <v>7495</v>
       </c>
     </row>
     <row r="1214">
       <c r="B1214" s="6" t="s">
-        <v>7494</v>
+        <v>7496</v>
       </c>
       <c r="C1214" s="6" t="s">
-        <v>7495</v>
+        <v>5100</v>
       </c>
       <c r="D1214" s="6" t="s">
-        <v>7496</v>
+        <v>4530</v>
       </c>
       <c r="E1214" s="6" t="s">
         <v>7497</v>
@@ -51759,73 +51801,73 @@
         <v>7540</v>
       </c>
       <c r="G1220" s="6" t="s">
-        <v>7540</v>
+        <v>7541</v>
       </c>
       <c r="H1220" s="6" t="s">
-        <v>7541</v>
+        <v>7542</v>
       </c>
     </row>
     <row r="1221">
       <c r="B1221" s="5" t="s">
-        <v>7542</v>
+        <v>7543</v>
       </c>
       <c r="C1221" s="5" t="s">
-        <v>7543</v>
+        <v>7544</v>
       </c>
       <c r="D1221" s="5" t="s">
-        <v>7544</v>
+        <v>7545</v>
       </c>
       <c r="E1221" s="5" t="s">
-        <v>7545</v>
+        <v>7546</v>
       </c>
       <c r="F1221" s="5" t="s">
-        <v>7546</v>
+        <v>7547</v>
       </c>
       <c r="G1221" s="5" t="s">
-        <v>7546</v>
+        <v>7548</v>
       </c>
       <c r="H1221" s="5" t="s">
-        <v>7547</v>
+        <v>7549</v>
       </c>
     </row>
     <row r="1222">
       <c r="B1222" s="6" t="s">
-        <v>7548</v>
+        <v>7550</v>
       </c>
       <c r="C1222" s="6" t="s">
-        <v>7549</v>
+        <v>7551</v>
       </c>
       <c r="D1222" s="6" t="s">
-        <v>7550</v>
+        <v>7552</v>
       </c>
       <c r="E1222" s="6" t="s">
-        <v>7551</v>
+        <v>7553</v>
       </c>
       <c r="F1222" s="6" t="s">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="G1222" s="6" t="s">
-        <v>7553</v>
+        <v>7554</v>
       </c>
       <c r="H1222" s="6" t="s">
-        <v>7554</v>
+        <v>7555</v>
       </c>
     </row>
     <row r="1223">
       <c r="B1223" s="5" t="s">
-        <v>7555</v>
+        <v>7556</v>
       </c>
       <c r="C1223" s="5" t="s">
-        <v>7556</v>
+        <v>7557</v>
       </c>
       <c r="D1223" s="5" t="s">
-        <v>7557</v>
+        <v>7558</v>
       </c>
       <c r="E1223" s="5" t="s">
-        <v>7558</v>
+        <v>7559</v>
       </c>
       <c r="F1223" s="5" t="s">
-        <v>7559</v>
+        <v>7560</v>
       </c>
       <c r="G1223" s="5" t="s">
         <v>7560</v>
@@ -51911,111 +51953,111 @@
         <v>7584</v>
       </c>
       <c r="D1227" s="5" t="s">
-        <v>6551</v>
+        <v>7585</v>
       </c>
       <c r="E1227" s="5" t="s">
-        <v>7585</v>
+        <v>7586</v>
       </c>
       <c r="F1227" s="5" t="s">
-        <v>5701</v>
+        <v>7587</v>
       </c>
       <c r="G1227" s="5" t="s">
-        <v>5702</v>
+        <v>7588</v>
       </c>
       <c r="H1227" s="5" t="s">
-        <v>7586</v>
+        <v>7589</v>
       </c>
     </row>
     <row r="1228">
       <c r="B1228" s="6" t="s">
-        <v>7587</v>
+        <v>7590</v>
       </c>
       <c r="C1228" s="6" t="s">
-        <v>7588</v>
+        <v>7591</v>
       </c>
       <c r="D1228" s="6" t="s">
-        <v>6556</v>
+        <v>7592</v>
       </c>
       <c r="E1228" s="6" t="s">
-        <v>5135</v>
+        <v>7593</v>
       </c>
       <c r="F1228" s="6" t="s">
-        <v>6558</v>
+        <v>7594</v>
       </c>
       <c r="G1228" s="6" t="s">
-        <v>6559</v>
+        <v>7595</v>
       </c>
       <c r="H1228" s="6" t="s">
-        <v>6560</v>
+        <v>7596</v>
       </c>
     </row>
     <row r="1229">
       <c r="B1229" s="5" t="s">
-        <v>7589</v>
+        <v>7597</v>
       </c>
       <c r="C1229" s="5" t="s">
-        <v>4679</v>
+        <v>7598</v>
       </c>
       <c r="D1229" s="5" t="s">
-        <v>4680</v>
+        <v>6565</v>
       </c>
       <c r="E1229" s="5" t="s">
-        <v>7590</v>
+        <v>7599</v>
       </c>
       <c r="F1229" s="5" t="s">
-        <v>7591</v>
+        <v>5715</v>
       </c>
       <c r="G1229" s="5" t="s">
-        <v>7592</v>
+        <v>5716</v>
       </c>
       <c r="H1229" s="5" t="s">
-        <v>4684</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="1230">
       <c r="B1230" s="6" t="s">
-        <v>7593</v>
+        <v>7601</v>
       </c>
       <c r="C1230" s="6" t="s">
-        <v>7594</v>
+        <v>7602</v>
       </c>
       <c r="D1230" s="6" t="s">
-        <v>7595</v>
+        <v>6570</v>
       </c>
       <c r="E1230" s="6" t="s">
-        <v>7596</v>
+        <v>5135</v>
       </c>
       <c r="F1230" s="6" t="s">
-        <v>7597</v>
+        <v>6572</v>
       </c>
       <c r="G1230" s="6" t="s">
-        <v>7598</v>
+        <v>6573</v>
       </c>
       <c r="H1230" s="6" t="s">
-        <v>7599</v>
+        <v>6574</v>
       </c>
     </row>
     <row r="1231">
       <c r="B1231" s="5" t="s">
-        <v>7600</v>
+        <v>7603</v>
       </c>
       <c r="C1231" s="5" t="s">
-        <v>7601</v>
+        <v>4679</v>
       </c>
       <c r="D1231" s="5" t="s">
-        <v>7602</v>
+        <v>4680</v>
       </c>
       <c r="E1231" s="5" t="s">
-        <v>7603</v>
+        <v>7604</v>
       </c>
       <c r="F1231" s="5" t="s">
-        <v>7604</v>
+        <v>7605</v>
       </c>
       <c r="G1231" s="5" t="s">
-        <v>7605</v>
+        <v>7606</v>
       </c>
       <c r="H1231" s="5" t="s">
-        <v>7606</v>
+        <v>4684</v>
       </c>
     </row>
     <row r="1232">
@@ -52035,61 +52077,61 @@
         <v>7611</v>
       </c>
       <c r="G1232" s="6" t="s">
-        <v>7611</v>
+        <v>7612</v>
       </c>
       <c r="H1232" s="6" t="s">
-        <v>7612</v>
+        <v>7613</v>
       </c>
     </row>
     <row r="1233">
       <c r="B1233" s="5" t="s">
-        <v>7613</v>
+        <v>7614</v>
       </c>
       <c r="C1233" s="5" t="s">
-        <v>7608</v>
+        <v>7615</v>
       </c>
       <c r="D1233" s="5" t="s">
-        <v>7609</v>
+        <v>7616</v>
       </c>
       <c r="E1233" s="5" t="s">
-        <v>7610</v>
+        <v>7617</v>
       </c>
       <c r="F1233" s="5" t="s">
-        <v>7611</v>
+        <v>7618</v>
       </c>
       <c r="G1233" s="5" t="s">
-        <v>7611</v>
+        <v>7619</v>
       </c>
       <c r="H1233" s="5" t="s">
-        <v>7612</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="1234">
       <c r="B1234" s="6" t="s">
-        <v>7614</v>
+        <v>7621</v>
       </c>
       <c r="C1234" s="6" t="s">
-        <v>7615</v>
+        <v>7622</v>
       </c>
       <c r="D1234" s="6" t="s">
-        <v>7616</v>
+        <v>7623</v>
       </c>
       <c r="E1234" s="6" t="s">
-        <v>7617</v>
+        <v>7624</v>
       </c>
       <c r="F1234" s="6" t="s">
-        <v>7618</v>
+        <v>7625</v>
       </c>
       <c r="G1234" s="6" t="s">
-        <v>7619</v>
+        <v>7625</v>
       </c>
       <c r="H1234" s="6" t="s">
-        <v>7620</v>
+        <v>7626</v>
       </c>
     </row>
     <row r="1235">
       <c r="B1235" s="5" t="s">
-        <v>7621</v>
+        <v>7627</v>
       </c>
       <c r="C1235" s="5" t="s">
         <v>7622</v>
@@ -52104,10 +52146,10 @@
         <v>7625</v>
       </c>
       <c r="G1235" s="5" t="s">
+        <v>7625</v>
+      </c>
+      <c r="H1235" s="5" t="s">
         <v>7626</v>
-      </c>
-      <c r="H1235" s="5" t="s">
-        <v>7627</v>
       </c>
     </row>
     <row r="1236">
@@ -52127,217 +52169,217 @@
         <v>7632</v>
       </c>
       <c r="G1236" s="6" t="s">
-        <v>7632</v>
+        <v>7633</v>
       </c>
       <c r="H1236" s="6" t="s">
-        <v>7633</v>
+        <v>7634</v>
       </c>
     </row>
     <row r="1237">
       <c r="B1237" s="5" t="s">
-        <v>7634</v>
+        <v>7635</v>
       </c>
       <c r="C1237" s="5" t="s">
-        <v>3751</v>
+        <v>7636</v>
       </c>
       <c r="D1237" s="5" t="s">
-        <v>3123</v>
+        <v>7637</v>
       </c>
       <c r="E1237" s="5" t="s">
-        <v>3753</v>
+        <v>7638</v>
       </c>
       <c r="F1237" s="5" t="s">
-        <v>5942</v>
+        <v>7639</v>
       </c>
       <c r="G1237" s="5" t="s">
-        <v>5942</v>
+        <v>7640</v>
       </c>
       <c r="H1237" s="5" t="s">
-        <v>3123</v>
+        <v>7641</v>
       </c>
     </row>
     <row r="1238">
       <c r="B1238" s="6" t="s">
-        <v>7635</v>
+        <v>7642</v>
       </c>
       <c r="C1238" s="6" t="s">
-        <v>3805</v>
+        <v>7643</v>
       </c>
       <c r="D1238" s="6" t="s">
-        <v>7636</v>
+        <v>7644</v>
       </c>
       <c r="E1238" s="6" t="s">
-        <v>3807</v>
+        <v>7645</v>
       </c>
       <c r="F1238" s="6" t="s">
-        <v>3808</v>
+        <v>7646</v>
       </c>
       <c r="G1238" s="6" t="s">
-        <v>3807</v>
+        <v>7646</v>
       </c>
       <c r="H1238" s="6" t="s">
-        <v>3809</v>
+        <v>7647</v>
       </c>
     </row>
     <row r="1239">
       <c r="B1239" s="5" t="s">
-        <v>7637</v>
+        <v>7648</v>
       </c>
       <c r="C1239" s="5" t="s">
-        <v>3811</v>
+        <v>3751</v>
       </c>
       <c r="D1239" s="5" t="s">
-        <v>7638</v>
+        <v>3123</v>
       </c>
       <c r="E1239" s="5" t="s">
-        <v>3813</v>
+        <v>3753</v>
       </c>
       <c r="F1239" s="5" t="s">
-        <v>7639</v>
+        <v>5956</v>
       </c>
       <c r="G1239" s="5" t="s">
-        <v>7640</v>
+        <v>5956</v>
       </c>
       <c r="H1239" s="5" t="s">
-        <v>3816</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="1240">
       <c r="B1240" s="6" t="s">
-        <v>7641</v>
+        <v>7649</v>
       </c>
       <c r="C1240" s="6" t="s">
-        <v>3818</v>
+        <v>3805</v>
       </c>
       <c r="D1240" s="6" t="s">
-        <v>3822</v>
+        <v>7650</v>
       </c>
       <c r="E1240" s="6" t="s">
-        <v>3820</v>
+        <v>3807</v>
       </c>
       <c r="F1240" s="6" t="s">
-        <v>3821</v>
+        <v>3808</v>
       </c>
       <c r="G1240" s="6" t="s">
-        <v>3821</v>
+        <v>3807</v>
       </c>
       <c r="H1240" s="6" t="s">
-        <v>3822</v>
+        <v>3809</v>
       </c>
     </row>
     <row r="1241">
       <c r="B1241" s="5" t="s">
-        <v>7642</v>
+        <v>7651</v>
       </c>
       <c r="C1241" s="5" t="s">
-        <v>4619</v>
+        <v>3811</v>
       </c>
       <c r="D1241" s="5" t="s">
-        <v>4804</v>
+        <v>7652</v>
       </c>
       <c r="E1241" s="5" t="s">
-        <v>4621</v>
+        <v>3813</v>
       </c>
       <c r="F1241" s="5" t="s">
-        <v>4622</v>
+        <v>7653</v>
       </c>
       <c r="G1241" s="5" t="s">
-        <v>4622</v>
+        <v>7654</v>
       </c>
       <c r="H1241" s="5" t="s">
-        <v>4804</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="1242">
       <c r="B1242" s="6" t="s">
-        <v>7643</v>
+        <v>7655</v>
       </c>
       <c r="C1242" s="6" t="s">
-        <v>5239</v>
+        <v>3818</v>
       </c>
       <c r="D1242" s="6" t="s">
-        <v>5240</v>
+        <v>3822</v>
       </c>
       <c r="E1242" s="6" t="s">
-        <v>5241</v>
+        <v>3820</v>
       </c>
       <c r="F1242" s="6" t="s">
-        <v>5240</v>
+        <v>3821</v>
       </c>
       <c r="G1242" s="6" t="s">
-        <v>5240</v>
+        <v>3821</v>
       </c>
       <c r="H1242" s="6" t="s">
-        <v>5240</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="1243">
       <c r="B1243" s="5" t="s">
-        <v>7644</v>
+        <v>7656</v>
       </c>
       <c r="C1243" s="5" t="s">
-        <v>4624</v>
+        <v>4619</v>
       </c>
       <c r="D1243" s="5" t="s">
-        <v>6861</v>
+        <v>4804</v>
       </c>
       <c r="E1243" s="5" t="s">
-        <v>4626</v>
+        <v>4621</v>
       </c>
       <c r="F1243" s="5" t="s">
-        <v>4251</v>
+        <v>4622</v>
       </c>
       <c r="G1243" s="5" t="s">
-        <v>4251</v>
+        <v>4622</v>
       </c>
       <c r="H1243" s="5" t="s">
-        <v>6862</v>
+        <v>4804</v>
       </c>
     </row>
     <row r="1244">
       <c r="B1244" s="6" t="s">
-        <v>7645</v>
+        <v>7657</v>
       </c>
       <c r="C1244" s="6" t="s">
-        <v>7646</v>
+        <v>5239</v>
       </c>
       <c r="D1244" s="6" t="s">
-        <v>7647</v>
+        <v>5240</v>
       </c>
       <c r="E1244" s="6" t="s">
-        <v>7648</v>
+        <v>5241</v>
       </c>
       <c r="F1244" s="6" t="s">
-        <v>7649</v>
+        <v>5240</v>
       </c>
       <c r="G1244" s="6" t="s">
-        <v>7650</v>
+        <v>5240</v>
       </c>
       <c r="H1244" s="6" t="s">
-        <v>7651</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="1245">
       <c r="B1245" s="5" t="s">
-        <v>7652</v>
+        <v>7658</v>
       </c>
       <c r="C1245" s="5" t="s">
-        <v>7653</v>
+        <v>4624</v>
       </c>
       <c r="D1245" s="5" t="s">
-        <v>7654</v>
+        <v>6875</v>
       </c>
       <c r="E1245" s="5" t="s">
-        <v>7655</v>
+        <v>4626</v>
       </c>
       <c r="F1245" s="5" t="s">
-        <v>7656</v>
+        <v>4251</v>
       </c>
       <c r="G1245" s="5" t="s">
-        <v>7657</v>
+        <v>4251</v>
       </c>
       <c r="H1245" s="5" t="s">
-        <v>7658</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="1246">
@@ -52426,50 +52468,50 @@
         <v>7684</v>
       </c>
       <c r="G1249" s="5" t="s">
-        <v>7684</v>
+        <v>7685</v>
       </c>
       <c r="H1249" s="5" t="s">
-        <v>7685</v>
+        <v>7686</v>
       </c>
     </row>
     <row r="1250">
       <c r="B1250" s="6" t="s">
-        <v>7686</v>
+        <v>7687</v>
       </c>
       <c r="C1250" s="6" t="s">
-        <v>7687</v>
+        <v>7688</v>
       </c>
       <c r="D1250" s="6" t="s">
-        <v>7688</v>
+        <v>7689</v>
       </c>
       <c r="E1250" s="6" t="s">
-        <v>7689</v>
+        <v>7690</v>
       </c>
       <c r="F1250" s="6" t="s">
-        <v>7690</v>
+        <v>7691</v>
       </c>
       <c r="G1250" s="6" t="s">
-        <v>7691</v>
+        <v>7692</v>
       </c>
       <c r="H1250" s="6" t="s">
-        <v>7692</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="1251">
       <c r="B1251" s="5" t="s">
-        <v>7693</v>
+        <v>7694</v>
       </c>
       <c r="C1251" s="5" t="s">
-        <v>7694</v>
+        <v>7695</v>
       </c>
       <c r="D1251" s="5" t="s">
-        <v>7695</v>
+        <v>7696</v>
       </c>
       <c r="E1251" s="5" t="s">
-        <v>7696</v>
+        <v>7697</v>
       </c>
       <c r="F1251" s="5" t="s">
-        <v>7697</v>
+        <v>7698</v>
       </c>
       <c r="G1251" s="5" t="s">
         <v>7698</v>
@@ -52578,65 +52620,65 @@
         <v>7729</v>
       </c>
       <c r="D1256" s="6" t="s">
-        <v>7450</v>
+        <v>7730</v>
       </c>
       <c r="E1256" s="6" t="s">
-        <v>7730</v>
+        <v>7731</v>
       </c>
       <c r="F1256" s="6" t="s">
-        <v>7452</v>
+        <v>7732</v>
       </c>
       <c r="G1256" s="6" t="s">
-        <v>7453</v>
+        <v>7733</v>
       </c>
       <c r="H1256" s="6" t="s">
-        <v>7454</v>
+        <v>7734</v>
       </c>
     </row>
     <row r="1257">
       <c r="B1257" s="5" t="s">
-        <v>7731</v>
+        <v>7735</v>
       </c>
       <c r="C1257" s="5" t="s">
-        <v>7732</v>
+        <v>7736</v>
       </c>
       <c r="D1257" s="5" t="s">
-        <v>7733</v>
+        <v>7737</v>
       </c>
       <c r="E1257" s="5" t="s">
-        <v>7734</v>
+        <v>7738</v>
       </c>
       <c r="F1257" s="5" t="s">
-        <v>7735</v>
+        <v>7739</v>
       </c>
       <c r="G1257" s="5" t="s">
-        <v>7736</v>
+        <v>7740</v>
       </c>
       <c r="H1257" s="5" t="s">
-        <v>7737</v>
+        <v>7741</v>
       </c>
     </row>
     <row r="1258">
       <c r="B1258" s="6" t="s">
-        <v>7738</v>
+        <v>7742</v>
       </c>
       <c r="C1258" s="6" t="s">
-        <v>7739</v>
+        <v>7743</v>
       </c>
       <c r="D1258" s="6" t="s">
-        <v>7740</v>
+        <v>7464</v>
       </c>
       <c r="E1258" s="6" t="s">
-        <v>7741</v>
+        <v>7744</v>
       </c>
       <c r="F1258" s="6" t="s">
-        <v>7742</v>
+        <v>7466</v>
       </c>
       <c r="G1258" s="6" t="s">
-        <v>7743</v>
+        <v>7467</v>
       </c>
       <c r="H1258" s="6" t="s">
-        <v>7744</v>
+        <v>7468</v>
       </c>
     </row>
     <row r="1259">
@@ -52644,68 +52686,68 @@
         <v>7745</v>
       </c>
       <c r="C1259" s="5" t="s">
-        <v>4679</v>
+        <v>7746</v>
       </c>
       <c r="D1259" s="5" t="s">
-        <v>4680</v>
+        <v>7747</v>
       </c>
       <c r="E1259" s="5" t="s">
-        <v>4681</v>
+        <v>7748</v>
       </c>
       <c r="F1259" s="5" t="s">
-        <v>7746</v>
+        <v>7749</v>
       </c>
       <c r="G1259" s="5" t="s">
-        <v>7747</v>
+        <v>7750</v>
       </c>
       <c r="H1259" s="5" t="s">
-        <v>4684</v>
+        <v>7751</v>
       </c>
     </row>
     <row r="1260">
       <c r="B1260" s="6" t="s">
-        <v>7748</v>
+        <v>7752</v>
       </c>
       <c r="C1260" s="6" t="s">
-        <v>7749</v>
+        <v>7753</v>
       </c>
       <c r="D1260" s="6" t="s">
-        <v>7750</v>
+        <v>7754</v>
       </c>
       <c r="E1260" s="6" t="s">
-        <v>7751</v>
+        <v>7755</v>
       </c>
       <c r="F1260" s="6" t="s">
-        <v>7752</v>
+        <v>7756</v>
       </c>
       <c r="G1260" s="6" t="s">
-        <v>7753</v>
+        <v>7757</v>
       </c>
       <c r="H1260" s="6" t="s">
-        <v>7754</v>
+        <v>7758</v>
       </c>
     </row>
     <row r="1261">
       <c r="B1261" s="5" t="s">
-        <v>7755</v>
+        <v>7759</v>
       </c>
       <c r="C1261" s="5" t="s">
-        <v>7756</v>
+        <v>4679</v>
       </c>
       <c r="D1261" s="5" t="s">
-        <v>7757</v>
+        <v>4680</v>
       </c>
       <c r="E1261" s="5" t="s">
-        <v>7758</v>
+        <v>4681</v>
       </c>
       <c r="F1261" s="5" t="s">
-        <v>7759</v>
+        <v>7760</v>
       </c>
       <c r="G1261" s="5" t="s">
-        <v>7760</v>
+        <v>7761</v>
       </c>
       <c r="H1261" s="5" t="s">
-        <v>7761</v>
+        <v>4684</v>
       </c>
     </row>
     <row r="1262">
@@ -52782,49 +52824,95 @@
         <v>7783</v>
       </c>
       <c r="C1265" s="5" t="s">
-        <v>4798</v>
+        <v>7784</v>
       </c>
       <c r="D1265" s="5" t="s">
-        <v>4799</v>
+        <v>7785</v>
       </c>
       <c r="E1265" s="5" t="s">
-        <v>4800</v>
+        <v>7786</v>
       </c>
       <c r="F1265" s="5" t="s">
-        <v>4801</v>
+        <v>7787</v>
       </c>
       <c r="G1265" s="5" t="s">
-        <v>4801</v>
+        <v>7788</v>
       </c>
       <c r="H1265" s="5" t="s">
-        <v>4802</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="1266">
       <c r="B1266" s="6" t="s">
-        <v>7784</v>
+        <v>7790</v>
       </c>
       <c r="C1266" s="6" t="s">
+        <v>7791</v>
+      </c>
+      <c r="D1266" s="6" t="s">
+        <v>7792</v>
+      </c>
+      <c r="E1266" s="6" t="s">
+        <v>7793</v>
+      </c>
+      <c r="F1266" s="6" t="s">
+        <v>7794</v>
+      </c>
+      <c r="G1266" s="6" t="s">
+        <v>7795</v>
+      </c>
+      <c r="H1266" s="6" t="s">
+        <v>7796</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="B1267" s="5" t="s">
+        <v>7797</v>
+      </c>
+      <c r="C1267" s="5" t="s">
+        <v>4798</v>
+      </c>
+      <c r="D1267" s="5" t="s">
+        <v>4799</v>
+      </c>
+      <c r="E1267" s="5" t="s">
+        <v>4800</v>
+      </c>
+      <c r="F1267" s="5" t="s">
+        <v>4801</v>
+      </c>
+      <c r="G1267" s="5" t="s">
+        <v>4801</v>
+      </c>
+      <c r="H1267" s="5" t="s">
+        <v>4802</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="B1268" s="6" t="s">
+        <v>7798</v>
+      </c>
+      <c r="C1268" s="6" t="s">
         <v>2178</v>
       </c>
-      <c r="D1266" s="6" t="s">
+      <c r="D1268" s="6" t="s">
         <v>2179</v>
       </c>
-      <c r="E1266" s="6" t="s">
+      <c r="E1268" s="6" t="s">
         <v>2180</v>
       </c>
-      <c r="F1266" s="6" t="s">
+      <c r="F1268" s="6" t="s">
         <v>2181</v>
       </c>
-      <c r="G1266" s="6" t="s">
+      <c r="G1268" s="6" t="s">
         <v>2182</v>
       </c>
-      <c r="H1266" s="6" t="s">
+      <c r="H1268" s="6" t="s">
         <v>2183</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H1266"/>
+  <autoFilter ref="B2:H1268"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -52843,10 +52931,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>7785</v>
+        <v>7799</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7786</v>
+        <v>7800</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -52857,16 +52945,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7787</v>
+        <v>7801</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7788</v>
+        <v>7802</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7789</v>
+        <v>7803</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>7790</v>
+        <v>7804</v>
       </c>
     </row>
     <row r="3">
@@ -52874,16 +52962,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7791</v>
+        <v>7805</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>7792</v>
+        <v>7806</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>7793</v>
+        <v>7807</v>
       </c>
     </row>
     <row r="4">
@@ -52894,24 +52982,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>7794</v>
+        <v>7808</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>7795</v>
+        <v>7809</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>7796</v>
+        <v>7810</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>7797</v>
+        <v>7811</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2287</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>7798</v>
+        <v>7812</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -52919,13 +53007,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>7799</v>
+        <v>7813</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2294</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>7800</v>
+        <v>7814</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -52933,13 +53021,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>7801</v>
+        <v>7815</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2300</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>7802</v>
+        <v>7816</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -52947,13 +53035,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>7803</v>
+        <v>7817</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2306</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>7804</v>
+        <v>7818</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -52961,13 +53049,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>7805</v>
+        <v>7819</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2313</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>7806</v>
+        <v>7820</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -52975,13 +53063,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>7807</v>
+        <v>7821</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2320</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>7808</v>
+        <v>7822</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -52989,13 +53077,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>7809</v>
+        <v>7823</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2326</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>7810</v>
+        <v>7824</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -53003,13 +53091,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>7811</v>
+        <v>7825</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2332</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>7812</v>
+        <v>7826</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -53017,13 +53105,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>7813</v>
+        <v>7827</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2339</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>7814</v>
+        <v>7828</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -53031,13 +53119,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>7815</v>
+        <v>7829</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2345</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>7816</v>
+        <v>7830</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -53051,7 +53139,7 @@
         <v>2352</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>7817</v>
+        <v>7831</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -53059,13 +53147,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>7818</v>
+        <v>7832</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2359</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>7819</v>
+        <v>7833</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -53073,13 +53161,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>7820</v>
+        <v>7834</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2366</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>7821</v>
+        <v>7835</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -53087,13 +53175,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>7822</v>
+        <v>7836</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2372</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>7823</v>
+        <v>7837</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -53101,13 +53189,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>7824</v>
+        <v>7838</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2379</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>7825</v>
+        <v>7839</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -53115,13 +53203,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>7826</v>
+        <v>7840</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2385</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>7827</v>
+        <v>7841</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -53129,13 +53217,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>7828</v>
+        <v>7842</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2390</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>7829</v>
+        <v>7843</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -53143,13 +53231,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>7830</v>
+        <v>7844</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2397</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>7831</v>
+        <v>7845</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -53157,13 +53245,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>7832</v>
+        <v>7846</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2222</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>7833</v>
+        <v>7847</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -53171,13 +53259,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>7834</v>
+        <v>7848</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2405</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>7835</v>
+        <v>7849</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1268]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1270]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8939" uniqueCount="7850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8953" uniqueCount="7864">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -15532,6 +15532,27 @@
     <t xml:space="preserve">Ausgelöst</t>
   </si>
   <si>
+    <t xml:space="preserve">ui.label.missed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">불발</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不発</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未触发</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未觸發</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fehlschlag</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.act.make</t>
   </si>
   <si>
@@ -22985,6 +23006,27 @@
   </si>
   <si>
     <t xml:space="preserve">ui.kind.edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.kind.counter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">누적값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計値</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累计值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zähler</t>
   </si>
   <si>
     <t xml:space="preserve">ui.kind.blind</t>
@@ -23766,7 +23808,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -23775,7 +23817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1268"/>
+  <dimension ref="A1:H1270"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -42532,27 +42574,27 @@
         <v>5175</v>
       </c>
       <c r="G817" s="5" t="s">
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="H817" s="5" t="s">
-        <v>5176</v>
+        <v>5177</v>
       </c>
     </row>
     <row r="818">
       <c r="B818" s="6" t="s">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="C818" s="6" t="s">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="D818" s="6" t="s">
-        <v>5179</v>
+        <v>5180</v>
       </c>
       <c r="E818" s="6" t="s">
-        <v>5180</v>
+        <v>5181</v>
       </c>
       <c r="F818" s="6" t="s">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="G818" s="6" t="s">
         <v>5182</v>
@@ -42624,332 +42666,332 @@
         <v>5202</v>
       </c>
       <c r="G821" s="5" t="s">
-        <v>5202</v>
+        <v>5203</v>
       </c>
       <c r="H821" s="5" t="s">
-        <v>5203</v>
+        <v>5204</v>
       </c>
     </row>
     <row r="822">
       <c r="B822" s="6" t="s">
-        <v>5204</v>
+        <v>5205</v>
       </c>
       <c r="C822" s="6" t="s">
-        <v>5205</v>
+        <v>5206</v>
       </c>
       <c r="D822" s="6" t="s">
-        <v>5206</v>
+        <v>5207</v>
       </c>
       <c r="E822" s="6" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="F822" s="6" t="s">
-        <v>5207</v>
+        <v>5209</v>
       </c>
       <c r="G822" s="6" t="s">
-        <v>5207</v>
+        <v>5209</v>
       </c>
       <c r="H822" s="6" t="s">
-        <v>5208</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="823">
       <c r="B823" s="5" t="s">
-        <v>5209</v>
+        <v>5211</v>
       </c>
       <c r="C823" s="5" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
       <c r="D823" s="5" t="s">
-        <v>5211</v>
+        <v>5213</v>
       </c>
       <c r="E823" s="5" t="s">
-        <v>5212</v>
+        <v>5214</v>
       </c>
       <c r="F823" s="5" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="G823" s="5" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="H823" s="5" t="s">
-        <v>5214</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="824">
       <c r="B824" s="6" t="s">
-        <v>5215</v>
+        <v>5216</v>
       </c>
       <c r="C824" s="6" t="s">
-        <v>5216</v>
+        <v>5217</v>
       </c>
       <c r="D824" s="6" t="s">
-        <v>5217</v>
+        <v>5218</v>
       </c>
       <c r="E824" s="6" t="s">
-        <v>5218</v>
+        <v>5219</v>
       </c>
       <c r="F824" s="6" t="s">
-        <v>4602</v>
+        <v>5220</v>
       </c>
       <c r="G824" s="6" t="s">
-        <v>4603</v>
+        <v>5220</v>
       </c>
       <c r="H824" s="6" t="s">
-        <v>5219</v>
+        <v>5221</v>
       </c>
     </row>
     <row r="825">
       <c r="B825" s="5" t="s">
-        <v>5220</v>
+        <v>5222</v>
       </c>
       <c r="C825" s="5" t="s">
-        <v>5221</v>
+        <v>5223</v>
       </c>
       <c r="D825" s="5" t="s">
-        <v>5222</v>
+        <v>5224</v>
       </c>
       <c r="E825" s="5" t="s">
-        <v>5223</v>
+        <v>5225</v>
       </c>
       <c r="F825" s="5" t="s">
-        <v>5224</v>
+        <v>4602</v>
       </c>
       <c r="G825" s="5" t="s">
-        <v>5224</v>
+        <v>4603</v>
       </c>
       <c r="H825" s="5" t="s">
-        <v>5225</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="826">
       <c r="B826" s="6" t="s">
-        <v>5226</v>
+        <v>5227</v>
       </c>
       <c r="C826" s="6" t="s">
-        <v>5227</v>
+        <v>5228</v>
       </c>
       <c r="D826" s="6" t="s">
-        <v>5228</v>
+        <v>5229</v>
       </c>
       <c r="E826" s="6" t="s">
-        <v>5229</v>
+        <v>5230</v>
       </c>
       <c r="F826" s="6" t="s">
-        <v>5230</v>
+        <v>5231</v>
       </c>
       <c r="G826" s="6" t="s">
-        <v>5230</v>
+        <v>5231</v>
       </c>
       <c r="H826" s="6" t="s">
-        <v>5231</v>
+        <v>5232</v>
       </c>
     </row>
     <row r="827">
       <c r="B827" s="5" t="s">
-        <v>5232</v>
+        <v>5233</v>
       </c>
       <c r="C827" s="5" t="s">
-        <v>5233</v>
+        <v>5234</v>
       </c>
       <c r="D827" s="5" t="s">
-        <v>5234</v>
+        <v>5235</v>
       </c>
       <c r="E827" s="5" t="s">
-        <v>5235</v>
+        <v>5236</v>
       </c>
       <c r="F827" s="5" t="s">
-        <v>5236</v>
+        <v>5237</v>
       </c>
       <c r="G827" s="5" t="s">
-        <v>5236</v>
+        <v>5237</v>
       </c>
       <c r="H827" s="5" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
     </row>
     <row r="828">
       <c r="B828" s="6" t="s">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="C828" s="6" t="s">
-        <v>5239</v>
+        <v>5240</v>
       </c>
       <c r="D828" s="6" t="s">
-        <v>5240</v>
+        <v>5241</v>
       </c>
       <c r="E828" s="6" t="s">
-        <v>5241</v>
+        <v>5242</v>
       </c>
       <c r="F828" s="6" t="s">
-        <v>5240</v>
+        <v>5243</v>
       </c>
       <c r="G828" s="6" t="s">
-        <v>5240</v>
+        <v>5243</v>
       </c>
       <c r="H828" s="6" t="s">
-        <v>5240</v>
+        <v>5244</v>
       </c>
     </row>
     <row r="829">
       <c r="B829" s="5" t="s">
-        <v>5242</v>
+        <v>5245</v>
       </c>
       <c r="C829" s="5" t="s">
-        <v>3751</v>
+        <v>5246</v>
       </c>
       <c r="D829" s="5" t="s">
-        <v>3123</v>
+        <v>5247</v>
       </c>
       <c r="E829" s="5" t="s">
-        <v>3753</v>
+        <v>5248</v>
       </c>
       <c r="F829" s="5" t="s">
-        <v>3754</v>
+        <v>5247</v>
       </c>
       <c r="G829" s="5" t="s">
-        <v>3754</v>
+        <v>5247</v>
       </c>
       <c r="H829" s="5" t="s">
-        <v>3123</v>
+        <v>5247</v>
       </c>
     </row>
     <row r="830">
       <c r="B830" s="6" t="s">
-        <v>5243</v>
+        <v>5249</v>
       </c>
       <c r="C830" s="6" t="s">
-        <v>4798</v>
+        <v>3751</v>
       </c>
       <c r="D830" s="6" t="s">
-        <v>5244</v>
+        <v>3123</v>
       </c>
       <c r="E830" s="6" t="s">
-        <v>4801</v>
+        <v>3753</v>
       </c>
       <c r="F830" s="6" t="s">
-        <v>4801</v>
+        <v>3754</v>
       </c>
       <c r="G830" s="6" t="s">
-        <v>4801</v>
+        <v>3754</v>
       </c>
       <c r="H830" s="6" t="s">
-        <v>5245</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="831">
       <c r="B831" s="5" t="s">
-        <v>5246</v>
+        <v>5250</v>
       </c>
       <c r="C831" s="5" t="s">
-        <v>3798</v>
+        <v>4798</v>
       </c>
       <c r="D831" s="5" t="s">
-        <v>5247</v>
+        <v>5251</v>
       </c>
       <c r="E831" s="5" t="s">
-        <v>3800</v>
+        <v>4801</v>
       </c>
       <c r="F831" s="5" t="s">
-        <v>3801</v>
+        <v>4801</v>
       </c>
       <c r="G831" s="5" t="s">
-        <v>3802</v>
+        <v>4801</v>
       </c>
       <c r="H831" s="5" t="s">
-        <v>5248</v>
+        <v>5252</v>
       </c>
     </row>
     <row r="832">
       <c r="B832" s="6" t="s">
-        <v>5249</v>
+        <v>5253</v>
       </c>
       <c r="C832" s="6" t="s">
-        <v>3792</v>
+        <v>3798</v>
       </c>
       <c r="D832" s="6" t="s">
-        <v>5250</v>
+        <v>5254</v>
       </c>
       <c r="E832" s="6" t="s">
-        <v>3794</v>
+        <v>3800</v>
       </c>
       <c r="F832" s="6" t="s">
-        <v>3795</v>
+        <v>3801</v>
       </c>
       <c r="G832" s="6" t="s">
-        <v>3795</v>
+        <v>3802</v>
       </c>
       <c r="H832" s="6" t="s">
-        <v>5251</v>
+        <v>5255</v>
       </c>
     </row>
     <row r="833">
       <c r="B833" s="5" t="s">
-        <v>5252</v>
+        <v>5256</v>
       </c>
       <c r="C833" s="5" t="s">
-        <v>5253</v>
+        <v>3792</v>
       </c>
       <c r="D833" s="5" t="s">
-        <v>5254</v>
+        <v>5257</v>
       </c>
       <c r="E833" s="5" t="s">
-        <v>5255</v>
+        <v>3794</v>
       </c>
       <c r="F833" s="5" t="s">
-        <v>5256</v>
+        <v>3795</v>
       </c>
       <c r="G833" s="5" t="s">
-        <v>5257</v>
+        <v>3795</v>
       </c>
       <c r="H833" s="5" t="s">
-        <v>5254</v>
+        <v>5258</v>
       </c>
     </row>
     <row r="834">
       <c r="B834" s="6" t="s">
-        <v>5258</v>
+        <v>5259</v>
       </c>
       <c r="C834" s="6" t="s">
-        <v>5259</v>
+        <v>5260</v>
       </c>
       <c r="D834" s="6" t="s">
-        <v>5260</v>
+        <v>5261</v>
       </c>
       <c r="E834" s="6" t="s">
+        <v>5262</v>
+      </c>
+      <c r="F834" s="6" t="s">
+        <v>5263</v>
+      </c>
+      <c r="G834" s="6" t="s">
+        <v>5264</v>
+      </c>
+      <c r="H834" s="6" t="s">
         <v>5261</v>
-      </c>
-      <c r="F834" s="6" t="s">
-        <v>5262</v>
-      </c>
-      <c r="G834" s="6" t="s">
-        <v>5262</v>
-      </c>
-      <c r="H834" s="6" t="s">
-        <v>5260</v>
       </c>
     </row>
     <row r="835">
       <c r="B835" s="5" t="s">
-        <v>5263</v>
+        <v>5265</v>
       </c>
       <c r="C835" s="5" t="s">
-        <v>5264</v>
+        <v>5266</v>
       </c>
       <c r="D835" s="5" t="s">
-        <v>5265</v>
+        <v>5267</v>
       </c>
       <c r="E835" s="5" t="s">
-        <v>5266</v>
+        <v>5268</v>
       </c>
       <c r="F835" s="5" t="s">
+        <v>5269</v>
+      </c>
+      <c r="G835" s="5" t="s">
+        <v>5269</v>
+      </c>
+      <c r="H835" s="5" t="s">
         <v>5267</v>
-      </c>
-      <c r="G835" s="5" t="s">
-        <v>5268</v>
-      </c>
-      <c r="H835" s="5" t="s">
-        <v>5269</v>
       </c>
     </row>
     <row r="836">
@@ -42957,505 +42999,505 @@
         <v>5270</v>
       </c>
       <c r="C836" s="6" t="s">
-        <v>3890</v>
+        <v>5271</v>
       </c>
       <c r="D836" s="6" t="s">
-        <v>5271</v>
+        <v>5272</v>
       </c>
       <c r="E836" s="6" t="s">
-        <v>3892</v>
+        <v>5273</v>
       </c>
       <c r="F836" s="6" t="s">
-        <v>3893</v>
+        <v>5274</v>
       </c>
       <c r="G836" s="6" t="s">
-        <v>3893</v>
+        <v>5275</v>
       </c>
       <c r="H836" s="6" t="s">
-        <v>3894</v>
+        <v>5276</v>
       </c>
     </row>
     <row r="837">
       <c r="B837" s="5" t="s">
-        <v>5272</v>
+        <v>5277</v>
       </c>
       <c r="C837" s="5" t="s">
-        <v>4791</v>
+        <v>3890</v>
       </c>
       <c r="D837" s="5" t="s">
-        <v>4568</v>
+        <v>5278</v>
       </c>
       <c r="E837" s="5" t="s">
-        <v>4792</v>
+        <v>3892</v>
       </c>
       <c r="F837" s="5" t="s">
-        <v>4793</v>
+        <v>3893</v>
       </c>
       <c r="G837" s="5" t="s">
-        <v>4794</v>
+        <v>3893</v>
       </c>
       <c r="H837" s="5" t="s">
-        <v>4568</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="838">
       <c r="B838" s="6" t="s">
-        <v>5273</v>
+        <v>5279</v>
       </c>
       <c r="C838" s="6" t="s">
-        <v>5274</v>
+        <v>4791</v>
       </c>
       <c r="D838" s="6" t="s">
-        <v>5275</v>
+        <v>4568</v>
       </c>
       <c r="E838" s="6" t="s">
-        <v>5276</v>
+        <v>4792</v>
       </c>
       <c r="F838" s="6" t="s">
-        <v>5277</v>
+        <v>4793</v>
       </c>
       <c r="G838" s="6" t="s">
-        <v>5277</v>
+        <v>4794</v>
       </c>
       <c r="H838" s="6" t="s">
-        <v>5275</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="839">
       <c r="B839" s="5" t="s">
-        <v>5278</v>
+        <v>5280</v>
       </c>
       <c r="C839" s="5" t="s">
-        <v>5279</v>
+        <v>5281</v>
       </c>
       <c r="D839" s="5" t="s">
-        <v>5280</v>
+        <v>5282</v>
       </c>
       <c r="E839" s="5" t="s">
-        <v>5281</v>
+        <v>5283</v>
       </c>
       <c r="F839" s="5" t="s">
+        <v>5284</v>
+      </c>
+      <c r="G839" s="5" t="s">
+        <v>5284</v>
+      </c>
+      <c r="H839" s="5" t="s">
         <v>5282</v>
-      </c>
-      <c r="G839" s="5" t="s">
-        <v>5282</v>
-      </c>
-      <c r="H839" s="5" t="s">
-        <v>5283</v>
       </c>
     </row>
     <row r="840">
       <c r="B840" s="6" t="s">
-        <v>5284</v>
+        <v>5285</v>
       </c>
       <c r="C840" s="6" t="s">
-        <v>3882</v>
+        <v>5286</v>
       </c>
       <c r="D840" s="6" t="s">
-        <v>5275</v>
+        <v>5287</v>
       </c>
       <c r="E840" s="6" t="s">
-        <v>3884</v>
+        <v>5288</v>
       </c>
       <c r="F840" s="6" t="s">
-        <v>3885</v>
+        <v>5289</v>
       </c>
       <c r="G840" s="6" t="s">
-        <v>3885</v>
+        <v>5289</v>
       </c>
       <c r="H840" s="6" t="s">
-        <v>3886</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="841">
       <c r="B841" s="5" t="s">
-        <v>5285</v>
+        <v>5291</v>
       </c>
       <c r="C841" s="5" t="s">
-        <v>3764</v>
+        <v>3882</v>
       </c>
       <c r="D841" s="5" t="s">
-        <v>5286</v>
+        <v>5282</v>
       </c>
       <c r="E841" s="5" t="s">
-        <v>3766</v>
+        <v>3884</v>
       </c>
       <c r="F841" s="5" t="s">
-        <v>3767</v>
+        <v>3885</v>
       </c>
       <c r="G841" s="5" t="s">
-        <v>3768</v>
+        <v>3885</v>
       </c>
       <c r="H841" s="5" t="s">
-        <v>5287</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="842">
       <c r="B842" s="6" t="s">
-        <v>5288</v>
+        <v>5292</v>
       </c>
       <c r="C842" s="6" t="s">
-        <v>5289</v>
+        <v>3764</v>
       </c>
       <c r="D842" s="6" t="s">
-        <v>5290</v>
+        <v>5293</v>
       </c>
       <c r="E842" s="6" t="s">
-        <v>5291</v>
+        <v>3766</v>
       </c>
       <c r="F842" s="6" t="s">
-        <v>5292</v>
+        <v>3767</v>
       </c>
       <c r="G842" s="6" t="s">
-        <v>5292</v>
+        <v>3768</v>
       </c>
       <c r="H842" s="6" t="s">
-        <v>5293</v>
+        <v>5294</v>
       </c>
     </row>
     <row r="843">
       <c r="B843" s="5" t="s">
-        <v>5294</v>
+        <v>5295</v>
       </c>
       <c r="C843" s="5" t="s">
-        <v>5295</v>
+        <v>5296</v>
       </c>
       <c r="D843" s="5" t="s">
-        <v>5296</v>
+        <v>5297</v>
       </c>
       <c r="E843" s="5" t="s">
-        <v>5297</v>
+        <v>5298</v>
       </c>
       <c r="F843" s="5" t="s">
-        <v>5297</v>
+        <v>5299</v>
       </c>
       <c r="G843" s="5" t="s">
-        <v>5297</v>
+        <v>5299</v>
       </c>
       <c r="H843" s="5" t="s">
-        <v>5298</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="844">
       <c r="B844" s="6" t="s">
-        <v>5299</v>
+        <v>5301</v>
       </c>
       <c r="C844" s="6" t="s">
-        <v>5300</v>
+        <v>5302</v>
       </c>
       <c r="D844" s="6" t="s">
-        <v>5301</v>
+        <v>5303</v>
       </c>
       <c r="E844" s="6" t="s">
-        <v>5302</v>
+        <v>5304</v>
       </c>
       <c r="F844" s="6" t="s">
-        <v>5303</v>
+        <v>5304</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>5303</v>
+        <v>5304</v>
       </c>
       <c r="H844" s="6" t="s">
-        <v>5304</v>
+        <v>5305</v>
       </c>
     </row>
     <row r="845">
       <c r="B845" s="5" t="s">
-        <v>5305</v>
+        <v>5306</v>
       </c>
       <c r="C845" s="5" t="s">
-        <v>3949</v>
+        <v>5307</v>
       </c>
       <c r="D845" s="5" t="s">
-        <v>5306</v>
+        <v>5308</v>
       </c>
       <c r="E845" s="5" t="s">
-        <v>3951</v>
+        <v>5309</v>
       </c>
       <c r="F845" s="5" t="s">
-        <v>2258</v>
+        <v>5310</v>
       </c>
       <c r="G845" s="5" t="s">
-        <v>2258</v>
+        <v>5310</v>
       </c>
       <c r="H845" s="5" t="s">
-        <v>5307</v>
+        <v>5311</v>
       </c>
     </row>
     <row r="846">
       <c r="B846" s="6" t="s">
-        <v>5308</v>
+        <v>5312</v>
       </c>
       <c r="C846" s="6" t="s">
-        <v>3954</v>
+        <v>3949</v>
       </c>
       <c r="D846" s="6" t="s">
-        <v>5309</v>
+        <v>5313</v>
       </c>
       <c r="E846" s="6" t="s">
-        <v>3956</v>
+        <v>3951</v>
       </c>
       <c r="F846" s="6" t="s">
-        <v>3957</v>
+        <v>2258</v>
       </c>
       <c r="G846" s="6" t="s">
-        <v>3958</v>
+        <v>2258</v>
       </c>
       <c r="H846" s="6" t="s">
-        <v>5310</v>
+        <v>5314</v>
       </c>
     </row>
     <row r="847">
       <c r="B847" s="5" t="s">
-        <v>5311</v>
+        <v>5315</v>
       </c>
       <c r="C847" s="5" t="s">
-        <v>3961</v>
+        <v>3954</v>
       </c>
       <c r="D847" s="5" t="s">
-        <v>5312</v>
+        <v>5316</v>
       </c>
       <c r="E847" s="5" t="s">
-        <v>3963</v>
+        <v>3956</v>
       </c>
       <c r="F847" s="5" t="s">
-        <v>3964</v>
+        <v>3957</v>
       </c>
       <c r="G847" s="5" t="s">
-        <v>3964</v>
+        <v>3958</v>
       </c>
       <c r="H847" s="5" t="s">
-        <v>5313</v>
+        <v>5317</v>
       </c>
     </row>
     <row r="848">
       <c r="B848" s="6" t="s">
-        <v>5314</v>
+        <v>5318</v>
       </c>
       <c r="C848" s="6" t="s">
-        <v>2352</v>
+        <v>3961</v>
       </c>
       <c r="D848" s="6" t="s">
-        <v>2353</v>
+        <v>5319</v>
       </c>
       <c r="E848" s="6" t="s">
-        <v>2354</v>
+        <v>3963</v>
       </c>
       <c r="F848" s="6" t="s">
-        <v>2355</v>
+        <v>3964</v>
       </c>
       <c r="G848" s="6" t="s">
-        <v>2356</v>
+        <v>3964</v>
       </c>
       <c r="H848" s="6" t="s">
-        <v>2357</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="849">
       <c r="B849" s="5" t="s">
-        <v>5315</v>
+        <v>5321</v>
       </c>
       <c r="C849" s="5" t="s">
-        <v>2222</v>
+        <v>2352</v>
       </c>
       <c r="D849" s="5" t="s">
-        <v>2152</v>
+        <v>2353</v>
       </c>
       <c r="E849" s="5" t="s">
-        <v>2153</v>
+        <v>2354</v>
       </c>
       <c r="F849" s="5" t="s">
-        <v>2154</v>
+        <v>2355</v>
       </c>
       <c r="G849" s="5" t="s">
-        <v>2155</v>
+        <v>2356</v>
       </c>
       <c r="H849" s="5" t="s">
-        <v>2152</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
-        <v>5316</v>
+        <v>5322</v>
       </c>
       <c r="C850" s="6" t="s">
-        <v>2208</v>
+        <v>2222</v>
       </c>
       <c r="D850" s="6" t="s">
-        <v>2209</v>
+        <v>2152</v>
       </c>
       <c r="E850" s="6" t="s">
-        <v>2210</v>
+        <v>2153</v>
       </c>
       <c r="F850" s="6" t="s">
-        <v>2211</v>
+        <v>2154</v>
       </c>
       <c r="G850" s="6" t="s">
-        <v>2212</v>
+        <v>2155</v>
       </c>
       <c r="H850" s="6" t="s">
-        <v>2213</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="851">
       <c r="B851" s="5" t="s">
-        <v>5317</v>
+        <v>5323</v>
       </c>
       <c r="C851" s="5" t="s">
-        <v>2202</v>
+        <v>2208</v>
       </c>
       <c r="D851" s="5" t="s">
-        <v>2203</v>
+        <v>2209</v>
       </c>
       <c r="E851" s="5" t="s">
-        <v>2204</v>
+        <v>2210</v>
       </c>
       <c r="F851" s="5" t="s">
-        <v>2205</v>
+        <v>2211</v>
       </c>
       <c r="G851" s="5" t="s">
-        <v>2205</v>
+        <v>2212</v>
       </c>
       <c r="H851" s="5" t="s">
-        <v>2206</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="852">
       <c r="B852" s="6" t="s">
-        <v>5318</v>
+        <v>5324</v>
       </c>
       <c r="C852" s="6" t="s">
-        <v>2215</v>
+        <v>2202</v>
       </c>
       <c r="D852" s="6" t="s">
-        <v>2216</v>
+        <v>2203</v>
       </c>
       <c r="E852" s="6" t="s">
-        <v>2217</v>
+        <v>2204</v>
       </c>
       <c r="F852" s="6" t="s">
-        <v>2218</v>
+        <v>2205</v>
       </c>
       <c r="G852" s="6" t="s">
-        <v>2219</v>
+        <v>2205</v>
       </c>
       <c r="H852" s="6" t="s">
-        <v>2220</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="853">
       <c r="B853" s="5" t="s">
-        <v>5319</v>
+        <v>5325</v>
       </c>
       <c r="C853" s="5" t="s">
-        <v>2196</v>
+        <v>2215</v>
       </c>
       <c r="D853" s="5" t="s">
-        <v>2197</v>
+        <v>2216</v>
       </c>
       <c r="E853" s="5" t="s">
-        <v>2198</v>
+        <v>2217</v>
       </c>
       <c r="F853" s="5" t="s">
-        <v>2199</v>
+        <v>2218</v>
       </c>
       <c r="G853" s="5" t="s">
-        <v>2200</v>
+        <v>2219</v>
       </c>
       <c r="H853" s="5" t="s">
-        <v>2197</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="854">
       <c r="B854" s="6" t="s">
-        <v>5320</v>
+        <v>5326</v>
       </c>
       <c r="C854" s="6" t="s">
-        <v>2224</v>
+        <v>2196</v>
       </c>
       <c r="D854" s="6" t="s">
-        <v>2225</v>
+        <v>2197</v>
       </c>
       <c r="E854" s="6" t="s">
-        <v>2226</v>
+        <v>2198</v>
       </c>
       <c r="F854" s="6" t="s">
-        <v>2227</v>
+        <v>2199</v>
       </c>
       <c r="G854" s="6" t="s">
-        <v>2228</v>
+        <v>2200</v>
       </c>
       <c r="H854" s="6" t="s">
-        <v>2229</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="855">
       <c r="B855" s="5" t="s">
-        <v>5321</v>
+        <v>5327</v>
       </c>
       <c r="C855" s="5" t="s">
-        <v>5322</v>
+        <v>2224</v>
       </c>
       <c r="D855" s="5" t="s">
-        <v>2192</v>
+        <v>2225</v>
       </c>
       <c r="E855" s="5" t="s">
-        <v>2193</v>
+        <v>2226</v>
       </c>
       <c r="F855" s="5" t="s">
-        <v>2194</v>
+        <v>2227</v>
       </c>
       <c r="G855" s="5" t="s">
-        <v>2194</v>
+        <v>2228</v>
       </c>
       <c r="H855" s="5" t="s">
-        <v>2192</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="856">
       <c r="B856" s="6" t="s">
-        <v>5323</v>
+        <v>5328</v>
       </c>
       <c r="C856" s="6" t="s">
-        <v>5324</v>
+        <v>5329</v>
       </c>
       <c r="D856" s="6" t="s">
-        <v>5325</v>
+        <v>2192</v>
       </c>
       <c r="E856" s="6" t="s">
-        <v>5326</v>
+        <v>2193</v>
       </c>
       <c r="F856" s="6" t="s">
-        <v>5327</v>
+        <v>2194</v>
       </c>
       <c r="G856" s="6" t="s">
-        <v>5328</v>
+        <v>2194</v>
       </c>
       <c r="H856" s="6" t="s">
-        <v>5325</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="857">
       <c r="B857" s="5" t="s">
-        <v>5329</v>
+        <v>5330</v>
       </c>
       <c r="C857" s="5" t="s">
-        <v>5330</v>
+        <v>5331</v>
       </c>
       <c r="D857" s="5" t="s">
-        <v>5331</v>
+        <v>5332</v>
       </c>
       <c r="E857" s="5" t="s">
+        <v>5333</v>
+      </c>
+      <c r="F857" s="5" t="s">
+        <v>5334</v>
+      </c>
+      <c r="G857" s="5" t="s">
+        <v>5335</v>
+      </c>
+      <c r="H857" s="5" t="s">
         <v>5332</v>
-      </c>
-      <c r="F857" s="5" t="s">
-        <v>5333</v>
-      </c>
-      <c r="G857" s="5" t="s">
-        <v>5334</v>
-      </c>
-      <c r="H857" s="5" t="s">
-        <v>5335</v>
       </c>
     </row>
     <row r="858">
@@ -43521,27 +43563,27 @@
         <v>5354</v>
       </c>
       <c r="G860" s="6" t="s">
-        <v>5354</v>
+        <v>5355</v>
       </c>
       <c r="H860" s="6" t="s">
-        <v>5355</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="861">
       <c r="B861" s="5" t="s">
-        <v>5356</v>
+        <v>5357</v>
       </c>
       <c r="C861" s="5" t="s">
-        <v>5357</v>
+        <v>5358</v>
       </c>
       <c r="D861" s="5" t="s">
-        <v>5358</v>
+        <v>5359</v>
       </c>
       <c r="E861" s="5" t="s">
-        <v>5359</v>
+        <v>5360</v>
       </c>
       <c r="F861" s="5" t="s">
-        <v>5360</v>
+        <v>5361</v>
       </c>
       <c r="G861" s="5" t="s">
         <v>5361</v>
@@ -43590,30 +43632,30 @@
         <v>5374</v>
       </c>
       <c r="G863" s="5" t="s">
-        <v>5373</v>
+        <v>5375</v>
       </c>
       <c r="H863" s="5" t="s">
-        <v>5372</v>
+        <v>5376</v>
       </c>
     </row>
     <row r="864">
       <c r="B864" s="6" t="s">
-        <v>5375</v>
+        <v>5377</v>
       </c>
       <c r="C864" s="6" t="s">
-        <v>5376</v>
+        <v>5378</v>
       </c>
       <c r="D864" s="6" t="s">
-        <v>5377</v>
+        <v>5379</v>
       </c>
       <c r="E864" s="6" t="s">
-        <v>5378</v>
+        <v>5380</v>
       </c>
       <c r="F864" s="6" t="s">
-        <v>5378</v>
+        <v>5381</v>
       </c>
       <c r="G864" s="6" t="s">
-        <v>5378</v>
+        <v>5380</v>
       </c>
       <c r="H864" s="6" t="s">
         <v>5379</v>
@@ -43621,111 +43663,111 @@
     </row>
     <row r="865">
       <c r="B865" s="5" t="s">
-        <v>5380</v>
+        <v>5382</v>
       </c>
       <c r="C865" s="5" t="s">
-        <v>5381</v>
+        <v>5383</v>
       </c>
       <c r="D865" s="5" t="s">
-        <v>1279</v>
+        <v>5384</v>
       </c>
       <c r="E865" s="5" t="s">
-        <v>5382</v>
+        <v>5385</v>
       </c>
       <c r="F865" s="5" t="s">
-        <v>5382</v>
+        <v>5385</v>
       </c>
       <c r="G865" s="5" t="s">
-        <v>5382</v>
+        <v>5385</v>
       </c>
       <c r="H865" s="5" t="s">
-        <v>5383</v>
+        <v>5386</v>
       </c>
     </row>
     <row r="866">
       <c r="B866" s="6" t="s">
-        <v>5384</v>
+        <v>5387</v>
       </c>
       <c r="C866" s="6" t="s">
-        <v>5385</v>
+        <v>5388</v>
       </c>
       <c r="D866" s="6" t="s">
-        <v>5386</v>
+        <v>1279</v>
       </c>
       <c r="E866" s="6" t="s">
-        <v>5387</v>
+        <v>5389</v>
       </c>
       <c r="F866" s="6" t="s">
-        <v>5387</v>
+        <v>5389</v>
       </c>
       <c r="G866" s="6" t="s">
-        <v>5387</v>
+        <v>5389</v>
       </c>
       <c r="H866" s="6" t="s">
-        <v>5388</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="867">
       <c r="B867" s="5" t="s">
-        <v>5389</v>
+        <v>5391</v>
       </c>
       <c r="C867" s="5" t="s">
-        <v>5390</v>
+        <v>5392</v>
       </c>
       <c r="D867" s="5" t="s">
-        <v>5391</v>
+        <v>5393</v>
       </c>
       <c r="E867" s="5" t="s">
-        <v>5392</v>
+        <v>5394</v>
       </c>
       <c r="F867" s="5" t="s">
-        <v>5393</v>
+        <v>5394</v>
       </c>
       <c r="G867" s="5" t="s">
-        <v>5393</v>
+        <v>5394</v>
       </c>
       <c r="H867" s="5" t="s">
-        <v>5394</v>
+        <v>5395</v>
       </c>
     </row>
     <row r="868">
       <c r="B868" s="6" t="s">
-        <v>5395</v>
+        <v>5396</v>
       </c>
       <c r="C868" s="6" t="s">
-        <v>5396</v>
+        <v>5397</v>
       </c>
       <c r="D868" s="6" t="s">
-        <v>5397</v>
+        <v>5398</v>
       </c>
       <c r="E868" s="6" t="s">
-        <v>5398</v>
+        <v>5399</v>
       </c>
       <c r="F868" s="6" t="s">
-        <v>5399</v>
+        <v>5400</v>
       </c>
       <c r="G868" s="6" t="s">
-        <v>5399</v>
+        <v>5400</v>
       </c>
       <c r="H868" s="6" t="s">
-        <v>5400</v>
+        <v>5401</v>
       </c>
     </row>
     <row r="869">
       <c r="B869" s="5" t="s">
-        <v>5401</v>
+        <v>5402</v>
       </c>
       <c r="C869" s="5" t="s">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="D869" s="5" t="s">
-        <v>5403</v>
+        <v>5404</v>
       </c>
       <c r="E869" s="5" t="s">
-        <v>5404</v>
+        <v>5405</v>
       </c>
       <c r="F869" s="5" t="s">
-        <v>5405</v>
+        <v>5406</v>
       </c>
       <c r="G869" s="5" t="s">
         <v>5406</v>
@@ -43797,50 +43839,50 @@
         <v>5426</v>
       </c>
       <c r="G872" s="6" t="s">
-        <v>5426</v>
+        <v>5427</v>
       </c>
       <c r="H872" s="6" t="s">
-        <v>5427</v>
+        <v>5428</v>
       </c>
     </row>
     <row r="873">
       <c r="B873" s="5" t="s">
-        <v>5428</v>
+        <v>5429</v>
       </c>
       <c r="C873" s="5" t="s">
-        <v>5429</v>
+        <v>5430</v>
       </c>
       <c r="D873" s="5" t="s">
-        <v>5430</v>
+        <v>5431</v>
       </c>
       <c r="E873" s="5" t="s">
-        <v>5431</v>
+        <v>5432</v>
       </c>
       <c r="F873" s="5" t="s">
-        <v>5432</v>
+        <v>5433</v>
       </c>
       <c r="G873" s="5" t="s">
-        <v>5432</v>
+        <v>5433</v>
       </c>
       <c r="H873" s="5" t="s">
-        <v>5433</v>
+        <v>5434</v>
       </c>
     </row>
     <row r="874">
       <c r="B874" s="6" t="s">
-        <v>5434</v>
+        <v>5435</v>
       </c>
       <c r="C874" s="6" t="s">
-        <v>5435</v>
+        <v>5436</v>
       </c>
       <c r="D874" s="6" t="s">
-        <v>5436</v>
+        <v>5437</v>
       </c>
       <c r="E874" s="6" t="s">
-        <v>5437</v>
+        <v>5438</v>
       </c>
       <c r="F874" s="6" t="s">
-        <v>5438</v>
+        <v>5439</v>
       </c>
       <c r="G874" s="6" t="s">
         <v>5439</v>
@@ -43912,27 +43954,27 @@
         <v>5459</v>
       </c>
       <c r="G877" s="5" t="s">
-        <v>5459</v>
+        <v>5460</v>
       </c>
       <c r="H877" s="5" t="s">
-        <v>5460</v>
+        <v>5461</v>
       </c>
     </row>
     <row r="878">
       <c r="B878" s="6" t="s">
-        <v>5461</v>
+        <v>5462</v>
       </c>
       <c r="C878" s="6" t="s">
-        <v>5462</v>
+        <v>5463</v>
       </c>
       <c r="D878" s="6" t="s">
-        <v>5463</v>
+        <v>5464</v>
       </c>
       <c r="E878" s="6" t="s">
-        <v>5464</v>
+        <v>5465</v>
       </c>
       <c r="F878" s="6" t="s">
-        <v>5465</v>
+        <v>5466</v>
       </c>
       <c r="G878" s="6" t="s">
         <v>5466</v>
@@ -44004,56 +44046,56 @@
         <v>5486</v>
       </c>
       <c r="G881" s="5" t="s">
-        <v>5485</v>
+        <v>5487</v>
       </c>
       <c r="H881" s="5" t="s">
-        <v>5484</v>
+        <v>5488</v>
       </c>
     </row>
     <row r="882">
       <c r="B882" s="6" t="s">
-        <v>5487</v>
+        <v>5489</v>
       </c>
       <c r="C882" s="6" t="s">
-        <v>5488</v>
+        <v>5490</v>
       </c>
       <c r="D882" s="6" t="s">
-        <v>4450</v>
+        <v>5491</v>
       </c>
       <c r="E882" s="6" t="s">
-        <v>4451</v>
+        <v>5492</v>
       </c>
       <c r="F882" s="6" t="s">
-        <v>4452</v>
+        <v>5493</v>
       </c>
       <c r="G882" s="6" t="s">
-        <v>4453</v>
+        <v>5492</v>
       </c>
       <c r="H882" s="6" t="s">
-        <v>4454</v>
+        <v>5491</v>
       </c>
     </row>
     <row r="883">
       <c r="B883" s="5" t="s">
-        <v>5489</v>
+        <v>5494</v>
       </c>
       <c r="C883" s="5" t="s">
-        <v>5490</v>
+        <v>5495</v>
       </c>
       <c r="D883" s="5" t="s">
-        <v>5491</v>
+        <v>4450</v>
       </c>
       <c r="E883" s="5" t="s">
-        <v>5492</v>
+        <v>4451</v>
       </c>
       <c r="F883" s="5" t="s">
-        <v>5493</v>
+        <v>4452</v>
       </c>
       <c r="G883" s="5" t="s">
-        <v>5494</v>
+        <v>4453</v>
       </c>
       <c r="H883" s="5" t="s">
-        <v>5495</v>
+        <v>4454</v>
       </c>
     </row>
     <row r="884">
@@ -44257,27 +44299,27 @@
         <v>5556</v>
       </c>
       <c r="G892" s="6" t="s">
-        <v>5556</v>
+        <v>5557</v>
       </c>
       <c r="H892" s="6" t="s">
-        <v>5557</v>
+        <v>5558</v>
       </c>
     </row>
     <row r="893">
       <c r="B893" s="5" t="s">
-        <v>5558</v>
+        <v>5559</v>
       </c>
       <c r="C893" s="5" t="s">
-        <v>5559</v>
+        <v>5560</v>
       </c>
       <c r="D893" s="5" t="s">
-        <v>5560</v>
+        <v>5561</v>
       </c>
       <c r="E893" s="5" t="s">
-        <v>5561</v>
+        <v>5562</v>
       </c>
       <c r="F893" s="5" t="s">
-        <v>5562</v>
+        <v>5563</v>
       </c>
       <c r="G893" s="5" t="s">
         <v>5563</v>
@@ -44763,27 +44805,27 @@
         <v>5709</v>
       </c>
       <c r="G914" s="6" t="s">
-        <v>5709</v>
+        <v>5710</v>
       </c>
       <c r="H914" s="6" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
     </row>
     <row r="915">
       <c r="B915" s="5" t="s">
-        <v>5711</v>
+        <v>5712</v>
       </c>
       <c r="C915" s="5" t="s">
-        <v>5712</v>
+        <v>5713</v>
       </c>
       <c r="D915" s="5" t="s">
-        <v>5713</v>
+        <v>5714</v>
       </c>
       <c r="E915" s="5" t="s">
-        <v>5714</v>
+        <v>5715</v>
       </c>
       <c r="F915" s="5" t="s">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="G915" s="5" t="s">
         <v>5716</v>
@@ -44832,27 +44874,27 @@
         <v>5729</v>
       </c>
       <c r="G917" s="5" t="s">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="H917" s="5" t="s">
-        <v>5730</v>
+        <v>5731</v>
       </c>
     </row>
     <row r="918">
       <c r="B918" s="6" t="s">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="C918" s="6" t="s">
-        <v>5732</v>
+        <v>5733</v>
       </c>
       <c r="D918" s="6" t="s">
-        <v>5733</v>
+        <v>5734</v>
       </c>
       <c r="E918" s="6" t="s">
-        <v>5734</v>
+        <v>5735</v>
       </c>
       <c r="F918" s="6" t="s">
-        <v>5735</v>
+        <v>5736</v>
       </c>
       <c r="G918" s="6" t="s">
         <v>5736</v>
@@ -44924,50 +44966,50 @@
         <v>5756</v>
       </c>
       <c r="G921" s="5" t="s">
-        <v>5756</v>
+        <v>5757</v>
       </c>
       <c r="H921" s="5" t="s">
-        <v>5757</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="922">
       <c r="B922" s="6" t="s">
-        <v>5758</v>
+        <v>5759</v>
       </c>
       <c r="C922" s="6" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="D922" s="6" t="s">
-        <v>5760</v>
+        <v>5761</v>
       </c>
       <c r="E922" s="6" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="F922" s="6" t="s">
-        <v>5762</v>
+        <v>5763</v>
       </c>
       <c r="G922" s="6" t="s">
-        <v>5762</v>
+        <v>5763</v>
       </c>
       <c r="H922" s="6" t="s">
-        <v>5763</v>
+        <v>5764</v>
       </c>
     </row>
     <row r="923">
       <c r="B923" s="5" t="s">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="C923" s="5" t="s">
-        <v>5765</v>
+        <v>5766</v>
       </c>
       <c r="D923" s="5" t="s">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="E923" s="5" t="s">
-        <v>5767</v>
+        <v>5768</v>
       </c>
       <c r="F923" s="5" t="s">
-        <v>5768</v>
+        <v>5769</v>
       </c>
       <c r="G923" s="5" t="s">
         <v>5769</v>
@@ -45076,39 +45118,39 @@
         <v>5800</v>
       </c>
       <c r="D928" s="6" t="s">
-        <v>5800</v>
+        <v>5801</v>
       </c>
       <c r="E928" s="6" t="s">
-        <v>5800</v>
+        <v>5802</v>
       </c>
       <c r="F928" s="6" t="s">
-        <v>5800</v>
+        <v>5803</v>
       </c>
       <c r="G928" s="6" t="s">
-        <v>5800</v>
+        <v>5804</v>
       </c>
       <c r="H928" s="6" t="s">
-        <v>5800</v>
+        <v>5805</v>
       </c>
     </row>
     <row r="929">
       <c r="B929" s="5" t="s">
-        <v>5801</v>
+        <v>5806</v>
       </c>
       <c r="C929" s="5" t="s">
-        <v>5802</v>
+        <v>5807</v>
       </c>
       <c r="D929" s="5" t="s">
-        <v>5803</v>
+        <v>5807</v>
       </c>
       <c r="E929" s="5" t="s">
-        <v>5804</v>
+        <v>5807</v>
       </c>
       <c r="F929" s="5" t="s">
-        <v>5805</v>
+        <v>5807</v>
       </c>
       <c r="G929" s="5" t="s">
-        <v>5806</v>
+        <v>5807</v>
       </c>
       <c r="H929" s="5" t="s">
         <v>5807</v>
@@ -45134,30 +45176,30 @@
         <v>5813</v>
       </c>
       <c r="H930" s="6" t="s">
-        <v>5810</v>
+        <v>5814</v>
       </c>
     </row>
     <row r="931">
       <c r="B931" s="5" t="s">
-        <v>5814</v>
+        <v>5815</v>
       </c>
       <c r="C931" s="5" t="s">
-        <v>5815</v>
+        <v>5816</v>
       </c>
       <c r="D931" s="5" t="s">
-        <v>5816</v>
+        <v>5817</v>
       </c>
       <c r="E931" s="5" t="s">
+        <v>5818</v>
+      </c>
+      <c r="F931" s="5" t="s">
+        <v>5819</v>
+      </c>
+      <c r="G931" s="5" t="s">
+        <v>5820</v>
+      </c>
+      <c r="H931" s="5" t="s">
         <v>5817</v>
-      </c>
-      <c r="F931" s="5" t="s">
-        <v>5818</v>
-      </c>
-      <c r="G931" s="5" t="s">
-        <v>5819</v>
-      </c>
-      <c r="H931" s="5" t="s">
-        <v>5820</v>
       </c>
     </row>
     <row r="932">
@@ -45257,91 +45299,91 @@
         <v>5849</v>
       </c>
       <c r="C936" s="6" t="s">
-        <v>3163</v>
+        <v>5850</v>
       </c>
       <c r="D936" s="6" t="s">
-        <v>5850</v>
+        <v>5851</v>
       </c>
       <c r="E936" s="6" t="s">
-        <v>3165</v>
+        <v>5852</v>
       </c>
       <c r="F936" s="6" t="s">
-        <v>5851</v>
+        <v>5853</v>
       </c>
       <c r="G936" s="6" t="s">
-        <v>5852</v>
+        <v>5854</v>
       </c>
       <c r="H936" s="6" t="s">
-        <v>5853</v>
+        <v>5855</v>
       </c>
     </row>
     <row r="937">
       <c r="B937" s="5" t="s">
-        <v>5854</v>
+        <v>5856</v>
       </c>
       <c r="C937" s="5" t="s">
-        <v>3156</v>
+        <v>3163</v>
       </c>
       <c r="D937" s="5" t="s">
-        <v>5855</v>
+        <v>5857</v>
       </c>
       <c r="E937" s="5" t="s">
-        <v>3158</v>
+        <v>3165</v>
       </c>
       <c r="F937" s="5" t="s">
-        <v>5856</v>
+        <v>5858</v>
       </c>
       <c r="G937" s="5" t="s">
-        <v>5857</v>
+        <v>5859</v>
       </c>
       <c r="H937" s="5" t="s">
-        <v>5858</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="938">
       <c r="B938" s="6" t="s">
-        <v>5859</v>
+        <v>5861</v>
       </c>
       <c r="C938" s="6" t="s">
-        <v>4619</v>
+        <v>3156</v>
       </c>
       <c r="D938" s="6" t="s">
-        <v>4620</v>
+        <v>5862</v>
       </c>
       <c r="E938" s="6" t="s">
-        <v>4621</v>
+        <v>3158</v>
       </c>
       <c r="F938" s="6" t="s">
-        <v>4622</v>
+        <v>5863</v>
       </c>
       <c r="G938" s="6" t="s">
-        <v>4622</v>
+        <v>5864</v>
       </c>
       <c r="H938" s="6" t="s">
-        <v>4620</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="939">
       <c r="B939" s="5" t="s">
-        <v>5860</v>
+        <v>5866</v>
       </c>
       <c r="C939" s="5" t="s">
-        <v>5861</v>
+        <v>4619</v>
       </c>
       <c r="D939" s="5" t="s">
-        <v>5862</v>
+        <v>4620</v>
       </c>
       <c r="E939" s="5" t="s">
-        <v>5863</v>
+        <v>4621</v>
       </c>
       <c r="F939" s="5" t="s">
-        <v>5864</v>
+        <v>4622</v>
       </c>
       <c r="G939" s="5" t="s">
-        <v>5865</v>
+        <v>4622</v>
       </c>
       <c r="H939" s="5" t="s">
-        <v>5866</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="940">
@@ -45487,45 +45529,45 @@
         <v>5909</v>
       </c>
       <c r="C946" s="6" t="s">
-        <v>4456</v>
+        <v>5910</v>
       </c>
       <c r="D946" s="6" t="s">
-        <v>4457</v>
+        <v>5911</v>
       </c>
       <c r="E946" s="6" t="s">
-        <v>4458</v>
+        <v>5912</v>
       </c>
       <c r="F946" s="6" t="s">
-        <v>4459</v>
+        <v>5913</v>
       </c>
       <c r="G946" s="6" t="s">
-        <v>4460</v>
+        <v>5914</v>
       </c>
       <c r="H946" s="6" t="s">
-        <v>4457</v>
+        <v>5915</v>
       </c>
     </row>
     <row r="947">
       <c r="B947" s="5" t="s">
-        <v>5910</v>
+        <v>5916</v>
       </c>
       <c r="C947" s="5" t="s">
-        <v>5911</v>
+        <v>4456</v>
       </c>
       <c r="D947" s="5" t="s">
-        <v>5912</v>
+        <v>4457</v>
       </c>
       <c r="E947" s="5" t="s">
-        <v>5913</v>
+        <v>4458</v>
       </c>
       <c r="F947" s="5" t="s">
-        <v>5914</v>
+        <v>4459</v>
       </c>
       <c r="G947" s="5" t="s">
-        <v>5915</v>
+        <v>4460</v>
       </c>
       <c r="H947" s="5" t="s">
-        <v>5916</v>
+        <v>4457</v>
       </c>
     </row>
     <row r="948">
@@ -45533,45 +45575,45 @@
         <v>5917</v>
       </c>
       <c r="C948" s="6" t="s">
-        <v>4798</v>
+        <v>5918</v>
       </c>
       <c r="D948" s="6" t="s">
-        <v>4799</v>
+        <v>5919</v>
       </c>
       <c r="E948" s="6" t="s">
-        <v>4801</v>
+        <v>5920</v>
       </c>
       <c r="F948" s="6" t="s">
-        <v>4801</v>
+        <v>5921</v>
       </c>
       <c r="G948" s="6" t="s">
-        <v>4801</v>
+        <v>5922</v>
       </c>
       <c r="H948" s="6" t="s">
-        <v>5245</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="949">
       <c r="B949" s="5" t="s">
-        <v>5918</v>
+        <v>5924</v>
       </c>
       <c r="C949" s="5" t="s">
-        <v>5919</v>
+        <v>4798</v>
       </c>
       <c r="D949" s="5" t="s">
-        <v>5920</v>
+        <v>4799</v>
       </c>
       <c r="E949" s="5" t="s">
-        <v>5921</v>
+        <v>4801</v>
       </c>
       <c r="F949" s="5" t="s">
-        <v>5922</v>
+        <v>4801</v>
       </c>
       <c r="G949" s="5" t="s">
-        <v>5923</v>
+        <v>4801</v>
       </c>
       <c r="H949" s="5" t="s">
-        <v>5924</v>
+        <v>5252</v>
       </c>
     </row>
     <row r="950">
@@ -45671,108 +45713,108 @@
         <v>5953</v>
       </c>
       <c r="C954" s="6" t="s">
-        <v>3882</v>
+        <v>5954</v>
       </c>
       <c r="D954" s="6" t="s">
-        <v>5275</v>
+        <v>5955</v>
       </c>
       <c r="E954" s="6" t="s">
-        <v>3884</v>
+        <v>5956</v>
       </c>
       <c r="F954" s="6" t="s">
-        <v>3885</v>
+        <v>5957</v>
       </c>
       <c r="G954" s="6" t="s">
-        <v>3885</v>
+        <v>5958</v>
       </c>
       <c r="H954" s="6" t="s">
-        <v>3886</v>
+        <v>5959</v>
       </c>
     </row>
     <row r="955">
       <c r="B955" s="5" t="s">
-        <v>5954</v>
+        <v>5960</v>
       </c>
       <c r="C955" s="5" t="s">
-        <v>3890</v>
+        <v>3882</v>
       </c>
       <c r="D955" s="5" t="s">
-        <v>4434</v>
+        <v>5282</v>
       </c>
       <c r="E955" s="5" t="s">
-        <v>3892</v>
+        <v>3884</v>
       </c>
       <c r="F955" s="5" t="s">
-        <v>3893</v>
+        <v>3885</v>
       </c>
       <c r="G955" s="5" t="s">
-        <v>3893</v>
+        <v>3885</v>
       </c>
       <c r="H955" s="5" t="s">
-        <v>4435</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="956">
       <c r="B956" s="6" t="s">
-        <v>5955</v>
+        <v>5961</v>
       </c>
       <c r="C956" s="6" t="s">
-        <v>3751</v>
+        <v>3890</v>
       </c>
       <c r="D956" s="6" t="s">
-        <v>4796</v>
+        <v>4434</v>
       </c>
       <c r="E956" s="6" t="s">
-        <v>3753</v>
+        <v>3892</v>
       </c>
       <c r="F956" s="6" t="s">
-        <v>5956</v>
+        <v>3893</v>
       </c>
       <c r="G956" s="6" t="s">
-        <v>5956</v>
+        <v>3893</v>
       </c>
       <c r="H956" s="6" t="s">
-        <v>3123</v>
+        <v>4435</v>
       </c>
     </row>
     <row r="957">
       <c r="B957" s="5" t="s">
-        <v>5957</v>
+        <v>5962</v>
       </c>
       <c r="C957" s="5" t="s">
-        <v>5958</v>
+        <v>3751</v>
       </c>
       <c r="D957" s="5" t="s">
-        <v>5959</v>
+        <v>4796</v>
       </c>
       <c r="E957" s="5" t="s">
-        <v>5960</v>
+        <v>3753</v>
       </c>
       <c r="F957" s="5" t="s">
-        <v>5961</v>
+        <v>5963</v>
       </c>
       <c r="G957" s="5" t="s">
-        <v>5961</v>
+        <v>5963</v>
       </c>
       <c r="H957" s="5" t="s">
-        <v>5962</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="958">
       <c r="B958" s="6" t="s">
-        <v>5963</v>
+        <v>5964</v>
       </c>
       <c r="C958" s="6" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="D958" s="6" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
       <c r="E958" s="6" t="s">
-        <v>5966</v>
+        <v>5967</v>
       </c>
       <c r="F958" s="6" t="s">
-        <v>5967</v>
+        <v>5968</v>
       </c>
       <c r="G958" s="6" t="s">
         <v>5968</v>
@@ -45821,73 +45863,73 @@
         <v>5981</v>
       </c>
       <c r="G960" s="6" t="s">
-        <v>5981</v>
+        <v>5982</v>
       </c>
       <c r="H960" s="6" t="s">
-        <v>5982</v>
+        <v>5983</v>
       </c>
     </row>
     <row r="961">
       <c r="B961" s="5" t="s">
-        <v>5983</v>
+        <v>5984</v>
       </c>
       <c r="C961" s="5" t="s">
-        <v>5984</v>
+        <v>5985</v>
       </c>
       <c r="D961" s="5" t="s">
-        <v>5985</v>
+        <v>5986</v>
       </c>
       <c r="E961" s="5" t="s">
-        <v>5986</v>
+        <v>5987</v>
       </c>
       <c r="F961" s="5" t="s">
-        <v>5987</v>
+        <v>5988</v>
       </c>
       <c r="G961" s="5" t="s">
-        <v>5987</v>
+        <v>5988</v>
       </c>
       <c r="H961" s="5" t="s">
-        <v>5988</v>
+        <v>5989</v>
       </c>
     </row>
     <row r="962">
       <c r="B962" s="6" t="s">
-        <v>5989</v>
+        <v>5990</v>
       </c>
       <c r="C962" s="6" t="s">
-        <v>5990</v>
+        <v>5991</v>
       </c>
       <c r="D962" s="6" t="s">
-        <v>5991</v>
+        <v>5992</v>
       </c>
       <c r="E962" s="6" t="s">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="F962" s="6" t="s">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="G962" s="6" t="s">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="H962" s="6" t="s">
-        <v>5994</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="963">
       <c r="B963" s="5" t="s">
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="C963" s="5" t="s">
-        <v>5996</v>
+        <v>5997</v>
       </c>
       <c r="D963" s="5" t="s">
-        <v>5997</v>
+        <v>5998</v>
       </c>
       <c r="E963" s="5" t="s">
-        <v>5998</v>
+        <v>5999</v>
       </c>
       <c r="F963" s="5" t="s">
-        <v>5999</v>
+        <v>6000</v>
       </c>
       <c r="G963" s="5" t="s">
         <v>6000</v>
@@ -46005,27 +46047,27 @@
         <v>6034</v>
       </c>
       <c r="G968" s="6" t="s">
-        <v>6034</v>
+        <v>6035</v>
       </c>
       <c r="H968" s="6" t="s">
-        <v>6035</v>
+        <v>6036</v>
       </c>
     </row>
     <row r="969">
       <c r="B969" s="5" t="s">
-        <v>6036</v>
+        <v>6037</v>
       </c>
       <c r="C969" s="5" t="s">
-        <v>6037</v>
+        <v>6038</v>
       </c>
       <c r="D969" s="5" t="s">
-        <v>6038</v>
+        <v>6039</v>
       </c>
       <c r="E969" s="5" t="s">
-        <v>6039</v>
+        <v>6040</v>
       </c>
       <c r="F969" s="5" t="s">
-        <v>6040</v>
+        <v>6041</v>
       </c>
       <c r="G969" s="5" t="s">
         <v>6041</v>
@@ -46054,30 +46096,30 @@
         <v>6048</v>
       </c>
       <c r="H970" s="6" t="s">
-        <v>5777</v>
+        <v>6049</v>
       </c>
     </row>
     <row r="971">
       <c r="B971" s="5" t="s">
-        <v>6049</v>
+        <v>6050</v>
       </c>
       <c r="C971" s="5" t="s">
-        <v>6050</v>
+        <v>6051</v>
       </c>
       <c r="D971" s="5" t="s">
-        <v>6051</v>
+        <v>6052</v>
       </c>
       <c r="E971" s="5" t="s">
-        <v>6052</v>
+        <v>6053</v>
       </c>
       <c r="F971" s="5" t="s">
-        <v>6053</v>
+        <v>6054</v>
       </c>
       <c r="G971" s="5" t="s">
-        <v>6054</v>
+        <v>6055</v>
       </c>
       <c r="H971" s="5" t="s">
-        <v>6055</v>
+        <v>5784</v>
       </c>
     </row>
     <row r="972">
@@ -46117,36 +46159,36 @@
         <v>6066</v>
       </c>
       <c r="F973" s="5" t="s">
-        <v>6066</v>
+        <v>6067</v>
       </c>
       <c r="G973" s="5" t="s">
-        <v>6066</v>
+        <v>6068</v>
       </c>
       <c r="H973" s="5" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="974">
       <c r="B974" s="6" t="s">
-        <v>6067</v>
+        <v>6070</v>
       </c>
       <c r="C974" s="6" t="s">
-        <v>6068</v>
+        <v>6071</v>
       </c>
       <c r="D974" s="6" t="s">
-        <v>6069</v>
+        <v>6072</v>
       </c>
       <c r="E974" s="6" t="s">
-        <v>6070</v>
+        <v>6073</v>
       </c>
       <c r="F974" s="6" t="s">
-        <v>6071</v>
+        <v>6073</v>
       </c>
       <c r="G974" s="6" t="s">
+        <v>6073</v>
+      </c>
+      <c r="H974" s="6" t="s">
         <v>6072</v>
-      </c>
-      <c r="H974" s="6" t="s">
-        <v>6073</v>
       </c>
     </row>
     <row r="975">
@@ -46226,42 +46268,42 @@
         <v>6096</v>
       </c>
       <c r="D978" s="6" t="s">
-        <v>6065</v>
+        <v>6097</v>
       </c>
       <c r="E978" s="6" t="s">
-        <v>6097</v>
+        <v>6098</v>
       </c>
       <c r="F978" s="6" t="s">
-        <v>6098</v>
+        <v>6099</v>
       </c>
       <c r="G978" s="6" t="s">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="H978" s="6" t="s">
-        <v>6065</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="979">
       <c r="B979" s="5" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
       <c r="C979" s="5" t="s">
-        <v>6100</v>
+        <v>6103</v>
       </c>
       <c r="D979" s="5" t="s">
-        <v>6101</v>
+        <v>6072</v>
       </c>
       <c r="E979" s="5" t="s">
-        <v>6102</v>
+        <v>6104</v>
       </c>
       <c r="F979" s="5" t="s">
-        <v>6103</v>
+        <v>6105</v>
       </c>
       <c r="G979" s="5" t="s">
-        <v>6104</v>
+        <v>6105</v>
       </c>
       <c r="H979" s="5" t="s">
-        <v>6105</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="980">
@@ -46284,30 +46326,30 @@
         <v>6111</v>
       </c>
       <c r="H980" s="6" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="981">
       <c r="B981" s="5" t="s">
-        <v>6112</v>
+        <v>6113</v>
       </c>
       <c r="C981" s="5" t="s">
-        <v>6113</v>
+        <v>6114</v>
       </c>
       <c r="D981" s="5" t="s">
-        <v>6114</v>
+        <v>6115</v>
       </c>
       <c r="E981" s="5" t="s">
+        <v>6116</v>
+      </c>
+      <c r="F981" s="5" t="s">
+        <v>6117</v>
+      </c>
+      <c r="G981" s="5" t="s">
+        <v>6118</v>
+      </c>
+      <c r="H981" s="5" t="s">
         <v>6115</v>
-      </c>
-      <c r="F981" s="5" t="s">
-        <v>6116</v>
-      </c>
-      <c r="G981" s="5" t="s">
-        <v>6117</v>
-      </c>
-      <c r="H981" s="5" t="s">
-        <v>6118</v>
       </c>
     </row>
     <row r="982">
@@ -46396,27 +46438,27 @@
         <v>6144</v>
       </c>
       <c r="G985" s="5" t="s">
-        <v>6144</v>
+        <v>6145</v>
       </c>
       <c r="H985" s="5" t="s">
-        <v>6145</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="986">
       <c r="B986" s="6" t="s">
-        <v>6146</v>
+        <v>6147</v>
       </c>
       <c r="C986" s="6" t="s">
-        <v>6147</v>
+        <v>6148</v>
       </c>
       <c r="D986" s="6" t="s">
-        <v>6148</v>
+        <v>6149</v>
       </c>
       <c r="E986" s="6" t="s">
-        <v>6149</v>
+        <v>6150</v>
       </c>
       <c r="F986" s="6" t="s">
-        <v>6150</v>
+        <v>6151</v>
       </c>
       <c r="G986" s="6" t="s">
         <v>6151</v>
@@ -46442,27 +46484,27 @@
         <v>6157</v>
       </c>
       <c r="G987" s="5" t="s">
-        <v>6157</v>
+        <v>6158</v>
       </c>
       <c r="H987" s="5" t="s">
-        <v>6158</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="988">
       <c r="B988" s="6" t="s">
-        <v>6159</v>
+        <v>6160</v>
       </c>
       <c r="C988" s="6" t="s">
-        <v>6160</v>
+        <v>6161</v>
       </c>
       <c r="D988" s="6" t="s">
-        <v>6161</v>
+        <v>6162</v>
       </c>
       <c r="E988" s="6" t="s">
-        <v>6162</v>
+        <v>6163</v>
       </c>
       <c r="F988" s="6" t="s">
-        <v>6163</v>
+        <v>6164</v>
       </c>
       <c r="G988" s="6" t="s">
         <v>6164</v>
@@ -46511,56 +46553,56 @@
         <v>6177</v>
       </c>
       <c r="G990" s="6" t="s">
-        <v>6176</v>
+        <v>6178</v>
       </c>
       <c r="H990" s="6" t="s">
-        <v>6178</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="991">
       <c r="B991" s="5" t="s">
-        <v>6179</v>
+        <v>6180</v>
       </c>
       <c r="C991" s="5" t="s">
-        <v>6180</v>
+        <v>6181</v>
       </c>
       <c r="D991" s="5" t="s">
-        <v>6181</v>
+        <v>6182</v>
       </c>
       <c r="E991" s="5" t="s">
-        <v>6182</v>
+        <v>6183</v>
       </c>
       <c r="F991" s="5" t="s">
-        <v>6183</v>
+        <v>6184</v>
       </c>
       <c r="G991" s="5" t="s">
         <v>6183</v>
       </c>
       <c r="H991" s="5" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="992">
       <c r="B992" s="6" t="s">
-        <v>6184</v>
+        <v>6186</v>
       </c>
       <c r="C992" s="6" t="s">
-        <v>6185</v>
+        <v>6187</v>
       </c>
       <c r="D992" s="6" t="s">
-        <v>6186</v>
+        <v>6188</v>
       </c>
       <c r="E992" s="6" t="s">
-        <v>6187</v>
+        <v>6189</v>
       </c>
       <c r="F992" s="6" t="s">
+        <v>6190</v>
+      </c>
+      <c r="G992" s="6" t="s">
+        <v>6190</v>
+      </c>
+      <c r="H992" s="6" t="s">
         <v>6188</v>
-      </c>
-      <c r="G992" s="6" t="s">
-        <v>6189</v>
-      </c>
-      <c r="H992" s="6" t="s">
-        <v>6190</v>
       </c>
     </row>
     <row r="993">
@@ -46583,30 +46625,30 @@
         <v>6196</v>
       </c>
       <c r="H993" s="5" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="994">
       <c r="B994" s="6" t="s">
-        <v>6197</v>
+        <v>6198</v>
       </c>
       <c r="C994" s="6" t="s">
-        <v>6198</v>
+        <v>6199</v>
       </c>
       <c r="D994" s="6" t="s">
-        <v>6199</v>
+        <v>6200</v>
       </c>
       <c r="E994" s="6" t="s">
+        <v>6201</v>
+      </c>
+      <c r="F994" s="6" t="s">
+        <v>6202</v>
+      </c>
+      <c r="G994" s="6" t="s">
+        <v>6203</v>
+      </c>
+      <c r="H994" s="6" t="s">
         <v>6200</v>
-      </c>
-      <c r="F994" s="6" t="s">
-        <v>6201</v>
-      </c>
-      <c r="G994" s="6" t="s">
-        <v>6202</v>
-      </c>
-      <c r="H994" s="6" t="s">
-        <v>6203</v>
       </c>
     </row>
     <row r="995">
@@ -46626,50 +46668,50 @@
         <v>6208</v>
       </c>
       <c r="G995" s="5" t="s">
-        <v>6208</v>
+        <v>6209</v>
       </c>
       <c r="H995" s="5" t="s">
-        <v>6209</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="996">
       <c r="B996" s="6" t="s">
-        <v>6210</v>
+        <v>6211</v>
       </c>
       <c r="C996" s="6" t="s">
-        <v>6211</v>
+        <v>6212</v>
       </c>
       <c r="D996" s="6" t="s">
-        <v>6212</v>
+        <v>6213</v>
       </c>
       <c r="E996" s="6" t="s">
-        <v>6213</v>
+        <v>6214</v>
       </c>
       <c r="F996" s="6" t="s">
-        <v>6214</v>
+        <v>6215</v>
       </c>
       <c r="G996" s="6" t="s">
-        <v>6214</v>
+        <v>6215</v>
       </c>
       <c r="H996" s="6" t="s">
-        <v>6215</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="997">
       <c r="B997" s="5" t="s">
-        <v>6216</v>
+        <v>6217</v>
       </c>
       <c r="C997" s="5" t="s">
-        <v>6217</v>
+        <v>6218</v>
       </c>
       <c r="D997" s="5" t="s">
-        <v>6218</v>
+        <v>6219</v>
       </c>
       <c r="E997" s="5" t="s">
-        <v>6219</v>
+        <v>6220</v>
       </c>
       <c r="F997" s="5" t="s">
-        <v>6220</v>
+        <v>6221</v>
       </c>
       <c r="G997" s="5" t="s">
         <v>6221</v>
@@ -46695,27 +46737,27 @@
         <v>6227</v>
       </c>
       <c r="G998" s="6" t="s">
-        <v>6227</v>
+        <v>6228</v>
       </c>
       <c r="H998" s="6" t="s">
-        <v>6228</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="999">
       <c r="B999" s="5" t="s">
-        <v>6229</v>
+        <v>6230</v>
       </c>
       <c r="C999" s="5" t="s">
-        <v>6230</v>
+        <v>6231</v>
       </c>
       <c r="D999" s="5" t="s">
-        <v>6231</v>
+        <v>6232</v>
       </c>
       <c r="E999" s="5" t="s">
-        <v>6232</v>
+        <v>6233</v>
       </c>
       <c r="F999" s="5" t="s">
-        <v>6233</v>
+        <v>6234</v>
       </c>
       <c r="G999" s="5" t="s">
         <v>6234</v>
@@ -46741,171 +46783,171 @@
         <v>6240</v>
       </c>
       <c r="G1000" s="6" t="s">
-        <v>6240</v>
+        <v>6241</v>
       </c>
       <c r="H1000" s="6" t="s">
-        <v>6241</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="1001">
       <c r="B1001" s="5" t="s">
-        <v>6242</v>
+        <v>6243</v>
       </c>
       <c r="C1001" s="5" t="s">
-        <v>6243</v>
+        <v>6244</v>
       </c>
       <c r="D1001" s="5" t="s">
-        <v>6244</v>
+        <v>6245</v>
       </c>
       <c r="E1001" s="5" t="s">
-        <v>6245</v>
+        <v>6246</v>
       </c>
       <c r="F1001" s="5" t="s">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="G1001" s="5" t="s">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="H1001" s="5" t="s">
-        <v>6247</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="1002">
       <c r="B1002" s="6" t="s">
-        <v>6248</v>
+        <v>6249</v>
       </c>
       <c r="C1002" s="6" t="s">
-        <v>6249</v>
+        <v>6250</v>
       </c>
       <c r="D1002" s="6" t="s">
-        <v>6249</v>
+        <v>6251</v>
       </c>
       <c r="E1002" s="6" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
       <c r="F1002" s="6" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="G1002" s="6" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="H1002" s="6" t="s">
-        <v>6249</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="1003">
       <c r="B1003" s="5" t="s">
-        <v>6250</v>
+        <v>6255</v>
       </c>
       <c r="C1003" s="5" t="s">
-        <v>6251</v>
+        <v>6256</v>
       </c>
       <c r="D1003" s="5" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="E1003" s="5" t="s">
-        <v>6253</v>
+        <v>6256</v>
       </c>
       <c r="F1003" s="5" t="s">
-        <v>6254</v>
+        <v>6256</v>
       </c>
       <c r="G1003" s="5" t="s">
-        <v>6254</v>
+        <v>6256</v>
       </c>
       <c r="H1003" s="5" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="1004">
       <c r="B1004" s="6" t="s">
-        <v>6255</v>
+        <v>6257</v>
       </c>
       <c r="C1004" s="6" t="s">
-        <v>6256</v>
+        <v>6258</v>
       </c>
       <c r="D1004" s="6" t="s">
-        <v>6257</v>
+        <v>6259</v>
       </c>
       <c r="E1004" s="6" t="s">
-        <v>6258</v>
+        <v>6260</v>
       </c>
       <c r="F1004" s="6" t="s">
+        <v>6261</v>
+      </c>
+      <c r="G1004" s="6" t="s">
+        <v>6261</v>
+      </c>
+      <c r="H1004" s="6" t="s">
         <v>6259</v>
-      </c>
-      <c r="G1004" s="6" t="s">
-        <v>6260</v>
-      </c>
-      <c r="H1004" s="6" t="s">
-        <v>6257</v>
       </c>
     </row>
     <row r="1005">
       <c r="B1005" s="5" t="s">
-        <v>6261</v>
+        <v>6262</v>
       </c>
       <c r="C1005" s="5" t="s">
-        <v>6262</v>
+        <v>6263</v>
       </c>
       <c r="D1005" s="5" t="s">
-        <v>6263</v>
+        <v>6264</v>
       </c>
       <c r="E1005" s="5" t="s">
+        <v>6265</v>
+      </c>
+      <c r="F1005" s="5" t="s">
+        <v>6266</v>
+      </c>
+      <c r="G1005" s="5" t="s">
+        <v>6267</v>
+      </c>
+      <c r="H1005" s="5" t="s">
         <v>6264</v>
-      </c>
-      <c r="F1005" s="5" t="s">
-        <v>6264</v>
-      </c>
-      <c r="G1005" s="5" t="s">
-        <v>6264</v>
-      </c>
-      <c r="H1005" s="5" t="s">
-        <v>6263</v>
       </c>
     </row>
     <row r="1006">
       <c r="B1006" s="6" t="s">
-        <v>6265</v>
+        <v>6268</v>
       </c>
       <c r="C1006" s="6" t="s">
-        <v>6266</v>
+        <v>6269</v>
       </c>
       <c r="D1006" s="6" t="s">
-        <v>6267</v>
+        <v>6270</v>
       </c>
       <c r="E1006" s="6" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
       <c r="F1006" s="6" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
       <c r="G1006" s="6" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
       <c r="H1006" s="6" t="s">
-        <v>6267</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="1007">
       <c r="B1007" s="5" t="s">
-        <v>6269</v>
+        <v>6272</v>
       </c>
       <c r="C1007" s="5" t="s">
-        <v>6270</v>
+        <v>6273</v>
       </c>
       <c r="D1007" s="5" t="s">
-        <v>6271</v>
+        <v>6274</v>
       </c>
       <c r="E1007" s="5" t="s">
-        <v>6272</v>
+        <v>6275</v>
       </c>
       <c r="F1007" s="5" t="s">
-        <v>6273</v>
+        <v>6275</v>
       </c>
       <c r="G1007" s="5" t="s">
+        <v>6275</v>
+      </c>
+      <c r="H1007" s="5" t="s">
         <v>6274</v>
-      </c>
-      <c r="H1007" s="5" t="s">
-        <v>6275</v>
       </c>
     </row>
     <row r="1008">
@@ -46928,30 +46970,30 @@
         <v>6281</v>
       </c>
       <c r="H1008" s="6" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="1009">
       <c r="B1009" s="5" t="s">
-        <v>6282</v>
+        <v>6283</v>
       </c>
       <c r="C1009" s="5" t="s">
-        <v>6283</v>
+        <v>6284</v>
       </c>
       <c r="D1009" s="5" t="s">
-        <v>6284</v>
+        <v>6285</v>
       </c>
       <c r="E1009" s="5" t="s">
+        <v>6286</v>
+      </c>
+      <c r="F1009" s="5" t="s">
+        <v>6287</v>
+      </c>
+      <c r="G1009" s="5" t="s">
+        <v>6288</v>
+      </c>
+      <c r="H1009" s="5" t="s">
         <v>6285</v>
-      </c>
-      <c r="F1009" s="5" t="s">
-        <v>6286</v>
-      </c>
-      <c r="G1009" s="5" t="s">
-        <v>6287</v>
-      </c>
-      <c r="H1009" s="5" t="s">
-        <v>6288</v>
       </c>
     </row>
     <row r="1010">
@@ -47020,30 +47062,30 @@
         <v>6308</v>
       </c>
       <c r="H1012" s="6" t="s">
-        <v>6278</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="1013">
       <c r="B1013" s="5" t="s">
-        <v>6309</v>
+        <v>6310</v>
       </c>
       <c r="C1013" s="5" t="s">
-        <v>6310</v>
+        <v>6311</v>
       </c>
       <c r="D1013" s="5" t="s">
-        <v>6311</v>
+        <v>6312</v>
       </c>
       <c r="E1013" s="5" t="s">
-        <v>6312</v>
+        <v>6313</v>
       </c>
       <c r="F1013" s="5" t="s">
-        <v>6313</v>
+        <v>6314</v>
       </c>
       <c r="G1013" s="5" t="s">
-        <v>6314</v>
+        <v>6315</v>
       </c>
       <c r="H1013" s="5" t="s">
-        <v>6315</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="1014">
@@ -47063,50 +47105,50 @@
         <v>6320</v>
       </c>
       <c r="G1014" s="6" t="s">
-        <v>6320</v>
+        <v>6321</v>
       </c>
       <c r="H1014" s="6" t="s">
-        <v>6321</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="1015">
       <c r="B1015" s="5" t="s">
-        <v>6322</v>
+        <v>6323</v>
       </c>
       <c r="C1015" s="5" t="s">
-        <v>6323</v>
+        <v>6324</v>
       </c>
       <c r="D1015" s="5" t="s">
-        <v>6324</v>
+        <v>6325</v>
       </c>
       <c r="E1015" s="5" t="s">
-        <v>6325</v>
+        <v>6326</v>
       </c>
       <c r="F1015" s="5" t="s">
-        <v>6326</v>
+        <v>6327</v>
       </c>
       <c r="G1015" s="5" t="s">
-        <v>6326</v>
+        <v>6327</v>
       </c>
       <c r="H1015" s="5" t="s">
-        <v>6327</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="1016">
       <c r="B1016" s="6" t="s">
-        <v>6328</v>
+        <v>6329</v>
       </c>
       <c r="C1016" s="6" t="s">
-        <v>6329</v>
+        <v>6330</v>
       </c>
       <c r="D1016" s="6" t="s">
-        <v>6330</v>
+        <v>6331</v>
       </c>
       <c r="E1016" s="6" t="s">
-        <v>6331</v>
+        <v>6332</v>
       </c>
       <c r="F1016" s="6" t="s">
-        <v>6332</v>
+        <v>6333</v>
       </c>
       <c r="G1016" s="6" t="s">
         <v>6333</v>
@@ -47143,183 +47185,183 @@
         <v>6342</v>
       </c>
       <c r="C1018" s="6" t="s">
-        <v>4700</v>
+        <v>6343</v>
       </c>
       <c r="D1018" s="6" t="s">
-        <v>4701</v>
+        <v>6344</v>
       </c>
       <c r="E1018" s="6" t="s">
-        <v>6343</v>
+        <v>6345</v>
       </c>
       <c r="F1018" s="6" t="s">
-        <v>6344</v>
+        <v>6346</v>
       </c>
       <c r="G1018" s="6" t="s">
-        <v>6344</v>
+        <v>6347</v>
       </c>
       <c r="H1018" s="6" t="s">
-        <v>6345</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="1019">
       <c r="B1019" s="5" t="s">
-        <v>6346</v>
+        <v>6349</v>
       </c>
       <c r="C1019" s="5" t="s">
-        <v>3751</v>
+        <v>4700</v>
       </c>
       <c r="D1019" s="5" t="s">
-        <v>4796</v>
+        <v>4701</v>
       </c>
       <c r="E1019" s="5" t="s">
-        <v>3753</v>
+        <v>6350</v>
       </c>
       <c r="F1019" s="5" t="s">
-        <v>5956</v>
+        <v>6351</v>
       </c>
       <c r="G1019" s="5" t="s">
-        <v>5956</v>
+        <v>6351</v>
       </c>
       <c r="H1019" s="5" t="s">
-        <v>3123</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="1020">
       <c r="B1020" s="6" t="s">
-        <v>6347</v>
+        <v>6353</v>
       </c>
       <c r="C1020" s="6" t="s">
-        <v>6348</v>
+        <v>3751</v>
       </c>
       <c r="D1020" s="6" t="s">
-        <v>6349</v>
+        <v>4796</v>
       </c>
       <c r="E1020" s="6" t="s">
-        <v>6349</v>
+        <v>3753</v>
       </c>
       <c r="F1020" s="6" t="s">
-        <v>6349</v>
+        <v>5963</v>
       </c>
       <c r="G1020" s="6" t="s">
-        <v>6349</v>
+        <v>5963</v>
       </c>
       <c r="H1020" s="6" t="s">
-        <v>6349</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="1021">
       <c r="B1021" s="5" t="s">
-        <v>6350</v>
+        <v>6354</v>
       </c>
       <c r="C1021" s="5" t="s">
-        <v>6351</v>
+        <v>6355</v>
       </c>
       <c r="D1021" s="5" t="s">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="E1021" s="5" t="s">
-        <v>6353</v>
+        <v>6356</v>
       </c>
       <c r="F1021" s="5" t="s">
-        <v>6354</v>
+        <v>6356</v>
       </c>
       <c r="G1021" s="5" t="s">
-        <v>6354</v>
+        <v>6356</v>
       </c>
       <c r="H1021" s="5" t="s">
-        <v>6355</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="1022">
       <c r="B1022" s="6" t="s">
-        <v>6356</v>
+        <v>6357</v>
       </c>
       <c r="C1022" s="6" t="s">
-        <v>6357</v>
+        <v>6358</v>
       </c>
       <c r="D1022" s="6" t="s">
-        <v>5948</v>
+        <v>6359</v>
       </c>
       <c r="E1022" s="6" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
       <c r="F1022" s="6" t="s">
-        <v>5950</v>
+        <v>6361</v>
       </c>
       <c r="G1022" s="6" t="s">
-        <v>5951</v>
+        <v>6361</v>
       </c>
       <c r="H1022" s="6" t="s">
-        <v>6359</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="1023">
       <c r="B1023" s="5" t="s">
-        <v>6360</v>
+        <v>6363</v>
       </c>
       <c r="C1023" s="5" t="s">
-        <v>6361</v>
+        <v>6364</v>
       </c>
       <c r="D1023" s="5" t="s">
-        <v>6362</v>
+        <v>5955</v>
       </c>
       <c r="E1023" s="5" t="s">
-        <v>3963</v>
+        <v>6365</v>
       </c>
       <c r="F1023" s="5" t="s">
-        <v>3964</v>
+        <v>5957</v>
       </c>
       <c r="G1023" s="5" t="s">
-        <v>3964</v>
+        <v>5958</v>
       </c>
       <c r="H1023" s="5" t="s">
-        <v>5313</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="1024">
       <c r="B1024" s="6" t="s">
-        <v>6363</v>
+        <v>6367</v>
       </c>
       <c r="C1024" s="6" t="s">
-        <v>6364</v>
+        <v>6368</v>
       </c>
       <c r="D1024" s="6" t="s">
-        <v>6365</v>
+        <v>6369</v>
       </c>
       <c r="E1024" s="6" t="s">
-        <v>6366</v>
+        <v>3963</v>
       </c>
       <c r="F1024" s="6" t="s">
-        <v>6367</v>
+        <v>3964</v>
       </c>
       <c r="G1024" s="6" t="s">
-        <v>6368</v>
+        <v>3964</v>
       </c>
       <c r="H1024" s="6" t="s">
-        <v>6365</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="1025">
       <c r="B1025" s="5" t="s">
-        <v>6369</v>
+        <v>6370</v>
       </c>
       <c r="C1025" s="5" t="s">
-        <v>6370</v>
+        <v>6371</v>
       </c>
       <c r="D1025" s="5" t="s">
-        <v>6371</v>
+        <v>6372</v>
       </c>
       <c r="E1025" s="5" t="s">
+        <v>6373</v>
+      </c>
+      <c r="F1025" s="5" t="s">
+        <v>6374</v>
+      </c>
+      <c r="G1025" s="5" t="s">
+        <v>6375</v>
+      </c>
+      <c r="H1025" s="5" t="s">
         <v>6372</v>
-      </c>
-      <c r="F1025" s="5" t="s">
-        <v>6373</v>
-      </c>
-      <c r="G1025" s="5" t="s">
-        <v>6374</v>
-      </c>
-      <c r="H1025" s="5" t="s">
-        <v>6375</v>
       </c>
     </row>
     <row r="1026">
@@ -47339,27 +47381,27 @@
         <v>6380</v>
       </c>
       <c r="G1026" s="6" t="s">
-        <v>6380</v>
+        <v>6381</v>
       </c>
       <c r="H1026" s="6" t="s">
-        <v>6381</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="1027">
       <c r="B1027" s="5" t="s">
-        <v>6382</v>
+        <v>6383</v>
       </c>
       <c r="C1027" s="5" t="s">
-        <v>6383</v>
+        <v>6384</v>
       </c>
       <c r="D1027" s="5" t="s">
-        <v>6384</v>
+        <v>6385</v>
       </c>
       <c r="E1027" s="5" t="s">
-        <v>6385</v>
+        <v>6386</v>
       </c>
       <c r="F1027" s="5" t="s">
-        <v>6386</v>
+        <v>6387</v>
       </c>
       <c r="G1027" s="5" t="s">
         <v>6387</v>
@@ -47408,73 +47450,73 @@
         <v>6400</v>
       </c>
       <c r="G1029" s="5" t="s">
-        <v>6400</v>
+        <v>6401</v>
       </c>
       <c r="H1029" s="5" t="s">
-        <v>6401</v>
+        <v>6402</v>
       </c>
     </row>
     <row r="1030">
       <c r="B1030" s="6" t="s">
-        <v>6402</v>
+        <v>6403</v>
       </c>
       <c r="C1030" s="6" t="s">
-        <v>6403</v>
+        <v>6404</v>
       </c>
       <c r="D1030" s="6" t="s">
-        <v>6404</v>
+        <v>6405</v>
       </c>
       <c r="E1030" s="6" t="s">
-        <v>6405</v>
+        <v>6406</v>
       </c>
       <c r="F1030" s="6" t="s">
-        <v>6406</v>
+        <v>6407</v>
       </c>
       <c r="G1030" s="6" t="s">
-        <v>6406</v>
+        <v>6407</v>
       </c>
       <c r="H1030" s="6" t="s">
-        <v>6407</v>
+        <v>6408</v>
       </c>
     </row>
     <row r="1031">
       <c r="B1031" s="5" t="s">
-        <v>6408</v>
+        <v>6409</v>
       </c>
       <c r="C1031" s="5" t="s">
-        <v>6409</v>
+        <v>6410</v>
       </c>
       <c r="D1031" s="5" t="s">
-        <v>6410</v>
+        <v>6411</v>
       </c>
       <c r="E1031" s="5" t="s">
-        <v>6411</v>
+        <v>6412</v>
       </c>
       <c r="F1031" s="5" t="s">
-        <v>6412</v>
+        <v>6413</v>
       </c>
       <c r="G1031" s="5" t="s">
-        <v>6412</v>
+        <v>6413</v>
       </c>
       <c r="H1031" s="5" t="s">
-        <v>6413</v>
+        <v>6414</v>
       </c>
     </row>
     <row r="1032">
       <c r="B1032" s="6" t="s">
-        <v>6414</v>
+        <v>6415</v>
       </c>
       <c r="C1032" s="6" t="s">
-        <v>6415</v>
+        <v>6416</v>
       </c>
       <c r="D1032" s="6" t="s">
-        <v>6416</v>
+        <v>6417</v>
       </c>
       <c r="E1032" s="6" t="s">
-        <v>6417</v>
+        <v>6418</v>
       </c>
       <c r="F1032" s="6" t="s">
-        <v>6418</v>
+        <v>6419</v>
       </c>
       <c r="G1032" s="6" t="s">
         <v>6419</v>
@@ -47523,27 +47565,27 @@
         <v>6432</v>
       </c>
       <c r="G1034" s="6" t="s">
-        <v>6432</v>
+        <v>6433</v>
       </c>
       <c r="H1034" s="6" t="s">
-        <v>6433</v>
+        <v>6434</v>
       </c>
     </row>
     <row r="1035">
       <c r="B1035" s="5" t="s">
-        <v>6434</v>
+        <v>6435</v>
       </c>
       <c r="C1035" s="5" t="s">
-        <v>6435</v>
+        <v>6436</v>
       </c>
       <c r="D1035" s="5" t="s">
-        <v>6436</v>
+        <v>6437</v>
       </c>
       <c r="E1035" s="5" t="s">
-        <v>6437</v>
+        <v>6438</v>
       </c>
       <c r="F1035" s="5" t="s">
-        <v>6438</v>
+        <v>6439</v>
       </c>
       <c r="G1035" s="5" t="s">
         <v>6439</v>
@@ -47569,27 +47611,27 @@
         <v>6445</v>
       </c>
       <c r="G1036" s="6" t="s">
-        <v>6445</v>
+        <v>6446</v>
       </c>
       <c r="H1036" s="6" t="s">
-        <v>6446</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="1037">
       <c r="B1037" s="5" t="s">
-        <v>6447</v>
+        <v>6448</v>
       </c>
       <c r="C1037" s="5" t="s">
-        <v>6448</v>
+        <v>6449</v>
       </c>
       <c r="D1037" s="5" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="E1037" s="5" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="F1037" s="5" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
       <c r="G1037" s="5" t="s">
         <v>6452</v>
@@ -47615,122 +47657,122 @@
         <v>6458</v>
       </c>
       <c r="G1038" s="6" t="s">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="H1038" s="6" t="s">
-        <v>6459</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="1039">
       <c r="B1039" s="5" t="s">
-        <v>6460</v>
+        <v>6461</v>
       </c>
       <c r="C1039" s="5" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D1039" s="5" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E1039" s="5" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F1039" s="5" t="s">
-        <v>6464</v>
+        <v>6465</v>
       </c>
       <c r="G1039" s="5" t="s">
-        <v>6464</v>
+        <v>6465</v>
       </c>
       <c r="H1039" s="5" t="s">
-        <v>6465</v>
+        <v>6466</v>
       </c>
     </row>
     <row r="1040">
       <c r="B1040" s="6" t="s">
-        <v>6466</v>
+        <v>6467</v>
       </c>
       <c r="C1040" s="6" t="s">
-        <v>6467</v>
+        <v>6468</v>
       </c>
       <c r="D1040" s="6" t="s">
-        <v>6468</v>
+        <v>6469</v>
       </c>
       <c r="E1040" s="6" t="s">
-        <v>6469</v>
+        <v>6470</v>
       </c>
       <c r="F1040" s="6" t="s">
-        <v>6470</v>
+        <v>6471</v>
       </c>
       <c r="G1040" s="6" t="s">
-        <v>6470</v>
+        <v>6471</v>
       </c>
       <c r="H1040" s="6" t="s">
-        <v>6471</v>
+        <v>6472</v>
       </c>
     </row>
     <row r="1041">
       <c r="B1041" s="5" t="s">
-        <v>6472</v>
+        <v>6473</v>
       </c>
       <c r="C1041" s="5" t="s">
-        <v>6473</v>
+        <v>6474</v>
       </c>
       <c r="D1041" s="5" t="s">
-        <v>6474</v>
+        <v>6475</v>
       </c>
       <c r="E1041" s="5" t="s">
-        <v>6475</v>
+        <v>6476</v>
       </c>
       <c r="F1041" s="5" t="s">
-        <v>6476</v>
+        <v>6477</v>
       </c>
       <c r="G1041" s="5" t="s">
-        <v>6476</v>
+        <v>6477</v>
       </c>
       <c r="H1041" s="5" t="s">
-        <v>6477</v>
+        <v>6478</v>
       </c>
     </row>
     <row r="1042">
       <c r="B1042" s="6" t="s">
-        <v>6478</v>
+        <v>6479</v>
       </c>
       <c r="C1042" s="6" t="s">
-        <v>6479</v>
+        <v>6480</v>
       </c>
       <c r="D1042" s="6" t="s">
-        <v>6480</v>
+        <v>6481</v>
       </c>
       <c r="E1042" s="6" t="s">
-        <v>6481</v>
+        <v>6482</v>
       </c>
       <c r="F1042" s="6" t="s">
-        <v>6482</v>
+        <v>6483</v>
       </c>
       <c r="G1042" s="6" t="s">
-        <v>6481</v>
+        <v>6483</v>
       </c>
       <c r="H1042" s="6" t="s">
-        <v>6483</v>
+        <v>6484</v>
       </c>
     </row>
     <row r="1043">
       <c r="B1043" s="5" t="s">
-        <v>6484</v>
+        <v>6485</v>
       </c>
       <c r="C1043" s="5" t="s">
-        <v>6485</v>
+        <v>6486</v>
       </c>
       <c r="D1043" s="5" t="s">
-        <v>6486</v>
+        <v>6487</v>
       </c>
       <c r="E1043" s="5" t="s">
-        <v>6487</v>
+        <v>6488</v>
       </c>
       <c r="F1043" s="5" t="s">
+        <v>6489</v>
+      </c>
+      <c r="G1043" s="5" t="s">
         <v>6488</v>
-      </c>
-      <c r="G1043" s="5" t="s">
-        <v>6489</v>
       </c>
       <c r="H1043" s="5" t="s">
         <v>6490</v>
@@ -47753,50 +47795,50 @@
         <v>6495</v>
       </c>
       <c r="G1044" s="6" t="s">
-        <v>6495</v>
+        <v>6496</v>
       </c>
       <c r="H1044" s="6" t="s">
-        <v>6496</v>
+        <v>6497</v>
       </c>
     </row>
     <row r="1045">
       <c r="B1045" s="5" t="s">
-        <v>6497</v>
+        <v>6498</v>
       </c>
       <c r="C1045" s="5" t="s">
-        <v>6498</v>
+        <v>6499</v>
       </c>
       <c r="D1045" s="5" t="s">
-        <v>6499</v>
+        <v>6500</v>
       </c>
       <c r="E1045" s="5" t="s">
-        <v>6500</v>
+        <v>6501</v>
       </c>
       <c r="F1045" s="5" t="s">
-        <v>6501</v>
+        <v>6502</v>
       </c>
       <c r="G1045" s="5" t="s">
-        <v>6501</v>
+        <v>6502</v>
       </c>
       <c r="H1045" s="5" t="s">
-        <v>6502</v>
+        <v>6503</v>
       </c>
     </row>
     <row r="1046">
       <c r="B1046" s="6" t="s">
-        <v>6503</v>
+        <v>6504</v>
       </c>
       <c r="C1046" s="6" t="s">
-        <v>6504</v>
+        <v>6505</v>
       </c>
       <c r="D1046" s="6" t="s">
-        <v>6505</v>
+        <v>6506</v>
       </c>
       <c r="E1046" s="6" t="s">
-        <v>6506</v>
+        <v>6507</v>
       </c>
       <c r="F1046" s="6" t="s">
-        <v>6507</v>
+        <v>6508</v>
       </c>
       <c r="G1046" s="6" t="s">
         <v>6508</v>
@@ -47833,82 +47875,82 @@
         <v>6517</v>
       </c>
       <c r="C1048" s="6" t="s">
-        <v>5926</v>
+        <v>6518</v>
       </c>
       <c r="D1048" s="6" t="s">
-        <v>5927</v>
+        <v>6519</v>
       </c>
       <c r="E1048" s="6" t="s">
-        <v>5928</v>
+        <v>6520</v>
       </c>
       <c r="F1048" s="6" t="s">
-        <v>5929</v>
+        <v>6521</v>
       </c>
       <c r="G1048" s="6" t="s">
-        <v>5930</v>
+        <v>6522</v>
       </c>
       <c r="H1048" s="6" t="s">
-        <v>5931</v>
+        <v>6523</v>
       </c>
     </row>
     <row r="1049">
       <c r="B1049" s="5" t="s">
-        <v>6518</v>
+        <v>6524</v>
       </c>
       <c r="C1049" s="5" t="s">
-        <v>4791</v>
+        <v>5933</v>
       </c>
       <c r="D1049" s="5" t="s">
-        <v>6519</v>
+        <v>5934</v>
       </c>
       <c r="E1049" s="5" t="s">
-        <v>4792</v>
+        <v>5935</v>
       </c>
       <c r="F1049" s="5" t="s">
-        <v>4793</v>
+        <v>5936</v>
       </c>
       <c r="G1049" s="5" t="s">
-        <v>4794</v>
+        <v>5937</v>
       </c>
       <c r="H1049" s="5" t="s">
-        <v>6519</v>
+        <v>5938</v>
       </c>
     </row>
     <row r="1050">
       <c r="B1050" s="6" t="s">
-        <v>6520</v>
+        <v>6525</v>
       </c>
       <c r="C1050" s="6" t="s">
-        <v>4624</v>
+        <v>4791</v>
       </c>
       <c r="D1050" s="6" t="s">
-        <v>6521</v>
+        <v>6526</v>
       </c>
       <c r="E1050" s="6" t="s">
-        <v>4626</v>
+        <v>4792</v>
       </c>
       <c r="F1050" s="6" t="s">
-        <v>6522</v>
+        <v>4793</v>
       </c>
       <c r="G1050" s="6" t="s">
-        <v>6523</v>
+        <v>4794</v>
       </c>
       <c r="H1050" s="6" t="s">
-        <v>6524</v>
+        <v>6526</v>
       </c>
     </row>
     <row r="1051">
       <c r="B1051" s="5" t="s">
-        <v>6525</v>
+        <v>6527</v>
       </c>
       <c r="C1051" s="5" t="s">
-        <v>6526</v>
+        <v>4624</v>
       </c>
       <c r="D1051" s="5" t="s">
-        <v>6527</v>
+        <v>6528</v>
       </c>
       <c r="E1051" s="5" t="s">
-        <v>6528</v>
+        <v>4626</v>
       </c>
       <c r="F1051" s="5" t="s">
         <v>6529</v>
@@ -47931,36 +47973,36 @@
         <v>6534</v>
       </c>
       <c r="E1052" s="6" t="s">
-        <v>6513</v>
+        <v>6535</v>
       </c>
       <c r="F1052" s="6" t="s">
-        <v>6514</v>
+        <v>6536</v>
       </c>
       <c r="G1052" s="6" t="s">
-        <v>6515</v>
+        <v>6537</v>
       </c>
       <c r="H1052" s="6" t="s">
-        <v>6535</v>
+        <v>6538</v>
       </c>
     </row>
     <row r="1053">
       <c r="B1053" s="5" t="s">
-        <v>6536</v>
+        <v>6539</v>
       </c>
       <c r="C1053" s="5" t="s">
-        <v>6537</v>
+        <v>6540</v>
       </c>
       <c r="D1053" s="5" t="s">
-        <v>6538</v>
+        <v>6541</v>
       </c>
       <c r="E1053" s="5" t="s">
-        <v>6539</v>
+        <v>6520</v>
       </c>
       <c r="F1053" s="5" t="s">
-        <v>6540</v>
+        <v>6521</v>
       </c>
       <c r="G1053" s="5" t="s">
-        <v>6541</v>
+        <v>6522</v>
       </c>
       <c r="H1053" s="5" t="s">
         <v>6542</v>
@@ -47983,27 +48025,27 @@
         <v>6547</v>
       </c>
       <c r="G1054" s="6" t="s">
-        <v>6547</v>
+        <v>6548</v>
       </c>
       <c r="H1054" s="6" t="s">
-        <v>6548</v>
+        <v>6549</v>
       </c>
     </row>
     <row r="1055">
       <c r="B1055" s="5" t="s">
-        <v>6549</v>
+        <v>6550</v>
       </c>
       <c r="C1055" s="5" t="s">
-        <v>6550</v>
+        <v>6551</v>
       </c>
       <c r="D1055" s="5" t="s">
-        <v>6551</v>
+        <v>6552</v>
       </c>
       <c r="E1055" s="5" t="s">
-        <v>6552</v>
+        <v>6553</v>
       </c>
       <c r="F1055" s="5" t="s">
-        <v>6553</v>
+        <v>6554</v>
       </c>
       <c r="G1055" s="5" t="s">
         <v>6554</v>
@@ -48049,33 +48091,33 @@
         <v>6566</v>
       </c>
       <c r="F1057" s="5" t="s">
-        <v>5715</v>
+        <v>6567</v>
       </c>
       <c r="G1057" s="5" t="s">
-        <v>5716</v>
+        <v>6568</v>
       </c>
       <c r="H1057" s="5" t="s">
-        <v>6567</v>
+        <v>6569</v>
       </c>
     </row>
     <row r="1058">
       <c r="B1058" s="6" t="s">
-        <v>6568</v>
+        <v>6570</v>
       </c>
       <c r="C1058" s="6" t="s">
-        <v>6569</v>
+        <v>6571</v>
       </c>
       <c r="D1058" s="6" t="s">
-        <v>6570</v>
+        <v>6572</v>
       </c>
       <c r="E1058" s="6" t="s">
-        <v>6571</v>
+        <v>6573</v>
       </c>
       <c r="F1058" s="6" t="s">
-        <v>6572</v>
+        <v>5722</v>
       </c>
       <c r="G1058" s="6" t="s">
-        <v>6573</v>
+        <v>5723</v>
       </c>
       <c r="H1058" s="6" t="s">
         <v>6574</v>
@@ -48098,211 +48140,211 @@
         <v>6579</v>
       </c>
       <c r="G1059" s="5" t="s">
-        <v>6578</v>
+        <v>6580</v>
       </c>
       <c r="H1059" s="5" t="s">
-        <v>6577</v>
+        <v>6581</v>
       </c>
     </row>
     <row r="1060">
       <c r="B1060" s="6" t="s">
-        <v>6580</v>
+        <v>6582</v>
       </c>
       <c r="C1060" s="6" t="s">
-        <v>3751</v>
+        <v>6583</v>
       </c>
       <c r="D1060" s="6" t="s">
-        <v>4796</v>
+        <v>6584</v>
       </c>
       <c r="E1060" s="6" t="s">
-        <v>3753</v>
+        <v>6585</v>
       </c>
       <c r="F1060" s="6" t="s">
-        <v>5956</v>
+        <v>6586</v>
       </c>
       <c r="G1060" s="6" t="s">
-        <v>5956</v>
+        <v>6585</v>
       </c>
       <c r="H1060" s="6" t="s">
-        <v>3123</v>
+        <v>6584</v>
       </c>
     </row>
     <row r="1061">
       <c r="B1061" s="5" t="s">
-        <v>6581</v>
+        <v>6587</v>
       </c>
       <c r="C1061" s="5" t="s">
-        <v>3798</v>
+        <v>3751</v>
       </c>
       <c r="D1061" s="5" t="s">
-        <v>6582</v>
+        <v>4796</v>
       </c>
       <c r="E1061" s="5" t="s">
-        <v>3800</v>
+        <v>3753</v>
       </c>
       <c r="F1061" s="5" t="s">
-        <v>6583</v>
+        <v>5963</v>
       </c>
       <c r="G1061" s="5" t="s">
-        <v>6584</v>
+        <v>5963</v>
       </c>
       <c r="H1061" s="5" t="s">
-        <v>6585</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="1062">
       <c r="B1062" s="6" t="s">
-        <v>6586</v>
+        <v>6588</v>
       </c>
       <c r="C1062" s="6" t="s">
-        <v>5253</v>
+        <v>3798</v>
       </c>
       <c r="D1062" s="6" t="s">
-        <v>6587</v>
+        <v>6589</v>
       </c>
       <c r="E1062" s="6" t="s">
-        <v>5255</v>
+        <v>3800</v>
       </c>
       <c r="F1062" s="6" t="s">
-        <v>3734</v>
+        <v>6590</v>
       </c>
       <c r="G1062" s="6" t="s">
-        <v>3735</v>
+        <v>6591</v>
       </c>
       <c r="H1062" s="6" t="s">
-        <v>5254</v>
+        <v>6592</v>
       </c>
     </row>
     <row r="1063">
       <c r="B1063" s="5" t="s">
-        <v>6588</v>
+        <v>6593</v>
       </c>
       <c r="C1063" s="5" t="s">
-        <v>5259</v>
+        <v>5260</v>
       </c>
       <c r="D1063" s="5" t="s">
-        <v>6589</v>
+        <v>6594</v>
       </c>
       <c r="E1063" s="5" t="s">
+        <v>5262</v>
+      </c>
+      <c r="F1063" s="5" t="s">
+        <v>3734</v>
+      </c>
+      <c r="G1063" s="5" t="s">
+        <v>3735</v>
+      </c>
+      <c r="H1063" s="5" t="s">
         <v>5261</v>
-      </c>
-      <c r="F1063" s="5" t="s">
-        <v>3741</v>
-      </c>
-      <c r="G1063" s="5" t="s">
-        <v>3741</v>
-      </c>
-      <c r="H1063" s="5" t="s">
-        <v>6590</v>
       </c>
     </row>
     <row r="1064">
       <c r="B1064" s="6" t="s">
-        <v>6591</v>
+        <v>6595</v>
       </c>
       <c r="C1064" s="6" t="s">
-        <v>5264</v>
+        <v>5266</v>
       </c>
       <c r="D1064" s="6" t="s">
-        <v>6592</v>
+        <v>6596</v>
       </c>
       <c r="E1064" s="6" t="s">
-        <v>5266</v>
+        <v>5268</v>
       </c>
       <c r="F1064" s="6" t="s">
-        <v>3747</v>
+        <v>3741</v>
       </c>
       <c r="G1064" s="6" t="s">
-        <v>3748</v>
+        <v>3741</v>
       </c>
       <c r="H1064" s="6" t="s">
-        <v>5269</v>
+        <v>6597</v>
       </c>
     </row>
     <row r="1065">
       <c r="B1065" s="5" t="s">
-        <v>6593</v>
+        <v>6598</v>
       </c>
       <c r="C1065" s="5" t="s">
-        <v>3764</v>
+        <v>5271</v>
       </c>
       <c r="D1065" s="5" t="s">
-        <v>6594</v>
+        <v>6599</v>
       </c>
       <c r="E1065" s="5" t="s">
-        <v>3766</v>
+        <v>5273</v>
       </c>
       <c r="F1065" s="5" t="s">
-        <v>3767</v>
+        <v>3747</v>
       </c>
       <c r="G1065" s="5" t="s">
-        <v>3768</v>
+        <v>3748</v>
       </c>
       <c r="H1065" s="5" t="s">
-        <v>6595</v>
+        <v>5276</v>
       </c>
     </row>
     <row r="1066">
       <c r="B1066" s="6" t="s">
-        <v>6596</v>
+        <v>6600</v>
       </c>
       <c r="C1066" s="6" t="s">
-        <v>6597</v>
+        <v>3764</v>
       </c>
       <c r="D1066" s="6" t="s">
-        <v>6598</v>
+        <v>6601</v>
       </c>
       <c r="E1066" s="6" t="s">
-        <v>3794</v>
+        <v>3766</v>
       </c>
       <c r="F1066" s="6" t="s">
-        <v>6599</v>
+        <v>3767</v>
       </c>
       <c r="G1066" s="6" t="s">
-        <v>6600</v>
+        <v>3768</v>
       </c>
       <c r="H1066" s="6" t="s">
-        <v>5251</v>
+        <v>6602</v>
       </c>
     </row>
     <row r="1067">
       <c r="B1067" s="5" t="s">
-        <v>6601</v>
+        <v>6603</v>
       </c>
       <c r="C1067" s="5" t="s">
-        <v>5239</v>
+        <v>6604</v>
       </c>
       <c r="D1067" s="5" t="s">
-        <v>6602</v>
+        <v>6605</v>
       </c>
       <c r="E1067" s="5" t="s">
-        <v>5241</v>
+        <v>3794</v>
       </c>
       <c r="F1067" s="5" t="s">
-        <v>6603</v>
+        <v>6606</v>
       </c>
       <c r="G1067" s="5" t="s">
-        <v>6603</v>
+        <v>6607</v>
       </c>
       <c r="H1067" s="5" t="s">
-        <v>6604</v>
+        <v>5258</v>
       </c>
     </row>
     <row r="1068">
       <c r="B1068" s="6" t="s">
-        <v>6605</v>
+        <v>6608</v>
       </c>
       <c r="C1068" s="6" t="s">
-        <v>6606</v>
+        <v>5246</v>
       </c>
       <c r="D1068" s="6" t="s">
-        <v>6607</v>
+        <v>6609</v>
       </c>
       <c r="E1068" s="6" t="s">
-        <v>6608</v>
+        <v>5248</v>
       </c>
       <c r="F1068" s="6" t="s">
-        <v>6609</v>
+        <v>6610</v>
       </c>
       <c r="G1068" s="6" t="s">
         <v>6610</v>
@@ -48316,45 +48358,45 @@
         <v>6612</v>
       </c>
       <c r="C1069" s="5" t="s">
-        <v>6504</v>
+        <v>6613</v>
       </c>
       <c r="D1069" s="5" t="s">
-        <v>6505</v>
+        <v>6614</v>
       </c>
       <c r="E1069" s="5" t="s">
-        <v>6506</v>
+        <v>6615</v>
       </c>
       <c r="F1069" s="5" t="s">
-        <v>6507</v>
+        <v>6616</v>
       </c>
       <c r="G1069" s="5" t="s">
-        <v>6508</v>
+        <v>6617</v>
       </c>
       <c r="H1069" s="5" t="s">
-        <v>6509</v>
+        <v>6618</v>
       </c>
     </row>
     <row r="1070">
       <c r="B1070" s="6" t="s">
-        <v>6613</v>
+        <v>6619</v>
       </c>
       <c r="C1070" s="6" t="s">
-        <v>6614</v>
+        <v>6511</v>
       </c>
       <c r="D1070" s="6" t="s">
-        <v>6615</v>
+        <v>6512</v>
       </c>
       <c r="E1070" s="6" t="s">
-        <v>6616</v>
+        <v>6513</v>
       </c>
       <c r="F1070" s="6" t="s">
-        <v>6617</v>
+        <v>6514</v>
       </c>
       <c r="G1070" s="6" t="s">
-        <v>6618</v>
+        <v>6515</v>
       </c>
       <c r="H1070" s="6" t="s">
-        <v>6619</v>
+        <v>6516</v>
       </c>
     </row>
     <row r="1071">
@@ -48489,27 +48531,27 @@
         <v>6659</v>
       </c>
       <c r="G1076" s="6" t="s">
-        <v>6659</v>
+        <v>6660</v>
       </c>
       <c r="H1076" s="6" t="s">
-        <v>6660</v>
+        <v>6661</v>
       </c>
     </row>
     <row r="1077">
       <c r="B1077" s="5" t="s">
-        <v>6661</v>
+        <v>6662</v>
       </c>
       <c r="C1077" s="5" t="s">
-        <v>6662</v>
+        <v>6663</v>
       </c>
       <c r="D1077" s="5" t="s">
-        <v>6663</v>
+        <v>6664</v>
       </c>
       <c r="E1077" s="5" t="s">
-        <v>6664</v>
+        <v>6665</v>
       </c>
       <c r="F1077" s="5" t="s">
-        <v>6665</v>
+        <v>6666</v>
       </c>
       <c r="G1077" s="5" t="s">
         <v>6666</v>
@@ -48742,27 +48784,27 @@
         <v>6735</v>
       </c>
       <c r="G1087" s="5" t="s">
-        <v>6735</v>
+        <v>6736</v>
       </c>
       <c r="H1087" s="5" t="s">
-        <v>6736</v>
+        <v>6737</v>
       </c>
     </row>
     <row r="1088">
       <c r="B1088" s="6" t="s">
-        <v>6737</v>
+        <v>6738</v>
       </c>
       <c r="C1088" s="6" t="s">
-        <v>6738</v>
+        <v>6739</v>
       </c>
       <c r="D1088" s="6" t="s">
-        <v>6739</v>
+        <v>6740</v>
       </c>
       <c r="E1088" s="6" t="s">
-        <v>6740</v>
+        <v>6741</v>
       </c>
       <c r="F1088" s="6" t="s">
-        <v>6741</v>
+        <v>6742</v>
       </c>
       <c r="G1088" s="6" t="s">
         <v>6742</v>
@@ -48785,33 +48827,33 @@
         <v>6747</v>
       </c>
       <c r="F1089" s="5" t="s">
-        <v>6665</v>
+        <v>6748</v>
       </c>
       <c r="G1089" s="5" t="s">
-        <v>6666</v>
+        <v>6749</v>
       </c>
       <c r="H1089" s="5" t="s">
-        <v>6748</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="1090">
       <c r="B1090" s="6" t="s">
-        <v>6749</v>
+        <v>6751</v>
       </c>
       <c r="C1090" s="6" t="s">
-        <v>6750</v>
+        <v>6752</v>
       </c>
       <c r="D1090" s="6" t="s">
-        <v>6751</v>
+        <v>6753</v>
       </c>
       <c r="E1090" s="6" t="s">
-        <v>6752</v>
+        <v>6754</v>
       </c>
       <c r="F1090" s="6" t="s">
-        <v>6753</v>
+        <v>6672</v>
       </c>
       <c r="G1090" s="6" t="s">
-        <v>6754</v>
+        <v>6673</v>
       </c>
       <c r="H1090" s="6" t="s">
         <v>6755</v>
@@ -48857,27 +48899,27 @@
         <v>6767</v>
       </c>
       <c r="G1092" s="6" t="s">
-        <v>6767</v>
+        <v>6768</v>
       </c>
       <c r="H1092" s="6" t="s">
-        <v>6768</v>
+        <v>6769</v>
       </c>
     </row>
     <row r="1093">
       <c r="B1093" s="5" t="s">
-        <v>6769</v>
+        <v>6770</v>
       </c>
       <c r="C1093" s="5" t="s">
-        <v>6770</v>
+        <v>6771</v>
       </c>
       <c r="D1093" s="5" t="s">
-        <v>6771</v>
+        <v>6772</v>
       </c>
       <c r="E1093" s="5" t="s">
-        <v>6772</v>
+        <v>6773</v>
       </c>
       <c r="F1093" s="5" t="s">
-        <v>6773</v>
+        <v>6774</v>
       </c>
       <c r="G1093" s="5" t="s">
         <v>6774</v>
@@ -48903,73 +48945,73 @@
         <v>6780</v>
       </c>
       <c r="G1094" s="6" t="s">
-        <v>6780</v>
+        <v>6781</v>
       </c>
       <c r="H1094" s="6" t="s">
-        <v>6781</v>
+        <v>6782</v>
       </c>
     </row>
     <row r="1095">
       <c r="B1095" s="5" t="s">
-        <v>6782</v>
+        <v>6783</v>
       </c>
       <c r="C1095" s="5" t="s">
-        <v>4517</v>
+        <v>6784</v>
       </c>
       <c r="D1095" s="5" t="s">
-        <v>6783</v>
+        <v>6785</v>
       </c>
       <c r="E1095" s="5" t="s">
-        <v>4519</v>
+        <v>6786</v>
       </c>
       <c r="F1095" s="5" t="s">
-        <v>4520</v>
+        <v>6787</v>
       </c>
       <c r="G1095" s="5" t="s">
-        <v>4521</v>
+        <v>6787</v>
       </c>
       <c r="H1095" s="5" t="s">
-        <v>4522</v>
+        <v>6788</v>
       </c>
     </row>
     <row r="1096">
       <c r="B1096" s="6" t="s">
-        <v>6784</v>
+        <v>6789</v>
       </c>
       <c r="C1096" s="6" t="s">
-        <v>6785</v>
+        <v>4517</v>
       </c>
       <c r="D1096" s="6" t="s">
-        <v>6786</v>
+        <v>6790</v>
       </c>
       <c r="E1096" s="6" t="s">
-        <v>6787</v>
+        <v>4519</v>
       </c>
       <c r="F1096" s="6" t="s">
-        <v>6788</v>
+        <v>4520</v>
       </c>
       <c r="G1096" s="6" t="s">
-        <v>6788</v>
+        <v>4521</v>
       </c>
       <c r="H1096" s="6" t="s">
-        <v>6789</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="1097">
       <c r="B1097" s="5" t="s">
-        <v>6790</v>
+        <v>6791</v>
       </c>
       <c r="C1097" s="5" t="s">
-        <v>6791</v>
+        <v>6792</v>
       </c>
       <c r="D1097" s="5" t="s">
-        <v>6792</v>
+        <v>6793</v>
       </c>
       <c r="E1097" s="5" t="s">
-        <v>6793</v>
+        <v>6794</v>
       </c>
       <c r="F1097" s="5" t="s">
-        <v>6794</v>
+        <v>6795</v>
       </c>
       <c r="G1097" s="5" t="s">
         <v>6795</v>
@@ -49018,27 +49060,27 @@
         <v>6808</v>
       </c>
       <c r="G1099" s="5" t="s">
-        <v>6808</v>
+        <v>6809</v>
       </c>
       <c r="H1099" s="5" t="s">
-        <v>6809</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="1100">
       <c r="B1100" s="6" t="s">
-        <v>6810</v>
+        <v>6811</v>
       </c>
       <c r="C1100" s="6" t="s">
-        <v>6811</v>
+        <v>6812</v>
       </c>
       <c r="D1100" s="6" t="s">
-        <v>6812</v>
+        <v>6813</v>
       </c>
       <c r="E1100" s="6" t="s">
-        <v>6813</v>
+        <v>6814</v>
       </c>
       <c r="F1100" s="6" t="s">
-        <v>6814</v>
+        <v>6815</v>
       </c>
       <c r="G1100" s="6" t="s">
         <v>6815</v>
@@ -49098,45 +49140,45 @@
         <v>6831</v>
       </c>
       <c r="C1103" s="5" t="s">
-        <v>6785</v>
+        <v>6832</v>
       </c>
       <c r="D1103" s="5" t="s">
-        <v>6786</v>
+        <v>6833</v>
       </c>
       <c r="E1103" s="5" t="s">
-        <v>6787</v>
+        <v>6834</v>
       </c>
       <c r="F1103" s="5" t="s">
-        <v>6788</v>
+        <v>6835</v>
       </c>
       <c r="G1103" s="5" t="s">
-        <v>6788</v>
+        <v>6836</v>
       </c>
       <c r="H1103" s="5" t="s">
-        <v>6789</v>
+        <v>6837</v>
       </c>
     </row>
     <row r="1104">
       <c r="B1104" s="6" t="s">
-        <v>6832</v>
+        <v>6838</v>
       </c>
       <c r="C1104" s="6" t="s">
-        <v>6833</v>
+        <v>6792</v>
       </c>
       <c r="D1104" s="6" t="s">
-        <v>6834</v>
+        <v>6793</v>
       </c>
       <c r="E1104" s="6" t="s">
-        <v>6835</v>
+        <v>6794</v>
       </c>
       <c r="F1104" s="6" t="s">
-        <v>6836</v>
+        <v>6795</v>
       </c>
       <c r="G1104" s="6" t="s">
-        <v>6837</v>
+        <v>6795</v>
       </c>
       <c r="H1104" s="6" t="s">
-        <v>6838</v>
+        <v>6796</v>
       </c>
     </row>
     <row r="1105">
@@ -49259,111 +49301,111 @@
         <v>6874</v>
       </c>
       <c r="C1110" s="6" t="s">
-        <v>4624</v>
+        <v>6875</v>
       </c>
       <c r="D1110" s="6" t="s">
-        <v>6875</v>
+        <v>6876</v>
       </c>
       <c r="E1110" s="6" t="s">
-        <v>4626</v>
+        <v>6877</v>
       </c>
       <c r="F1110" s="6" t="s">
-        <v>6522</v>
+        <v>6878</v>
       </c>
       <c r="G1110" s="6" t="s">
-        <v>6523</v>
+        <v>6879</v>
       </c>
       <c r="H1110" s="6" t="s">
-        <v>6876</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="1111">
       <c r="B1111" s="5" t="s">
-        <v>6877</v>
+        <v>6881</v>
       </c>
       <c r="C1111" s="5" t="s">
-        <v>4791</v>
+        <v>4624</v>
       </c>
       <c r="D1111" s="5" t="s">
-        <v>4568</v>
+        <v>6882</v>
       </c>
       <c r="E1111" s="5" t="s">
-        <v>4792</v>
+        <v>4626</v>
       </c>
       <c r="F1111" s="5" t="s">
-        <v>4793</v>
+        <v>6529</v>
       </c>
       <c r="G1111" s="5" t="s">
-        <v>4794</v>
+        <v>6530</v>
       </c>
       <c r="H1111" s="5" t="s">
-        <v>4568</v>
+        <v>6883</v>
       </c>
     </row>
     <row r="1112">
       <c r="B1112" s="6" t="s">
-        <v>6878</v>
+        <v>6884</v>
       </c>
       <c r="C1112" s="6" t="s">
-        <v>6504</v>
+        <v>4791</v>
       </c>
       <c r="D1112" s="6" t="s">
-        <v>6879</v>
+        <v>4568</v>
       </c>
       <c r="E1112" s="6" t="s">
-        <v>6506</v>
+        <v>4792</v>
       </c>
       <c r="F1112" s="6" t="s">
-        <v>6507</v>
+        <v>4793</v>
       </c>
       <c r="G1112" s="6" t="s">
-        <v>6508</v>
+        <v>4794</v>
       </c>
       <c r="H1112" s="6" t="s">
-        <v>6880</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="1113">
       <c r="B1113" s="5" t="s">
-        <v>6881</v>
+        <v>6885</v>
       </c>
       <c r="C1113" s="5" t="s">
-        <v>6882</v>
+        <v>6511</v>
       </c>
       <c r="D1113" s="5" t="s">
-        <v>6883</v>
+        <v>6886</v>
       </c>
       <c r="E1113" s="5" t="s">
-        <v>6884</v>
+        <v>6513</v>
       </c>
       <c r="F1113" s="5" t="s">
-        <v>6885</v>
+        <v>6514</v>
       </c>
       <c r="G1113" s="5" t="s">
-        <v>6884</v>
+        <v>6515</v>
       </c>
       <c r="H1113" s="5" t="s">
-        <v>6886</v>
+        <v>6887</v>
       </c>
     </row>
     <row r="1114">
       <c r="B1114" s="6" t="s">
-        <v>6887</v>
+        <v>6888</v>
       </c>
       <c r="C1114" s="6" t="s">
-        <v>6888</v>
+        <v>6889</v>
       </c>
       <c r="D1114" s="6" t="s">
-        <v>6889</v>
+        <v>6890</v>
       </c>
       <c r="E1114" s="6" t="s">
-        <v>6890</v>
+        <v>6891</v>
       </c>
       <c r="F1114" s="6" t="s">
+        <v>6892</v>
+      </c>
+      <c r="G1114" s="6" t="s">
         <v>6891</v>
-      </c>
-      <c r="G1114" s="6" t="s">
-        <v>6892</v>
       </c>
       <c r="H1114" s="6" t="s">
         <v>6893</v>
@@ -49449,30 +49491,30 @@
         <v>6917</v>
       </c>
       <c r="E1118" s="6" t="s">
-        <v>3172</v>
+        <v>6918</v>
       </c>
       <c r="F1118" s="6" t="s">
-        <v>6918</v>
+        <v>6919</v>
       </c>
       <c r="G1118" s="6" t="s">
-        <v>6919</v>
+        <v>6920</v>
       </c>
       <c r="H1118" s="6" t="s">
-        <v>6920</v>
+        <v>6921</v>
       </c>
     </row>
     <row r="1119">
       <c r="B1119" s="5" t="s">
-        <v>6921</v>
+        <v>6922</v>
       </c>
       <c r="C1119" s="5" t="s">
-        <v>6922</v>
+        <v>6923</v>
       </c>
       <c r="D1119" s="5" t="s">
-        <v>6923</v>
+        <v>6924</v>
       </c>
       <c r="E1119" s="5" t="s">
-        <v>6924</v>
+        <v>3172</v>
       </c>
       <c r="F1119" s="5" t="s">
         <v>6925</v>
@@ -49557,115 +49599,115 @@
       <c r="B1123" s="5" t="s">
         <v>6949</v>
       </c>
-      <c r="C1123" s="7" t="s">
+      <c r="C1123" s="5" t="s">
         <v>6950</v>
       </c>
-      <c r="D1123" s="7" t="s">
-        <v>6950</v>
-      </c>
-      <c r="E1123" s="7" t="s">
-        <v>6950</v>
-      </c>
-      <c r="F1123" s="7" t="s">
-        <v>6950</v>
-      </c>
-      <c r="G1123" s="7" t="s">
-        <v>6950</v>
-      </c>
-      <c r="H1123" s="7" t="s">
-        <v>6950</v>
+      <c r="D1123" s="5" t="s">
+        <v>6951</v>
+      </c>
+      <c r="E1123" s="5" t="s">
+        <v>6952</v>
+      </c>
+      <c r="F1123" s="5" t="s">
+        <v>6953</v>
+      </c>
+      <c r="G1123" s="5" t="s">
+        <v>6954</v>
+      </c>
+      <c r="H1123" s="5" t="s">
+        <v>6955</v>
       </c>
     </row>
     <row r="1124">
       <c r="B1124" s="6" t="s">
-        <v>6951</v>
-      </c>
-      <c r="C1124" s="6" t="s">
-        <v>6364</v>
-      </c>
-      <c r="D1124" s="6" t="s">
-        <v>6365</v>
-      </c>
-      <c r="E1124" s="6" t="s">
-        <v>6366</v>
-      </c>
-      <c r="F1124" s="6" t="s">
-        <v>6367</v>
-      </c>
-      <c r="G1124" s="6" t="s">
-        <v>6368</v>
-      </c>
-      <c r="H1124" s="6" t="s">
-        <v>6365</v>
+        <v>6956</v>
+      </c>
+      <c r="C1124" s="7" t="s">
+        <v>6957</v>
+      </c>
+      <c r="D1124" s="7" t="s">
+        <v>6957</v>
+      </c>
+      <c r="E1124" s="7" t="s">
+        <v>6957</v>
+      </c>
+      <c r="F1124" s="7" t="s">
+        <v>6957</v>
+      </c>
+      <c r="G1124" s="7" t="s">
+        <v>6957</v>
+      </c>
+      <c r="H1124" s="7" t="s">
+        <v>6957</v>
       </c>
     </row>
     <row r="1125">
       <c r="B1125" s="5" t="s">
-        <v>6952</v>
+        <v>6958</v>
       </c>
       <c r="C1125" s="5" t="s">
-        <v>6953</v>
+        <v>6371</v>
       </c>
       <c r="D1125" s="5" t="s">
-        <v>6954</v>
+        <v>6372</v>
       </c>
       <c r="E1125" s="5" t="s">
-        <v>6955</v>
+        <v>6373</v>
       </c>
       <c r="F1125" s="5" t="s">
-        <v>6956</v>
+        <v>6374</v>
       </c>
       <c r="G1125" s="5" t="s">
-        <v>6956</v>
+        <v>6375</v>
       </c>
       <c r="H1125" s="5" t="s">
-        <v>4649</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="1126">
       <c r="B1126" s="6" t="s">
-        <v>6957</v>
+        <v>6959</v>
       </c>
       <c r="C1126" s="6" t="s">
-        <v>6958</v>
+        <v>6960</v>
       </c>
       <c r="D1126" s="6" t="s">
-        <v>6959</v>
+        <v>6961</v>
       </c>
       <c r="E1126" s="6" t="s">
-        <v>6960</v>
+        <v>6962</v>
       </c>
       <c r="F1126" s="6" t="s">
-        <v>6961</v>
+        <v>6963</v>
       </c>
       <c r="G1126" s="6" t="s">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="H1126" s="6" t="s">
-        <v>3835</v>
+        <v>4649</v>
       </c>
     </row>
     <row r="1127">
       <c r="B1127" s="5" t="s">
-        <v>6963</v>
+        <v>6964</v>
       </c>
       <c r="C1127" s="5" t="s">
-        <v>6964</v>
+        <v>6965</v>
       </c>
       <c r="D1127" s="5" t="s">
-        <v>6965</v>
+        <v>6966</v>
       </c>
       <c r="E1127" s="5" t="s">
-        <v>6966</v>
+        <v>6967</v>
       </c>
       <c r="F1127" s="5" t="s">
-        <v>6967</v>
+        <v>6968</v>
       </c>
       <c r="G1127" s="5" t="s">
-        <v>6968</v>
+        <v>6969</v>
       </c>
       <c r="H1127" s="5" t="s">
-        <v>6969</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="1128">
@@ -49708,27 +49750,27 @@
         <v>6981</v>
       </c>
       <c r="G1129" s="5" t="s">
-        <v>6981</v>
+        <v>6982</v>
       </c>
       <c r="H1129" s="5" t="s">
-        <v>6982</v>
+        <v>6983</v>
       </c>
     </row>
     <row r="1130">
       <c r="B1130" s="6" t="s">
-        <v>6983</v>
+        <v>6984</v>
       </c>
       <c r="C1130" s="6" t="s">
-        <v>6984</v>
+        <v>6985</v>
       </c>
       <c r="D1130" s="6" t="s">
-        <v>6985</v>
+        <v>6986</v>
       </c>
       <c r="E1130" s="6" t="s">
-        <v>6986</v>
+        <v>6987</v>
       </c>
       <c r="F1130" s="6" t="s">
-        <v>6987</v>
+        <v>6988</v>
       </c>
       <c r="G1130" s="6" t="s">
         <v>6988</v>
@@ -49754,102 +49796,102 @@
         <v>6994</v>
       </c>
       <c r="G1131" s="5" t="s">
-        <v>6994</v>
+        <v>6995</v>
       </c>
       <c r="H1131" s="5" t="s">
-        <v>6995</v>
+        <v>6996</v>
       </c>
     </row>
     <row r="1132">
       <c r="B1132" s="6" t="s">
-        <v>6996</v>
+        <v>6997</v>
       </c>
       <c r="C1132" s="6" t="s">
-        <v>6997</v>
+        <v>6998</v>
       </c>
       <c r="D1132" s="6" t="s">
-        <v>6997</v>
+        <v>6999</v>
       </c>
       <c r="E1132" s="6" t="s">
-        <v>6997</v>
+        <v>7000</v>
       </c>
       <c r="F1132" s="6" t="s">
-        <v>6997</v>
+        <v>7001</v>
       </c>
       <c r="G1132" s="6" t="s">
-        <v>6997</v>
+        <v>7001</v>
       </c>
       <c r="H1132" s="6" t="s">
-        <v>6997</v>
+        <v>7002</v>
       </c>
     </row>
     <row r="1133">
       <c r="B1133" s="5" t="s">
-        <v>6998</v>
+        <v>7003</v>
       </c>
       <c r="C1133" s="5" t="s">
-        <v>6999</v>
+        <v>7004</v>
       </c>
       <c r="D1133" s="5" t="s">
-        <v>7000</v>
+        <v>7004</v>
       </c>
       <c r="E1133" s="5" t="s">
-        <v>7001</v>
+        <v>7004</v>
       </c>
       <c r="F1133" s="5" t="s">
-        <v>7002</v>
+        <v>7004</v>
       </c>
       <c r="G1133" s="5" t="s">
-        <v>7002</v>
+        <v>7004</v>
       </c>
       <c r="H1133" s="5" t="s">
-        <v>7003</v>
+        <v>7004</v>
       </c>
     </row>
     <row r="1134">
       <c r="B1134" s="6" t="s">
-        <v>7004</v>
+        <v>7005</v>
       </c>
       <c r="C1134" s="6" t="s">
-        <v>6997</v>
+        <v>7006</v>
       </c>
       <c r="D1134" s="6" t="s">
-        <v>6997</v>
+        <v>7007</v>
       </c>
       <c r="E1134" s="6" t="s">
-        <v>6997</v>
+        <v>7008</v>
       </c>
       <c r="F1134" s="6" t="s">
-        <v>6997</v>
+        <v>7009</v>
       </c>
       <c r="G1134" s="6" t="s">
-        <v>6997</v>
+        <v>7009</v>
       </c>
       <c r="H1134" s="6" t="s">
-        <v>6997</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="1135">
       <c r="B1135" s="5" t="s">
-        <v>7005</v>
+        <v>7011</v>
       </c>
       <c r="C1135" s="5" t="s">
-        <v>7006</v>
+        <v>7004</v>
       </c>
       <c r="D1135" s="5" t="s">
-        <v>7007</v>
+        <v>7004</v>
       </c>
       <c r="E1135" s="5" t="s">
-        <v>7008</v>
+        <v>7004</v>
       </c>
       <c r="F1135" s="5" t="s">
-        <v>7009</v>
+        <v>7004</v>
       </c>
       <c r="G1135" s="5" t="s">
-        <v>7010</v>
+        <v>7004</v>
       </c>
       <c r="H1135" s="5" t="s">
-        <v>7011</v>
+        <v>7004</v>
       </c>
     </row>
     <row r="1136">
@@ -49926,39 +49968,39 @@
         <v>7033</v>
       </c>
       <c r="C1139" s="5" t="s">
-        <v>3830</v>
+        <v>7034</v>
       </c>
       <c r="D1139" s="5" t="s">
-        <v>7034</v>
+        <v>7035</v>
       </c>
       <c r="E1139" s="5" t="s">
-        <v>3832</v>
+        <v>7036</v>
       </c>
       <c r="F1139" s="5" t="s">
-        <v>7035</v>
+        <v>7037</v>
       </c>
       <c r="G1139" s="5" t="s">
-        <v>7035</v>
+        <v>7038</v>
       </c>
       <c r="H1139" s="5" t="s">
-        <v>7036</v>
+        <v>7039</v>
       </c>
     </row>
     <row r="1140">
       <c r="B1140" s="6" t="s">
-        <v>7037</v>
+        <v>7040</v>
       </c>
       <c r="C1140" s="6" t="s">
-        <v>7038</v>
+        <v>3830</v>
       </c>
       <c r="D1140" s="6" t="s">
-        <v>7039</v>
+        <v>7041</v>
       </c>
       <c r="E1140" s="6" t="s">
-        <v>7040</v>
+        <v>3832</v>
       </c>
       <c r="F1140" s="6" t="s">
-        <v>7041</v>
+        <v>7042</v>
       </c>
       <c r="G1140" s="6" t="s">
         <v>7042</v>
@@ -50067,59 +50109,59 @@
         <v>7073</v>
       </c>
       <c r="D1145" s="5" t="s">
-        <v>7073</v>
+        <v>7074</v>
       </c>
       <c r="E1145" s="5" t="s">
-        <v>7073</v>
+        <v>7075</v>
       </c>
       <c r="F1145" s="5" t="s">
-        <v>7073</v>
+        <v>7076</v>
       </c>
       <c r="G1145" s="5" t="s">
-        <v>7073</v>
+        <v>7077</v>
       </c>
       <c r="H1145" s="5" t="s">
-        <v>7073</v>
+        <v>7078</v>
       </c>
     </row>
     <row r="1146">
       <c r="B1146" s="6" t="s">
-        <v>7074</v>
+        <v>7079</v>
       </c>
       <c r="C1146" s="6" t="s">
-        <v>7075</v>
+        <v>7080</v>
       </c>
       <c r="D1146" s="6" t="s">
-        <v>7076</v>
+        <v>7080</v>
       </c>
       <c r="E1146" s="6" t="s">
-        <v>7077</v>
+        <v>7080</v>
       </c>
       <c r="F1146" s="6" t="s">
-        <v>7078</v>
+        <v>7080</v>
       </c>
       <c r="G1146" s="6" t="s">
-        <v>7078</v>
+        <v>7080</v>
       </c>
       <c r="H1146" s="6" t="s">
-        <v>7079</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="1147">
       <c r="B1147" s="5" t="s">
-        <v>7080</v>
+        <v>7081</v>
       </c>
       <c r="C1147" s="5" t="s">
-        <v>7081</v>
+        <v>7082</v>
       </c>
       <c r="D1147" s="5" t="s">
-        <v>7082</v>
+        <v>7083</v>
       </c>
       <c r="E1147" s="5" t="s">
-        <v>7083</v>
+        <v>7084</v>
       </c>
       <c r="F1147" s="5" t="s">
-        <v>7084</v>
+        <v>7085</v>
       </c>
       <c r="G1147" s="5" t="s">
         <v>7085</v>
@@ -50168,50 +50210,50 @@
         <v>7098</v>
       </c>
       <c r="G1149" s="5" t="s">
-        <v>7098</v>
+        <v>7099</v>
       </c>
       <c r="H1149" s="5" t="s">
-        <v>7099</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="1150">
       <c r="B1150" s="6" t="s">
-        <v>7100</v>
+        <v>7101</v>
       </c>
       <c r="C1150" s="6" t="s">
-        <v>7101</v>
+        <v>7102</v>
       </c>
       <c r="D1150" s="6" t="s">
-        <v>7102</v>
+        <v>7103</v>
       </c>
       <c r="E1150" s="6" t="s">
-        <v>7103</v>
+        <v>7104</v>
       </c>
       <c r="F1150" s="6" t="s">
-        <v>7104</v>
+        <v>7105</v>
       </c>
       <c r="G1150" s="6" t="s">
-        <v>7104</v>
+        <v>7105</v>
       </c>
       <c r="H1150" s="6" t="s">
-        <v>7105</v>
+        <v>7106</v>
       </c>
     </row>
     <row r="1151">
       <c r="B1151" s="5" t="s">
-        <v>7106</v>
+        <v>7107</v>
       </c>
       <c r="C1151" s="5" t="s">
-        <v>7107</v>
+        <v>7108</v>
       </c>
       <c r="D1151" s="5" t="s">
-        <v>7108</v>
+        <v>7109</v>
       </c>
       <c r="E1151" s="5" t="s">
-        <v>7109</v>
+        <v>7110</v>
       </c>
       <c r="F1151" s="5" t="s">
-        <v>7110</v>
+        <v>7111</v>
       </c>
       <c r="G1151" s="5" t="s">
         <v>7111</v>
@@ -50478,36 +50520,36 @@
         <v>7190</v>
       </c>
       <c r="C1163" s="5" t="s">
-        <v>2300</v>
+        <v>7191</v>
       </c>
       <c r="D1163" s="5" t="s">
-        <v>7191</v>
+        <v>7192</v>
       </c>
       <c r="E1163" s="5" t="s">
-        <v>2302</v>
+        <v>7193</v>
       </c>
       <c r="F1163" s="5" t="s">
-        <v>7192</v>
+        <v>7194</v>
       </c>
       <c r="G1163" s="5" t="s">
-        <v>7193</v>
+        <v>7195</v>
       </c>
       <c r="H1163" s="5" t="s">
-        <v>7194</v>
+        <v>7196</v>
       </c>
     </row>
     <row r="1164">
       <c r="B1164" s="6" t="s">
-        <v>7195</v>
+        <v>7197</v>
       </c>
       <c r="C1164" s="6" t="s">
-        <v>7196</v>
+        <v>2300</v>
       </c>
       <c r="D1164" s="6" t="s">
-        <v>7197</v>
+        <v>7198</v>
       </c>
       <c r="E1164" s="6" t="s">
-        <v>7198</v>
+        <v>2302</v>
       </c>
       <c r="F1164" s="6" t="s">
         <v>7199</v>
@@ -50582,27 +50624,27 @@
         <v>7220</v>
       </c>
       <c r="G1167" s="5" t="s">
-        <v>7220</v>
+        <v>7221</v>
       </c>
       <c r="H1167" s="5" t="s">
-        <v>7221</v>
+        <v>7222</v>
       </c>
     </row>
     <row r="1168">
       <c r="B1168" s="6" t="s">
-        <v>7222</v>
+        <v>7223</v>
       </c>
       <c r="C1168" s="6" t="s">
-        <v>7223</v>
+        <v>7224</v>
       </c>
       <c r="D1168" s="6" t="s">
-        <v>7224</v>
+        <v>7225</v>
       </c>
       <c r="E1168" s="6" t="s">
-        <v>7225</v>
+        <v>7226</v>
       </c>
       <c r="F1168" s="6" t="s">
-        <v>7226</v>
+        <v>7227</v>
       </c>
       <c r="G1168" s="6" t="s">
         <v>7227</v>
@@ -50674,27 +50716,27 @@
         <v>7247</v>
       </c>
       <c r="G1171" s="5" t="s">
-        <v>7247</v>
+        <v>7248</v>
       </c>
       <c r="H1171" s="5" t="s">
-        <v>7248</v>
+        <v>7249</v>
       </c>
     </row>
     <row r="1172">
       <c r="B1172" s="6" t="s">
-        <v>7249</v>
+        <v>7250</v>
       </c>
       <c r="C1172" s="6" t="s">
-        <v>7250</v>
+        <v>7251</v>
       </c>
       <c r="D1172" s="6" t="s">
-        <v>7251</v>
+        <v>7252</v>
       </c>
       <c r="E1172" s="6" t="s">
-        <v>7252</v>
+        <v>7253</v>
       </c>
       <c r="F1172" s="6" t="s">
-        <v>7253</v>
+        <v>7254</v>
       </c>
       <c r="G1172" s="6" t="s">
         <v>7254</v>
@@ -50777,85 +50819,85 @@
         <v>7277</v>
       </c>
       <c r="C1176" s="6" t="s">
-        <v>3830</v>
+        <v>7278</v>
       </c>
       <c r="D1176" s="6" t="s">
-        <v>7034</v>
+        <v>7279</v>
       </c>
       <c r="E1176" s="6" t="s">
-        <v>7278</v>
+        <v>7280</v>
       </c>
       <c r="F1176" s="6" t="s">
-        <v>7035</v>
+        <v>7281</v>
       </c>
       <c r="G1176" s="6" t="s">
-        <v>7035</v>
+        <v>7282</v>
       </c>
       <c r="H1176" s="6" t="s">
-        <v>7036</v>
+        <v>7283</v>
       </c>
     </row>
     <row r="1177">
       <c r="B1177" s="5" t="s">
-        <v>7279</v>
+        <v>7284</v>
       </c>
       <c r="C1177" s="5" t="s">
-        <v>7280</v>
+        <v>3830</v>
       </c>
       <c r="D1177" s="5" t="s">
-        <v>7281</v>
+        <v>7041</v>
       </c>
       <c r="E1177" s="5" t="s">
-        <v>7282</v>
+        <v>7285</v>
       </c>
       <c r="F1177" s="5" t="s">
-        <v>7283</v>
+        <v>7042</v>
       </c>
       <c r="G1177" s="5" t="s">
-        <v>7283</v>
+        <v>7042</v>
       </c>
       <c r="H1177" s="5" t="s">
-        <v>7284</v>
+        <v>7043</v>
       </c>
     </row>
     <row r="1178">
       <c r="B1178" s="6" t="s">
-        <v>7285</v>
+        <v>7286</v>
       </c>
       <c r="C1178" s="6" t="s">
-        <v>7286</v>
+        <v>7287</v>
       </c>
       <c r="D1178" s="6" t="s">
-        <v>7287</v>
+        <v>7288</v>
       </c>
       <c r="E1178" s="6" t="s">
-        <v>7288</v>
+        <v>7289</v>
       </c>
       <c r="F1178" s="6" t="s">
-        <v>7289</v>
+        <v>7290</v>
       </c>
       <c r="G1178" s="6" t="s">
-        <v>7289</v>
+        <v>7290</v>
       </c>
       <c r="H1178" s="6" t="s">
-        <v>7290</v>
+        <v>7291</v>
       </c>
     </row>
     <row r="1179">
       <c r="B1179" s="5" t="s">
-        <v>7291</v>
+        <v>7292</v>
       </c>
       <c r="C1179" s="5" t="s">
-        <v>7292</v>
+        <v>7293</v>
       </c>
       <c r="D1179" s="5" t="s">
-        <v>7293</v>
+        <v>7294</v>
       </c>
       <c r="E1179" s="5" t="s">
-        <v>7294</v>
+        <v>7295</v>
       </c>
       <c r="F1179" s="5" t="s">
-        <v>7295</v>
+        <v>7296</v>
       </c>
       <c r="G1179" s="5" t="s">
         <v>7296</v>
@@ -50950,148 +50992,148 @@
         <v>7323</v>
       </c>
       <c r="G1183" s="5" t="s">
-        <v>7323</v>
+        <v>7324</v>
       </c>
       <c r="H1183" s="5" t="s">
-        <v>7324</v>
+        <v>7325</v>
       </c>
     </row>
     <row r="1184">
       <c r="B1184" s="6" t="s">
-        <v>7325</v>
+        <v>7326</v>
       </c>
       <c r="C1184" s="6" t="s">
-        <v>7326</v>
+        <v>7327</v>
       </c>
       <c r="D1184" s="6" t="s">
-        <v>7327</v>
+        <v>7328</v>
       </c>
       <c r="E1184" s="6" t="s">
-        <v>7328</v>
+        <v>7329</v>
       </c>
       <c r="F1184" s="6" t="s">
-        <v>7329</v>
+        <v>7330</v>
       </c>
       <c r="G1184" s="6" t="s">
-        <v>7328</v>
+        <v>7330</v>
       </c>
       <c r="H1184" s="6" t="s">
-        <v>7330</v>
+        <v>7331</v>
       </c>
     </row>
     <row r="1185">
       <c r="B1185" s="5" t="s">
-        <v>7331</v>
+        <v>7332</v>
       </c>
       <c r="C1185" s="5" t="s">
-        <v>7332</v>
+        <v>7333</v>
       </c>
       <c r="D1185" s="5" t="s">
-        <v>7333</v>
+        <v>7334</v>
       </c>
       <c r="E1185" s="5" t="s">
-        <v>4667</v>
+        <v>7335</v>
       </c>
       <c r="F1185" s="5" t="s">
-        <v>7334</v>
+        <v>7336</v>
       </c>
       <c r="G1185" s="5" t="s">
-        <v>7334</v>
+        <v>7335</v>
       </c>
       <c r="H1185" s="5" t="s">
-        <v>4670</v>
+        <v>7337</v>
       </c>
     </row>
     <row r="1186">
       <c r="B1186" s="6" t="s">
-        <v>7335</v>
+        <v>7338</v>
       </c>
       <c r="C1186" s="6" t="s">
-        <v>7336</v>
+        <v>7339</v>
       </c>
       <c r="D1186" s="6" t="s">
-        <v>7337</v>
+        <v>7340</v>
       </c>
       <c r="E1186" s="6" t="s">
-        <v>7338</v>
+        <v>4667</v>
       </c>
       <c r="F1186" s="6" t="s">
-        <v>7339</v>
+        <v>7341</v>
       </c>
       <c r="G1186" s="6" t="s">
-        <v>7339</v>
+        <v>7341</v>
       </c>
       <c r="H1186" s="6" t="s">
-        <v>7340</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="1187">
       <c r="B1187" s="5" t="s">
-        <v>7341</v>
+        <v>7342</v>
       </c>
       <c r="C1187" s="5" t="s">
-        <v>7342</v>
+        <v>7343</v>
       </c>
       <c r="D1187" s="5" t="s">
-        <v>6889</v>
+        <v>7344</v>
       </c>
       <c r="E1187" s="5" t="s">
-        <v>7343</v>
+        <v>7345</v>
       </c>
       <c r="F1187" s="5" t="s">
-        <v>7344</v>
+        <v>7346</v>
       </c>
       <c r="G1187" s="5" t="s">
-        <v>7344</v>
+        <v>7346</v>
       </c>
       <c r="H1187" s="5" t="s">
-        <v>6893</v>
+        <v>7347</v>
       </c>
     </row>
     <row r="1188">
       <c r="B1188" s="6" t="s">
-        <v>7345</v>
+        <v>7348</v>
       </c>
       <c r="C1188" s="6" t="s">
-        <v>7346</v>
+        <v>7349</v>
       </c>
       <c r="D1188" s="6" t="s">
-        <v>5105</v>
+        <v>6896</v>
       </c>
       <c r="E1188" s="6" t="s">
-        <v>3653</v>
+        <v>7350</v>
       </c>
       <c r="F1188" s="6" t="s">
-        <v>7347</v>
+        <v>7351</v>
       </c>
       <c r="G1188" s="6" t="s">
-        <v>7347</v>
+        <v>7351</v>
       </c>
       <c r="H1188" s="6" t="s">
-        <v>3656</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="1189">
       <c r="B1189" s="5" t="s">
-        <v>7348</v>
+        <v>7352</v>
       </c>
       <c r="C1189" s="5" t="s">
-        <v>7349</v>
+        <v>7353</v>
       </c>
       <c r="D1189" s="5" t="s">
-        <v>7350</v>
+        <v>5105</v>
       </c>
       <c r="E1189" s="5" t="s">
-        <v>7351</v>
+        <v>3653</v>
       </c>
       <c r="F1189" s="5" t="s">
-        <v>7352</v>
+        <v>7354</v>
       </c>
       <c r="G1189" s="5" t="s">
-        <v>7353</v>
+        <v>7354</v>
       </c>
       <c r="H1189" s="5" t="s">
-        <v>7354</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="1190">
@@ -51134,27 +51176,27 @@
         <v>7366</v>
       </c>
       <c r="G1191" s="5" t="s">
-        <v>7366</v>
+        <v>7367</v>
       </c>
       <c r="H1191" s="5" t="s">
-        <v>7367</v>
+        <v>7368</v>
       </c>
     </row>
     <row r="1192">
       <c r="B1192" s="6" t="s">
-        <v>7368</v>
+        <v>7369</v>
       </c>
       <c r="C1192" s="6" t="s">
-        <v>7369</v>
+        <v>7370</v>
       </c>
       <c r="D1192" s="6" t="s">
-        <v>7370</v>
+        <v>7371</v>
       </c>
       <c r="E1192" s="6" t="s">
-        <v>7371</v>
+        <v>7372</v>
       </c>
       <c r="F1192" s="6" t="s">
-        <v>7372</v>
+        <v>7373</v>
       </c>
       <c r="G1192" s="6" t="s">
         <v>7373</v>
@@ -51260,62 +51302,62 @@
         <v>7403</v>
       </c>
       <c r="C1197" s="5" t="s">
-        <v>2255</v>
+        <v>7404</v>
       </c>
       <c r="D1197" s="5" t="s">
-        <v>7404</v>
+        <v>7405</v>
       </c>
       <c r="E1197" s="5" t="s">
-        <v>5328</v>
+        <v>7406</v>
       </c>
       <c r="F1197" s="5" t="s">
-        <v>7405</v>
+        <v>7407</v>
       </c>
       <c r="G1197" s="5" t="s">
-        <v>7406</v>
+        <v>7408</v>
       </c>
       <c r="H1197" s="5" t="s">
-        <v>5325</v>
+        <v>7409</v>
       </c>
     </row>
     <row r="1198">
       <c r="B1198" s="6" t="s">
-        <v>7407</v>
+        <v>7410</v>
       </c>
       <c r="C1198" s="6" t="s">
-        <v>7408</v>
+        <v>2255</v>
       </c>
       <c r="D1198" s="6" t="s">
-        <v>7409</v>
+        <v>7411</v>
       </c>
       <c r="E1198" s="6" t="s">
-        <v>7410</v>
+        <v>5335</v>
       </c>
       <c r="F1198" s="6" t="s">
-        <v>7411</v>
+        <v>7412</v>
       </c>
       <c r="G1198" s="6" t="s">
-        <v>7411</v>
+        <v>7413</v>
       </c>
       <c r="H1198" s="6" t="s">
-        <v>7412</v>
+        <v>5332</v>
       </c>
     </row>
     <row r="1199">
       <c r="B1199" s="5" t="s">
-        <v>7413</v>
+        <v>7414</v>
       </c>
       <c r="C1199" s="5" t="s">
-        <v>7414</v>
+        <v>7415</v>
       </c>
       <c r="D1199" s="5" t="s">
-        <v>7415</v>
+        <v>7416</v>
       </c>
       <c r="E1199" s="5" t="s">
-        <v>7416</v>
+        <v>7417</v>
       </c>
       <c r="F1199" s="5" t="s">
-        <v>7417</v>
+        <v>7418</v>
       </c>
       <c r="G1199" s="5" t="s">
         <v>7418</v>
@@ -51410,96 +51452,96 @@
         <v>7445</v>
       </c>
       <c r="G1203" s="5" t="s">
-        <v>7445</v>
+        <v>7446</v>
       </c>
       <c r="H1203" s="5" t="s">
-        <v>7446</v>
+        <v>7447</v>
       </c>
     </row>
     <row r="1204">
       <c r="B1204" s="6" t="s">
-        <v>7447</v>
+        <v>7448</v>
       </c>
       <c r="C1204" s="6" t="s">
-        <v>7448</v>
+        <v>7449</v>
       </c>
       <c r="D1204" s="6" t="s">
-        <v>7449</v>
+        <v>7450</v>
       </c>
       <c r="E1204" s="6" t="s">
-        <v>7450</v>
+        <v>7451</v>
       </c>
       <c r="F1204" s="6" t="s">
-        <v>7451</v>
+        <v>7452</v>
       </c>
       <c r="G1204" s="6" t="s">
-        <v>7451</v>
+        <v>7452</v>
       </c>
       <c r="H1204" s="6" t="s">
-        <v>2253</v>
+        <v>7453</v>
       </c>
     </row>
     <row r="1205">
       <c r="B1205" s="5" t="s">
-        <v>7452</v>
+        <v>7454</v>
       </c>
       <c r="C1205" s="5" t="s">
-        <v>7453</v>
+        <v>7455</v>
       </c>
       <c r="D1205" s="5" t="s">
-        <v>7454</v>
+        <v>7456</v>
       </c>
       <c r="E1205" s="5" t="s">
-        <v>7455</v>
+        <v>7457</v>
       </c>
       <c r="F1205" s="5" t="s">
-        <v>7456</v>
+        <v>7458</v>
       </c>
       <c r="G1205" s="5" t="s">
-        <v>7457</v>
+        <v>7458</v>
       </c>
       <c r="H1205" s="5" t="s">
-        <v>6535</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="1206">
       <c r="B1206" s="6" t="s">
-        <v>7458</v>
+        <v>7459</v>
       </c>
       <c r="C1206" s="6" t="s">
-        <v>7459</v>
+        <v>7460</v>
       </c>
       <c r="D1206" s="6" t="s">
-        <v>4511</v>
+        <v>7461</v>
       </c>
       <c r="E1206" s="6" t="s">
-        <v>4512</v>
+        <v>7462</v>
       </c>
       <c r="F1206" s="6" t="s">
-        <v>7460</v>
+        <v>7463</v>
       </c>
       <c r="G1206" s="6" t="s">
-        <v>7460</v>
+        <v>7464</v>
       </c>
       <c r="H1206" s="6" t="s">
-        <v>7461</v>
+        <v>6542</v>
       </c>
     </row>
     <row r="1207">
       <c r="B1207" s="5" t="s">
-        <v>7462</v>
+        <v>7465</v>
       </c>
       <c r="C1207" s="5" t="s">
-        <v>7463</v>
+        <v>7466</v>
       </c>
       <c r="D1207" s="5" t="s">
-        <v>7464</v>
+        <v>4511</v>
       </c>
       <c r="E1207" s="5" t="s">
-        <v>7465</v>
+        <v>4512</v>
       </c>
       <c r="F1207" s="5" t="s">
-        <v>7466</v>
+        <v>7467</v>
       </c>
       <c r="G1207" s="5" t="s">
         <v>7467</v>
@@ -51513,45 +51555,45 @@
         <v>7469</v>
       </c>
       <c r="C1208" s="6" t="s">
-        <v>6504</v>
+        <v>7470</v>
       </c>
       <c r="D1208" s="6" t="s">
-        <v>6879</v>
+        <v>7471</v>
       </c>
       <c r="E1208" s="6" t="s">
-        <v>6506</v>
+        <v>7472</v>
       </c>
       <c r="F1208" s="6" t="s">
-        <v>6507</v>
+        <v>7473</v>
       </c>
       <c r="G1208" s="6" t="s">
-        <v>6508</v>
+        <v>7474</v>
       </c>
       <c r="H1208" s="6" t="s">
-        <v>6880</v>
+        <v>7475</v>
       </c>
     </row>
     <row r="1209">
       <c r="B1209" s="5" t="s">
-        <v>7470</v>
+        <v>7476</v>
       </c>
       <c r="C1209" s="5" t="s">
-        <v>7471</v>
+        <v>6511</v>
       </c>
       <c r="D1209" s="5" t="s">
-        <v>7472</v>
+        <v>6886</v>
       </c>
       <c r="E1209" s="5" t="s">
-        <v>7473</v>
+        <v>6513</v>
       </c>
       <c r="F1209" s="5" t="s">
-        <v>7474</v>
+        <v>6514</v>
       </c>
       <c r="G1209" s="5" t="s">
-        <v>7475</v>
+        <v>6515</v>
       </c>
       <c r="H1209" s="5" t="s">
-        <v>7476</v>
+        <v>6887</v>
       </c>
     </row>
     <row r="1210">
@@ -51582,102 +51624,102 @@
         <v>7484</v>
       </c>
       <c r="C1211" s="5" t="s">
-        <v>4775</v>
+        <v>7485</v>
       </c>
       <c r="D1211" s="5" t="s">
-        <v>7485</v>
+        <v>7486</v>
       </c>
       <c r="E1211" s="5" t="s">
-        <v>4777</v>
+        <v>7487</v>
       </c>
       <c r="F1211" s="5" t="s">
-        <v>4778</v>
+        <v>7488</v>
       </c>
       <c r="G1211" s="5" t="s">
-        <v>4778</v>
+        <v>7489</v>
       </c>
       <c r="H1211" s="5" t="s">
-        <v>7486</v>
+        <v>7490</v>
       </c>
     </row>
     <row r="1212">
       <c r="B1212" s="6" t="s">
-        <v>7487</v>
+        <v>7491</v>
       </c>
       <c r="C1212" s="6" t="s">
-        <v>5289</v>
+        <v>4775</v>
       </c>
       <c r="D1212" s="6" t="s">
-        <v>7488</v>
+        <v>7492</v>
       </c>
       <c r="E1212" s="6" t="s">
-        <v>5291</v>
+        <v>4777</v>
       </c>
       <c r="F1212" s="6" t="s">
-        <v>5292</v>
+        <v>4778</v>
       </c>
       <c r="G1212" s="6" t="s">
-        <v>5292</v>
+        <v>4778</v>
       </c>
       <c r="H1212" s="6" t="s">
-        <v>7489</v>
+        <v>7493</v>
       </c>
     </row>
     <row r="1213">
       <c r="B1213" s="5" t="s">
-        <v>7490</v>
+        <v>7494</v>
       </c>
       <c r="C1213" s="5" t="s">
-        <v>7491</v>
+        <v>5296</v>
       </c>
       <c r="D1213" s="5" t="s">
-        <v>7492</v>
+        <v>7495</v>
       </c>
       <c r="E1213" s="5" t="s">
-        <v>7465</v>
+        <v>5298</v>
       </c>
       <c r="F1213" s="5" t="s">
-        <v>7493</v>
+        <v>5299</v>
       </c>
       <c r="G1213" s="5" t="s">
-        <v>7494</v>
+        <v>5299</v>
       </c>
       <c r="H1213" s="5" t="s">
-        <v>7495</v>
+        <v>7496</v>
       </c>
     </row>
     <row r="1214">
       <c r="B1214" s="6" t="s">
-        <v>7496</v>
+        <v>7497</v>
       </c>
       <c r="C1214" s="6" t="s">
-        <v>5100</v>
+        <v>7498</v>
       </c>
       <c r="D1214" s="6" t="s">
-        <v>4530</v>
+        <v>7499</v>
       </c>
       <c r="E1214" s="6" t="s">
-        <v>7497</v>
+        <v>7472</v>
       </c>
       <c r="F1214" s="6" t="s">
-        <v>7498</v>
+        <v>7500</v>
       </c>
       <c r="G1214" s="6" t="s">
-        <v>7499</v>
+        <v>7501</v>
       </c>
       <c r="H1214" s="6" t="s">
-        <v>7500</v>
+        <v>7502</v>
       </c>
     </row>
     <row r="1215">
       <c r="B1215" s="5" t="s">
-        <v>7501</v>
+        <v>7503</v>
       </c>
       <c r="C1215" s="5" t="s">
-        <v>7502</v>
+        <v>5100</v>
       </c>
       <c r="D1215" s="5" t="s">
-        <v>7503</v>
+        <v>4530</v>
       </c>
       <c r="E1215" s="5" t="s">
         <v>7504</v>
@@ -51847,50 +51889,50 @@
         <v>7554</v>
       </c>
       <c r="G1222" s="6" t="s">
-        <v>7554</v>
+        <v>7555</v>
       </c>
       <c r="H1222" s="6" t="s">
-        <v>7555</v>
+        <v>7556</v>
       </c>
     </row>
     <row r="1223">
       <c r="B1223" s="5" t="s">
-        <v>7556</v>
+        <v>7557</v>
       </c>
       <c r="C1223" s="5" t="s">
-        <v>7557</v>
+        <v>7558</v>
       </c>
       <c r="D1223" s="5" t="s">
-        <v>7558</v>
+        <v>7559</v>
       </c>
       <c r="E1223" s="5" t="s">
-        <v>7559</v>
+        <v>7560</v>
       </c>
       <c r="F1223" s="5" t="s">
-        <v>7560</v>
+        <v>7561</v>
       </c>
       <c r="G1223" s="5" t="s">
-        <v>7560</v>
+        <v>7561</v>
       </c>
       <c r="H1223" s="5" t="s">
-        <v>7561</v>
+        <v>7562</v>
       </c>
     </row>
     <row r="1224">
       <c r="B1224" s="6" t="s">
-        <v>7562</v>
+        <v>7563</v>
       </c>
       <c r="C1224" s="6" t="s">
-        <v>7563</v>
+        <v>7564</v>
       </c>
       <c r="D1224" s="6" t="s">
-        <v>7564</v>
+        <v>7565</v>
       </c>
       <c r="E1224" s="6" t="s">
-        <v>7565</v>
+        <v>7566</v>
       </c>
       <c r="F1224" s="6" t="s">
-        <v>7566</v>
+        <v>7567</v>
       </c>
       <c r="G1224" s="6" t="s">
         <v>7567</v>
@@ -51999,88 +52041,88 @@
         <v>7598</v>
       </c>
       <c r="D1229" s="5" t="s">
-        <v>6565</v>
+        <v>7599</v>
       </c>
       <c r="E1229" s="5" t="s">
-        <v>7599</v>
+        <v>7600</v>
       </c>
       <c r="F1229" s="5" t="s">
-        <v>5715</v>
+        <v>7601</v>
       </c>
       <c r="G1229" s="5" t="s">
-        <v>5716</v>
+        <v>7602</v>
       </c>
       <c r="H1229" s="5" t="s">
-        <v>7600</v>
+        <v>7603</v>
       </c>
     </row>
     <row r="1230">
       <c r="B1230" s="6" t="s">
-        <v>7601</v>
+        <v>7604</v>
       </c>
       <c r="C1230" s="6" t="s">
-        <v>7602</v>
+        <v>7605</v>
       </c>
       <c r="D1230" s="6" t="s">
-        <v>6570</v>
+        <v>6572</v>
       </c>
       <c r="E1230" s="6" t="s">
-        <v>5135</v>
+        <v>7606</v>
       </c>
       <c r="F1230" s="6" t="s">
-        <v>6572</v>
+        <v>5722</v>
       </c>
       <c r="G1230" s="6" t="s">
-        <v>6573</v>
+        <v>5723</v>
       </c>
       <c r="H1230" s="6" t="s">
-        <v>6574</v>
+        <v>7607</v>
       </c>
     </row>
     <row r="1231">
       <c r="B1231" s="5" t="s">
-        <v>7603</v>
+        <v>7608</v>
       </c>
       <c r="C1231" s="5" t="s">
-        <v>4679</v>
+        <v>7609</v>
       </c>
       <c r="D1231" s="5" t="s">
-        <v>4680</v>
+        <v>6577</v>
       </c>
       <c r="E1231" s="5" t="s">
-        <v>7604</v>
+        <v>5135</v>
       </c>
       <c r="F1231" s="5" t="s">
-        <v>7605</v>
+        <v>6579</v>
       </c>
       <c r="G1231" s="5" t="s">
-        <v>7606</v>
+        <v>6580</v>
       </c>
       <c r="H1231" s="5" t="s">
-        <v>4684</v>
+        <v>6581</v>
       </c>
     </row>
     <row r="1232">
       <c r="B1232" s="6" t="s">
-        <v>7607</v>
+        <v>7610</v>
       </c>
       <c r="C1232" s="6" t="s">
-        <v>7608</v>
+        <v>4679</v>
       </c>
       <c r="D1232" s="6" t="s">
-        <v>7609</v>
+        <v>4680</v>
       </c>
       <c r="E1232" s="6" t="s">
-        <v>7610</v>
+        <v>7611</v>
       </c>
       <c r="F1232" s="6" t="s">
-        <v>7611</v>
+        <v>7612</v>
       </c>
       <c r="G1232" s="6" t="s">
-        <v>7612</v>
+        <v>7613</v>
       </c>
       <c r="H1232" s="6" t="s">
-        <v>7613</v>
+        <v>4684</v>
       </c>
     </row>
     <row r="1233">
@@ -52123,38 +52165,38 @@
         <v>7625</v>
       </c>
       <c r="G1234" s="6" t="s">
-        <v>7625</v>
+        <v>7626</v>
       </c>
       <c r="H1234" s="6" t="s">
-        <v>7626</v>
+        <v>7627</v>
       </c>
     </row>
     <row r="1235">
       <c r="B1235" s="5" t="s">
-        <v>7627</v>
+        <v>7628</v>
       </c>
       <c r="C1235" s="5" t="s">
-        <v>7622</v>
+        <v>7629</v>
       </c>
       <c r="D1235" s="5" t="s">
-        <v>7623</v>
+        <v>7630</v>
       </c>
       <c r="E1235" s="5" t="s">
-        <v>7624</v>
+        <v>7631</v>
       </c>
       <c r="F1235" s="5" t="s">
-        <v>7625</v>
+        <v>7632</v>
       </c>
       <c r="G1235" s="5" t="s">
-        <v>7625</v>
+        <v>7632</v>
       </c>
       <c r="H1235" s="5" t="s">
-        <v>7626</v>
+        <v>7633</v>
       </c>
     </row>
     <row r="1236">
       <c r="B1236" s="6" t="s">
-        <v>7628</v>
+        <v>7634</v>
       </c>
       <c r="C1236" s="6" t="s">
         <v>7629</v>
@@ -52169,10 +52211,10 @@
         <v>7632</v>
       </c>
       <c r="G1236" s="6" t="s">
+        <v>7632</v>
+      </c>
+      <c r="H1236" s="6" t="s">
         <v>7633</v>
-      </c>
-      <c r="H1236" s="6" t="s">
-        <v>7634</v>
       </c>
     </row>
     <row r="1237">
@@ -52215,217 +52257,217 @@
         <v>7646</v>
       </c>
       <c r="G1238" s="6" t="s">
-        <v>7646</v>
+        <v>7647</v>
       </c>
       <c r="H1238" s="6" t="s">
-        <v>7647</v>
+        <v>7648</v>
       </c>
     </row>
     <row r="1239">
       <c r="B1239" s="5" t="s">
-        <v>7648</v>
+        <v>7649</v>
       </c>
       <c r="C1239" s="5" t="s">
-        <v>3751</v>
+        <v>7650</v>
       </c>
       <c r="D1239" s="5" t="s">
-        <v>3123</v>
+        <v>7651</v>
       </c>
       <c r="E1239" s="5" t="s">
-        <v>3753</v>
+        <v>7652</v>
       </c>
       <c r="F1239" s="5" t="s">
-        <v>5956</v>
+        <v>7653</v>
       </c>
       <c r="G1239" s="5" t="s">
-        <v>5956</v>
+        <v>7653</v>
       </c>
       <c r="H1239" s="5" t="s">
-        <v>3123</v>
+        <v>7654</v>
       </c>
     </row>
     <row r="1240">
       <c r="B1240" s="6" t="s">
-        <v>7649</v>
+        <v>7655</v>
       </c>
       <c r="C1240" s="6" t="s">
-        <v>3805</v>
+        <v>3751</v>
       </c>
       <c r="D1240" s="6" t="s">
-        <v>7650</v>
+        <v>3123</v>
       </c>
       <c r="E1240" s="6" t="s">
-        <v>3807</v>
+        <v>3753</v>
       </c>
       <c r="F1240" s="6" t="s">
-        <v>3808</v>
+        <v>5963</v>
       </c>
       <c r="G1240" s="6" t="s">
-        <v>3807</v>
+        <v>5963</v>
       </c>
       <c r="H1240" s="6" t="s">
-        <v>3809</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="1241">
       <c r="B1241" s="5" t="s">
-        <v>7651</v>
+        <v>7656</v>
       </c>
       <c r="C1241" s="5" t="s">
-        <v>3811</v>
+        <v>3805</v>
       </c>
       <c r="D1241" s="5" t="s">
-        <v>7652</v>
+        <v>7657</v>
       </c>
       <c r="E1241" s="5" t="s">
-        <v>3813</v>
+        <v>3807</v>
       </c>
       <c r="F1241" s="5" t="s">
-        <v>7653</v>
+        <v>3808</v>
       </c>
       <c r="G1241" s="5" t="s">
-        <v>7654</v>
+        <v>3807</v>
       </c>
       <c r="H1241" s="5" t="s">
-        <v>3816</v>
+        <v>3809</v>
       </c>
     </row>
     <row r="1242">
       <c r="B1242" s="6" t="s">
-        <v>7655</v>
+        <v>7658</v>
       </c>
       <c r="C1242" s="6" t="s">
-        <v>3818</v>
+        <v>3811</v>
       </c>
       <c r="D1242" s="6" t="s">
-        <v>3822</v>
+        <v>7659</v>
       </c>
       <c r="E1242" s="6" t="s">
-        <v>3820</v>
+        <v>3813</v>
       </c>
       <c r="F1242" s="6" t="s">
-        <v>3821</v>
+        <v>7660</v>
       </c>
       <c r="G1242" s="6" t="s">
-        <v>3821</v>
+        <v>7661</v>
       </c>
       <c r="H1242" s="6" t="s">
-        <v>3822</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="1243">
       <c r="B1243" s="5" t="s">
-        <v>7656</v>
+        <v>7662</v>
       </c>
       <c r="C1243" s="5" t="s">
-        <v>4619</v>
+        <v>3818</v>
       </c>
       <c r="D1243" s="5" t="s">
-        <v>4804</v>
+        <v>3822</v>
       </c>
       <c r="E1243" s="5" t="s">
-        <v>4621</v>
+        <v>3820</v>
       </c>
       <c r="F1243" s="5" t="s">
-        <v>4622</v>
+        <v>3821</v>
       </c>
       <c r="G1243" s="5" t="s">
-        <v>4622</v>
+        <v>3821</v>
       </c>
       <c r="H1243" s="5" t="s">
-        <v>4804</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="1244">
       <c r="B1244" s="6" t="s">
-        <v>7657</v>
+        <v>7663</v>
       </c>
       <c r="C1244" s="6" t="s">
-        <v>5239</v>
+        <v>7664</v>
       </c>
       <c r="D1244" s="6" t="s">
-        <v>5240</v>
+        <v>7665</v>
       </c>
       <c r="E1244" s="6" t="s">
-        <v>5241</v>
+        <v>7666</v>
       </c>
       <c r="F1244" s="6" t="s">
-        <v>5240</v>
+        <v>7667</v>
       </c>
       <c r="G1244" s="6" t="s">
-        <v>5240</v>
+        <v>7668</v>
       </c>
       <c r="H1244" s="6" t="s">
-        <v>5240</v>
+        <v>7669</v>
       </c>
     </row>
     <row r="1245">
       <c r="B1245" s="5" t="s">
-        <v>7658</v>
+        <v>7670</v>
       </c>
       <c r="C1245" s="5" t="s">
-        <v>4624</v>
+        <v>4619</v>
       </c>
       <c r="D1245" s="5" t="s">
-        <v>6875</v>
+        <v>4804</v>
       </c>
       <c r="E1245" s="5" t="s">
-        <v>4626</v>
+        <v>4621</v>
       </c>
       <c r="F1245" s="5" t="s">
-        <v>4251</v>
+        <v>4622</v>
       </c>
       <c r="G1245" s="5" t="s">
-        <v>4251</v>
+        <v>4622</v>
       </c>
       <c r="H1245" s="5" t="s">
-        <v>6876</v>
+        <v>4804</v>
       </c>
     </row>
     <row r="1246">
       <c r="B1246" s="6" t="s">
-        <v>7659</v>
+        <v>7671</v>
       </c>
       <c r="C1246" s="6" t="s">
-        <v>7660</v>
+        <v>5246</v>
       </c>
       <c r="D1246" s="6" t="s">
-        <v>7661</v>
+        <v>5247</v>
       </c>
       <c r="E1246" s="6" t="s">
-        <v>7662</v>
+        <v>5248</v>
       </c>
       <c r="F1246" s="6" t="s">
-        <v>7663</v>
+        <v>5247</v>
       </c>
       <c r="G1246" s="6" t="s">
-        <v>7664</v>
+        <v>5247</v>
       </c>
       <c r="H1246" s="6" t="s">
-        <v>7665</v>
+        <v>5247</v>
       </c>
     </row>
     <row r="1247">
       <c r="B1247" s="5" t="s">
-        <v>7666</v>
+        <v>7672</v>
       </c>
       <c r="C1247" s="5" t="s">
-        <v>7667</v>
+        <v>4624</v>
       </c>
       <c r="D1247" s="5" t="s">
-        <v>7668</v>
+        <v>6882</v>
       </c>
       <c r="E1247" s="5" t="s">
-        <v>7669</v>
+        <v>4626</v>
       </c>
       <c r="F1247" s="5" t="s">
-        <v>7670</v>
+        <v>4251</v>
       </c>
       <c r="G1247" s="5" t="s">
-        <v>7671</v>
+        <v>4251</v>
       </c>
       <c r="H1247" s="5" t="s">
-        <v>7672</v>
+        <v>6883</v>
       </c>
     </row>
     <row r="1248">
@@ -52514,50 +52556,50 @@
         <v>7698</v>
       </c>
       <c r="G1251" s="5" t="s">
-        <v>7698</v>
+        <v>7699</v>
       </c>
       <c r="H1251" s="5" t="s">
-        <v>7699</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="1252">
       <c r="B1252" s="6" t="s">
-        <v>7700</v>
+        <v>7701</v>
       </c>
       <c r="C1252" s="6" t="s">
-        <v>7701</v>
+        <v>7702</v>
       </c>
       <c r="D1252" s="6" t="s">
-        <v>7702</v>
+        <v>7703</v>
       </c>
       <c r="E1252" s="6" t="s">
-        <v>7703</v>
+        <v>7704</v>
       </c>
       <c r="F1252" s="6" t="s">
-        <v>7704</v>
+        <v>7705</v>
       </c>
       <c r="G1252" s="6" t="s">
-        <v>7705</v>
+        <v>7706</v>
       </c>
       <c r="H1252" s="6" t="s">
-        <v>7706</v>
+        <v>7707</v>
       </c>
     </row>
     <row r="1253">
       <c r="B1253" s="5" t="s">
-        <v>7707</v>
+        <v>7708</v>
       </c>
       <c r="C1253" s="5" t="s">
-        <v>7708</v>
+        <v>7709</v>
       </c>
       <c r="D1253" s="5" t="s">
-        <v>7709</v>
+        <v>7710</v>
       </c>
       <c r="E1253" s="5" t="s">
-        <v>7710</v>
+        <v>7711</v>
       </c>
       <c r="F1253" s="5" t="s">
-        <v>7711</v>
+        <v>7712</v>
       </c>
       <c r="G1253" s="5" t="s">
         <v>7712</v>
@@ -52666,65 +52708,65 @@
         <v>7743</v>
       </c>
       <c r="D1258" s="6" t="s">
-        <v>7464</v>
+        <v>7744</v>
       </c>
       <c r="E1258" s="6" t="s">
-        <v>7744</v>
+        <v>7745</v>
       </c>
       <c r="F1258" s="6" t="s">
-        <v>7466</v>
+        <v>7746</v>
       </c>
       <c r="G1258" s="6" t="s">
-        <v>7467</v>
+        <v>7747</v>
       </c>
       <c r="H1258" s="6" t="s">
-        <v>7468</v>
+        <v>7748</v>
       </c>
     </row>
     <row r="1259">
       <c r="B1259" s="5" t="s">
-        <v>7745</v>
+        <v>7749</v>
       </c>
       <c r="C1259" s="5" t="s">
-        <v>7746</v>
+        <v>7750</v>
       </c>
       <c r="D1259" s="5" t="s">
-        <v>7747</v>
+        <v>7751</v>
       </c>
       <c r="E1259" s="5" t="s">
-        <v>7748</v>
+        <v>7752</v>
       </c>
       <c r="F1259" s="5" t="s">
-        <v>7749</v>
+        <v>7753</v>
       </c>
       <c r="G1259" s="5" t="s">
-        <v>7750</v>
+        <v>7754</v>
       </c>
       <c r="H1259" s="5" t="s">
-        <v>7751</v>
+        <v>7755</v>
       </c>
     </row>
     <row r="1260">
       <c r="B1260" s="6" t="s">
-        <v>7752</v>
+        <v>7756</v>
       </c>
       <c r="C1260" s="6" t="s">
-        <v>7753</v>
+        <v>7757</v>
       </c>
       <c r="D1260" s="6" t="s">
-        <v>7754</v>
+        <v>7471</v>
       </c>
       <c r="E1260" s="6" t="s">
-        <v>7755</v>
+        <v>7758</v>
       </c>
       <c r="F1260" s="6" t="s">
-        <v>7756</v>
+        <v>7473</v>
       </c>
       <c r="G1260" s="6" t="s">
-        <v>7757</v>
+        <v>7474</v>
       </c>
       <c r="H1260" s="6" t="s">
-        <v>7758</v>
+        <v>7475</v>
       </c>
     </row>
     <row r="1261">
@@ -52732,68 +52774,68 @@
         <v>7759</v>
       </c>
       <c r="C1261" s="5" t="s">
-        <v>4679</v>
+        <v>7760</v>
       </c>
       <c r="D1261" s="5" t="s">
-        <v>4680</v>
+        <v>7761</v>
       </c>
       <c r="E1261" s="5" t="s">
-        <v>4681</v>
+        <v>7762</v>
       </c>
       <c r="F1261" s="5" t="s">
-        <v>7760</v>
+        <v>7763</v>
       </c>
       <c r="G1261" s="5" t="s">
-        <v>7761</v>
+        <v>7764</v>
       </c>
       <c r="H1261" s="5" t="s">
-        <v>4684</v>
+        <v>7765</v>
       </c>
     </row>
     <row r="1262">
       <c r="B1262" s="6" t="s">
-        <v>7762</v>
+        <v>7766</v>
       </c>
       <c r="C1262" s="6" t="s">
-        <v>7763</v>
+        <v>7767</v>
       </c>
       <c r="D1262" s="6" t="s">
-        <v>7764</v>
+        <v>7768</v>
       </c>
       <c r="E1262" s="6" t="s">
-        <v>7765</v>
+        <v>7769</v>
       </c>
       <c r="F1262" s="6" t="s">
-        <v>7766</v>
+        <v>7770</v>
       </c>
       <c r="G1262" s="6" t="s">
-        <v>7767</v>
+        <v>7771</v>
       </c>
       <c r="H1262" s="6" t="s">
-        <v>7768</v>
+        <v>7772</v>
       </c>
     </row>
     <row r="1263">
       <c r="B1263" s="5" t="s">
-        <v>7769</v>
+        <v>7773</v>
       </c>
       <c r="C1263" s="5" t="s">
-        <v>7770</v>
+        <v>4679</v>
       </c>
       <c r="D1263" s="5" t="s">
-        <v>7771</v>
+        <v>4680</v>
       </c>
       <c r="E1263" s="5" t="s">
-        <v>7772</v>
+        <v>4681</v>
       </c>
       <c r="F1263" s="5" t="s">
-        <v>7773</v>
+        <v>7774</v>
       </c>
       <c r="G1263" s="5" t="s">
-        <v>7774</v>
+        <v>7775</v>
       </c>
       <c r="H1263" s="5" t="s">
-        <v>7775</v>
+        <v>4684</v>
       </c>
     </row>
     <row r="1264">
@@ -52870,49 +52912,95 @@
         <v>7797</v>
       </c>
       <c r="C1267" s="5" t="s">
-        <v>4798</v>
+        <v>7798</v>
       </c>
       <c r="D1267" s="5" t="s">
-        <v>4799</v>
+        <v>7799</v>
       </c>
       <c r="E1267" s="5" t="s">
-        <v>4800</v>
+        <v>7800</v>
       </c>
       <c r="F1267" s="5" t="s">
-        <v>4801</v>
+        <v>7801</v>
       </c>
       <c r="G1267" s="5" t="s">
-        <v>4801</v>
+        <v>7802</v>
       </c>
       <c r="H1267" s="5" t="s">
-        <v>4802</v>
+        <v>7803</v>
       </c>
     </row>
     <row r="1268">
       <c r="B1268" s="6" t="s">
-        <v>7798</v>
+        <v>7804</v>
       </c>
       <c r="C1268" s="6" t="s">
+        <v>7805</v>
+      </c>
+      <c r="D1268" s="6" t="s">
+        <v>7806</v>
+      </c>
+      <c r="E1268" s="6" t="s">
+        <v>7807</v>
+      </c>
+      <c r="F1268" s="6" t="s">
+        <v>7808</v>
+      </c>
+      <c r="G1268" s="6" t="s">
+        <v>7809</v>
+      </c>
+      <c r="H1268" s="6" t="s">
+        <v>7810</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="B1269" s="5" t="s">
+        <v>7811</v>
+      </c>
+      <c r="C1269" s="5" t="s">
+        <v>4798</v>
+      </c>
+      <c r="D1269" s="5" t="s">
+        <v>4799</v>
+      </c>
+      <c r="E1269" s="5" t="s">
+        <v>4800</v>
+      </c>
+      <c r="F1269" s="5" t="s">
+        <v>4801</v>
+      </c>
+      <c r="G1269" s="5" t="s">
+        <v>4801</v>
+      </c>
+      <c r="H1269" s="5" t="s">
+        <v>4802</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="B1270" s="6" t="s">
+        <v>7812</v>
+      </c>
+      <c r="C1270" s="6" t="s">
         <v>2178</v>
       </c>
-      <c r="D1268" s="6" t="s">
+      <c r="D1270" s="6" t="s">
         <v>2179</v>
       </c>
-      <c r="E1268" s="6" t="s">
+      <c r="E1270" s="6" t="s">
         <v>2180</v>
       </c>
-      <c r="F1268" s="6" t="s">
+      <c r="F1270" s="6" t="s">
         <v>2181</v>
       </c>
-      <c r="G1268" s="6" t="s">
+      <c r="G1270" s="6" t="s">
         <v>2182</v>
       </c>
-      <c r="H1268" s="6" t="s">
+      <c r="H1270" s="6" t="s">
         <v>2183</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H1268"/>
+  <autoFilter ref="B2:H1270"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -52931,10 +53019,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>7799</v>
+        <v>7813</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7800</v>
+        <v>7814</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -52945,16 +53033,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7801</v>
+        <v>7815</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7802</v>
+        <v>7816</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7803</v>
+        <v>7817</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>7804</v>
+        <v>7818</v>
       </c>
     </row>
     <row r="3">
@@ -52962,16 +53050,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7805</v>
+        <v>7819</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>7806</v>
+        <v>7820</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>7807</v>
+        <v>7821</v>
       </c>
     </row>
     <row r="4">
@@ -52982,24 +53070,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>7808</v>
+        <v>7822</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>7809</v>
+        <v>7823</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>7810</v>
+        <v>7824</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>7811</v>
+        <v>7825</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2287</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>7812</v>
+        <v>7826</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -53007,13 +53095,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>7813</v>
+        <v>7827</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2294</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>7814</v>
+        <v>7828</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -53021,13 +53109,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>7815</v>
+        <v>7829</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2300</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>7816</v>
+        <v>7830</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -53035,13 +53123,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>7817</v>
+        <v>7831</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2306</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>7818</v>
+        <v>7832</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -53049,13 +53137,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>7819</v>
+        <v>7833</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2313</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>7820</v>
+        <v>7834</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -53063,13 +53151,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>7821</v>
+        <v>7835</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2320</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>7822</v>
+        <v>7836</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -53077,13 +53165,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>7823</v>
+        <v>7837</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2326</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>7824</v>
+        <v>7838</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -53091,13 +53179,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>7825</v>
+        <v>7839</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2332</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>7826</v>
+        <v>7840</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -53105,13 +53193,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>7827</v>
+        <v>7841</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2339</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>7828</v>
+        <v>7842</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -53119,13 +53207,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>7829</v>
+        <v>7843</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2345</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>7830</v>
+        <v>7844</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -53139,7 +53227,7 @@
         <v>2352</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>7831</v>
+        <v>7845</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -53147,13 +53235,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>7832</v>
+        <v>7846</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2359</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>7833</v>
+        <v>7847</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -53161,13 +53249,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>7834</v>
+        <v>7848</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2366</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>7835</v>
+        <v>7849</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -53175,13 +53263,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>7836</v>
+        <v>7850</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2372</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>7837</v>
+        <v>7851</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -53189,13 +53277,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>7838</v>
+        <v>7852</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2379</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>7839</v>
+        <v>7853</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -53203,13 +53291,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>7840</v>
+        <v>7854</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2385</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>7841</v>
+        <v>7855</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -53217,13 +53305,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>7842</v>
+        <v>7856</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2390</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>7843</v>
+        <v>7857</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -53231,13 +53319,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>7844</v>
+        <v>7858</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2397</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>7845</v>
+        <v>7859</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -53245,13 +53333,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>7846</v>
+        <v>7860</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2222</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>7847</v>
+        <v>7861</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -53259,13 +53347,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>7848</v>
+        <v>7862</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2405</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>7849</v>
+        <v>7863</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>
